--- a/2026/BELGRANO 1646/Julio/Julio-BLG1646.xlsx
+++ b/2026/BELGRANO 1646/Julio/Julio-BLG1646.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101C1336-D563-462B-A840-693CA6712C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF79FA4F-F6DF-4F79-B6AB-B7E927FC5007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$129</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$130</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="146">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -429,30 +434,9 @@
     <t xml:space="preserve">Articulos de limpieza </t>
   </si>
   <si>
-    <t>Servisur - Reloj timer y programacion - 2 plafones externos de 12w</t>
-  </si>
-  <si>
     <t>Cerrajeria - Servicio de cerrajeria sobre control de acceso</t>
   </si>
   <si>
-    <t>Julio Doartero - Emergencia electrica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Alejo Simonassi </t>
-  </si>
-  <si>
-    <t>Sra. Abogada Edith Bragonzi (Abogada Sr Simonassi)</t>
-  </si>
-  <si>
-    <t>Sr. Servian Cesar - Mediador</t>
-  </si>
-  <si>
-    <t>Sr. Gabriel Villegas - Abogado Consorcio</t>
-  </si>
-  <si>
-    <t>Convenio de pago sindicato abogado Maximiliano Oliver</t>
-  </si>
-  <si>
     <t>Entendiendo que en su momento, se le habia cobrado al Sr. Simonassi $3.000.000, la diferencia entre lo gastado ($6.579.071,62) y el monto mencionado se prorrateara como extraordinario en los proximos dos meses ($1.789.535)</t>
   </si>
   <si>
@@ -477,28 +461,46 @@
     <t>Ingreso mes de JUNIO</t>
   </si>
   <si>
-    <t>Casa Ruan - Compra de materiales electricos</t>
-  </si>
-  <si>
     <t>SA seguridad - En concepto de servicio tecnico realizado por sistema cctv camaras de seguridad</t>
   </si>
   <si>
     <t>Gastañaga Sebastian - Encarrilar y destrabar paño metalico instalacion automatica</t>
   </si>
   <si>
-    <t>Sra. Mary - Reemplazo</t>
-  </si>
-  <si>
     <t>Mediacion Sr. Simonassi</t>
   </si>
   <si>
-    <t xml:space="preserve">Energroup </t>
-  </si>
-  <si>
     <t>Doartero julio - Rreparacion techo de baño - Mano de obra y materiales</t>
   </si>
   <si>
     <t>Contessi - Provision y colocacion de 40 litros de aceite hidraulico a la central del montaautos</t>
+  </si>
+  <si>
+    <t>Energroup - Mes anterior</t>
+  </si>
+  <si>
+    <t>Casa Ruan - Compra de materiales electricos - Luces de emergencias</t>
+  </si>
+  <si>
+    <t>Gastañaga Sebastian - Compra de motor persiana cochera</t>
+  </si>
+  <si>
+    <t>DÉBITO AUTOMÁTICO – DEUDA POR OBRA SOCIAL MAL LIQUIDADA (EXPLICADO EN EXPENSAS ANTERIORES)</t>
+  </si>
+  <si>
+    <t>Sra. Monica  - Reemplazo</t>
+  </si>
+  <si>
+    <t>Seguro Sra. Monica</t>
+  </si>
+  <si>
+    <t>Gastañaga Sebastian - Desinstalacion e instalacion del paño metalico con soldaduras laterales - Sustitucion de 6 barillas metalicas galvaizadas microperforadas - Cambio de flejes y renovacion de paños</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casa Ruan - compra de materiales electricos   </t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -690,7 +692,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -742,6 +744,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1088,9 +1096,8 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="223">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1147,7 +1154,6 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
@@ -1247,12 +1253,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1285,10 +1285,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1398,6 +1394,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1422,9 +1424,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1461,10 +1460,38 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="12" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="10" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1544,9 +1571,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1584,9 +1611,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1619,9 +1646,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1654,9 +1698,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1830,2030 +1891,2010 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N139"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N140"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="34.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="90"/>
-      <c r="B1" s="162" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="88"/>
+      <c r="B1" s="156" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="163"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="106" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="107"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="106" t="s">
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="157"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="105"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="107"/>
-    </row>
-    <row r="4" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="106" t="s">
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="105"/>
+    </row>
+    <row r="4" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="107"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="105"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="106" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5" s="106" t="s">
-        <v>132</v>
-      </c>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="107"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="B5" s="104" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="104" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="105"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="106"/>
-      <c r="C6" s="106"/>
-      <c r="D6" s="106"/>
-      <c r="E6" s="106"/>
-      <c r="F6" s="107"/>
-    </row>
-    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="110" t="s">
+      <c r="B6" s="104"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="105"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="108" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="111"/>
-      <c r="C7" s="111"/>
-      <c r="D7" s="111"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="109"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="78"/>
-      <c r="B8" s="78"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="78"/>
-    </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="78"/>
-      <c r="B9" s="78"/>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-    </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="78"/>
-      <c r="B10" s="78"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="78"/>
-    </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="78"/>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-    </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="78"/>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="78"/>
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="78"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="78"/>
-      <c r="B14" s="166" t="s">
+      <c r="B7" s="109"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="76"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+    </row>
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="76"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+    </row>
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="76"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+    </row>
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="76"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+    </row>
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="76"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="76"/>
+      <c r="B13" s="76"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="76"/>
+      <c r="B14" s="160" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="167"/>
-      <c r="D14" s="168"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="78"/>
-      <c r="B15" s="169"/>
-      <c r="C15" s="170"/>
-      <c r="D15" s="171"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="78"/>
-      <c r="B16" s="169"/>
-      <c r="C16" s="170"/>
-      <c r="D16" s="171"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="78"/>
-      <c r="B17" s="172"/>
-      <c r="C17" s="173"/>
-      <c r="D17" s="174"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="78"/>
-      <c r="B18" s="78"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="112"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="78"/>
-    </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="78"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
-    </row>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="113" t="s">
+      <c r="C14" s="161"/>
+      <c r="D14" s="162"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="76"/>
+      <c r="B15" s="163"/>
+      <c r="C15" s="164"/>
+      <c r="D15" s="165"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="76"/>
+      <c r="B16" s="163"/>
+      <c r="C16" s="164"/>
+      <c r="D16" s="165"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="76"/>
+      <c r="B17" s="166"/>
+      <c r="C17" s="167"/>
+      <c r="D17" s="168"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="76"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="76"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="110"/>
+      <c r="B19" s="76"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="76"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="76"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="111" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="114"/>
-      <c r="C21" s="115"/>
-      <c r="D21" s="116"/>
-      <c r="E21" s="83" t="s">
+      <c r="B21" s="112"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="F21" s="84" t="s">
+      <c r="F21" s="82" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="117" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="115" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="79" t="s">
-        <v>134</v>
-      </c>
-      <c r="C22" s="79"/>
-      <c r="D22" s="150"/>
-      <c r="E22" s="82"/>
-      <c r="F22" s="82"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="117" t="s">
+      <c r="B22" s="77" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="77"/>
+      <c r="D22" s="146"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="80"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="115" t="s">
         <v>96</v>
       </c>
-      <c r="B23" s="79"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="102">
-        <v>2640801.16</v>
-      </c>
-      <c r="E23" s="49">
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="213">
+        <v>1721576.91</v>
+      </c>
+      <c r="E23" s="48">
         <f>D23*91.91%</f>
-        <v>2427160.3461559997</v>
-      </c>
-      <c r="F23" s="49">
+        <v>1582301.3379809998</v>
+      </c>
+      <c r="F23" s="48">
         <f>D23*8.09%</f>
-        <v>213640.81384400002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="117" t="s">
+        <v>139275.57201899998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="79"/>
-      <c r="C24" s="79"/>
-      <c r="D24" s="102">
-        <v>-574674.24</v>
-      </c>
-      <c r="E24" s="49">
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="213">
+        <v>-374442.91</v>
+      </c>
+      <c r="E24" s="48">
         <f t="shared" ref="E24:E26" si="0">D24*91.91%</f>
-        <v>-528183.09398399992</v>
-      </c>
-      <c r="F24" s="49">
+        <v>-344150.47858099994</v>
+      </c>
+      <c r="F24" s="48">
         <f t="shared" ref="F24:F26" si="1">D24*8.09%</f>
-        <v>-46491.146015999999</v>
-      </c>
-      <c r="G24" s="34"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="117" t="s">
+        <v>-30292.431418999997</v>
+      </c>
+      <c r="G24" s="33"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="115" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="79"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="102">
-        <v>0.08</v>
-      </c>
-      <c r="E25" s="49">
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="100">
+        <v>0</v>
+      </c>
+      <c r="E25" s="48">
         <f t="shared" si="0"/>
-        <v>7.3527999999999996E-2</v>
-      </c>
-      <c r="F25" s="49">
+        <v>0</v>
+      </c>
+      <c r="F25" s="48">
         <f t="shared" si="1"/>
-        <v>6.4720000000000003E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="117"/>
-      <c r="B26" s="79"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="102"/>
-      <c r="E26" s="49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="115"/>
+      <c r="B26" s="77"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="100"/>
+      <c r="E26" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F26" s="49">
+      <c r="F26" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="118" t="s">
+    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="118"/>
-      <c r="C27" s="118"/>
-      <c r="D27" s="33">
+      <c r="B27" s="116"/>
+      <c r="C27" s="116"/>
+      <c r="D27" s="32">
         <f>SUM(D23:D26)</f>
-        <v>2066127.0000000002</v>
-      </c>
-      <c r="E27" s="33">
+        <v>1347134</v>
+      </c>
+      <c r="E27" s="32">
         <f>SUM(E23:E26)</f>
-        <v>1898977.3256999997</v>
-      </c>
-      <c r="F27" s="33">
+        <v>1238150.8594</v>
+      </c>
+      <c r="F27" s="32">
         <f>SUM(F23:F26)</f>
-        <v>167149.67430000004</v>
-      </c>
-      <c r="G27" s="34">
+        <v>108983.14059999998</v>
+      </c>
+      <c r="G27" s="33">
         <f>E27+F27</f>
-        <v>2066126.9999999998</v>
-      </c>
-      <c r="H27" s="61" t="str">
+        <v>1347134</v>
+      </c>
+      <c r="H27" s="59" t="str">
         <f>IF(D27=G27, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="119" t="s">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="117" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="79"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="103">
-        <v>0</v>
-      </c>
-      <c r="E28" s="49">
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="101">
+        <v>0</v>
+      </c>
+      <c r="E28" s="48">
         <f>D28*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F28" s="49">
+      <c r="F28" s="48">
         <f>D28*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H28" s="61"/>
-    </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="119"/>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="102">
-        <v>0</v>
-      </c>
-      <c r="E29" s="49">
+      <c r="H28" s="59"/>
+    </row>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="117"/>
+      <c r="B29" s="77"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="100">
+        <v>0</v>
+      </c>
+      <c r="E29" s="48">
         <f>D29*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F29" s="49">
+      <c r="F29" s="48">
         <f>D29*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H29" s="61"/>
-    </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="119"/>
-      <c r="B30" s="79"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="102"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="H30" s="61"/>
-    </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="119"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="102"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="H31" s="61"/>
-    </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="118" t="s">
+      <c r="H29" s="59"/>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="117"/>
+      <c r="B30" s="77"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="100"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="H30" s="59"/>
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="117"/>
+      <c r="B31" s="77"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="100"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="H31" s="59"/>
+    </row>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="116" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="118"/>
-      <c r="C32" s="118"/>
-      <c r="D32" s="33">
+      <c r="B32" s="116"/>
+      <c r="C32" s="116"/>
+      <c r="D32" s="32">
         <f>SUM(D28:D30)</f>
         <v>0</v>
       </c>
-      <c r="E32" s="33">
+      <c r="E32" s="32">
         <f t="shared" ref="E32:F32" si="2">SUM(E28:E30)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="33">
+      <c r="F32" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="33">
         <f>E32+F32</f>
         <v>0</v>
       </c>
-      <c r="H32" s="61" t="str">
+      <c r="H32" s="59" t="str">
         <f>IF(D32=G32, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="119"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="103"/>
-      <c r="E33" s="49">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="117"/>
+      <c r="B33" s="77"/>
+      <c r="C33" s="77"/>
+      <c r="D33" s="101"/>
+      <c r="E33" s="48">
         <f>D33*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F33" s="49">
+      <c r="F33" s="48">
         <f>D33*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H33" s="61"/>
-    </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="79"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="102"/>
-      <c r="E34" s="49">
+      <c r="H33" s="59"/>
+    </row>
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="77"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="48">
         <f t="shared" ref="E34:E35" si="3">D34*91.91%</f>
         <v>0</v>
       </c>
-      <c r="F34" s="49">
+      <c r="F34" s="48">
         <f t="shared" ref="F34:F35" si="4">D34*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H34" s="61"/>
-    </row>
-    <row r="35" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="119"/>
-      <c r="B35" s="79"/>
-      <c r="C35" s="79"/>
-      <c r="D35" s="102"/>
-      <c r="E35" s="49">
+      <c r="H34" s="59"/>
+    </row>
+    <row r="35" spans="1:8" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="117"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="100"/>
+      <c r="E35" s="48">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F35" s="49">
+      <c r="F35" s="48">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H35" s="61"/>
-    </row>
-    <row r="36" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="118" t="s">
+      <c r="H35" s="59"/>
+    </row>
+    <row r="36" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="116" t="s">
         <v>97</v>
       </c>
-      <c r="B36" s="118"/>
-      <c r="C36" s="118"/>
-      <c r="D36" s="33">
+      <c r="B36" s="116"/>
+      <c r="C36" s="116"/>
+      <c r="D36" s="32">
         <f>SUM(D29:D35)</f>
         <v>0</v>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="32">
         <f t="shared" ref="E36" si="5">SUM(E29:E35)</f>
         <v>0</v>
       </c>
-      <c r="F36" s="41">
+      <c r="F36" s="40">
         <f>E36*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H36" s="61"/>
-    </row>
-    <row r="37" spans="1:8" ht="0.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="120"/>
-      <c r="B37" s="101"/>
-      <c r="C37" s="101"/>
-      <c r="D37" s="102"/>
-      <c r="E37" s="42"/>
-      <c r="F37" s="42"/>
-      <c r="H37" s="61"/>
-    </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="120"/>
-      <c r="B38" s="101"/>
-      <c r="C38" s="101"/>
-      <c r="D38" s="102"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42"/>
-      <c r="H38" s="61"/>
-    </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="101"/>
-      <c r="B39" s="101"/>
-      <c r="C39" s="121"/>
-      <c r="D39" s="102"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="H39" s="61"/>
-    </row>
-    <row r="40" spans="1:8" ht="1.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="118" t="s">
+      <c r="H36" s="59"/>
+    </row>
+    <row r="37" spans="1:8" ht="0.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="118"/>
+      <c r="B37" s="99"/>
+      <c r="C37" s="99"/>
+      <c r="D37" s="100"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="H37" s="59"/>
+    </row>
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="118"/>
+      <c r="B38" s="99"/>
+      <c r="C38" s="99"/>
+      <c r="D38" s="100"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="H38" s="59"/>
+    </row>
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="99"/>
+      <c r="B39" s="99"/>
+      <c r="C39" s="119"/>
+      <c r="D39" s="100"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
+      <c r="H39" s="59"/>
+    </row>
+    <row r="40" spans="1:8" ht="1.1499999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="116" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="118"/>
-      <c r="C40" s="118"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="36">
+      <c r="B40" s="116"/>
+      <c r="C40" s="116"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="35">
         <f>SUM(D37:D39)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="35">
+      <c r="F40" s="34">
         <f>(D37)*8.09%</f>
         <v>0</v>
       </c>
-      <c r="H40" s="61"/>
-    </row>
-    <row r="41" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="79" t="s">
-        <v>142</v>
-      </c>
-      <c r="B41" s="79"/>
-      <c r="C41" s="101"/>
-      <c r="D41" s="215">
+      <c r="H40" s="59"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="77" t="s">
+        <v>141</v>
+      </c>
+      <c r="B41" s="77"/>
+      <c r="C41" s="99"/>
+      <c r="D41" s="209">
         <v>68000</v>
       </c>
-      <c r="E41" s="49">
+      <c r="E41" s="48">
         <f>D41</f>
         <v>68000</v>
       </c>
-      <c r="F41" s="49"/>
-      <c r="H41" s="61"/>
-    </row>
-    <row r="42" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="118" t="s">
+      <c r="F41" s="48"/>
+      <c r="H41" s="59"/>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="77" t="s">
+        <v>142</v>
+      </c>
+      <c r="B42" s="77"/>
+      <c r="C42" s="99"/>
+      <c r="D42" s="213">
+        <v>5837.2</v>
+      </c>
+      <c r="E42" s="48">
+        <f>D42</f>
+        <v>5837.2</v>
+      </c>
+      <c r="F42" s="48"/>
+      <c r="H42" s="59"/>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="116" t="s">
         <v>97</v>
       </c>
-      <c r="B42" s="118"/>
-      <c r="C42" s="118"/>
-      <c r="D42" s="33">
-        <f>SUM(D41:D41)</f>
-        <v>68000</v>
-      </c>
-      <c r="E42" s="65">
-        <f>SUM(E41:E41)</f>
-        <v>68000</v>
-      </c>
-      <c r="F42" s="71">
+      <c r="B43" s="116"/>
+      <c r="C43" s="116"/>
+      <c r="D43" s="32">
+        <f>SUM(D41:D42)</f>
+        <v>73837.2</v>
+      </c>
+      <c r="E43" s="63">
+        <f>SUM(E41:E42)</f>
+        <v>73837.2</v>
+      </c>
+      <c r="F43" s="69">
         <f>SUM(F41:F41)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="34">
-        <f>E42+F42</f>
-        <v>68000</v>
-      </c>
-      <c r="H42" s="61"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="119" t="s">
+      <c r="G43" s="33">
+        <f>E43+F43</f>
+        <v>73837.2</v>
+      </c>
+      <c r="H43" s="59"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="79"/>
-      <c r="C43" s="79"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="26"/>
-      <c r="H43" s="61"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="119" t="s">
+      <c r="B44" s="77"/>
+      <c r="C44" s="77"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="25"/>
+      <c r="H44" s="59"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="117" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="79"/>
-      <c r="C44" s="101"/>
-      <c r="D44" s="37">
+      <c r="B45" s="77"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="209">
         <v>6642</v>
       </c>
-      <c r="E44" s="49">
-        <f>D44*91.91%</f>
+      <c r="E45" s="48">
+        <f>D45*91.91%</f>
         <v>6104.6621999999998</v>
       </c>
-      <c r="F44" s="49">
-        <f>D44*8.09%</f>
+      <c r="F45" s="48">
+        <f>D45*8.09%</f>
         <v>537.33780000000002</v>
       </c>
-      <c r="H44" s="61"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="119" t="s">
+      <c r="H45" s="59"/>
+    </row>
+    <row r="46" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="210" t="s">
+        <v>140</v>
+      </c>
+      <c r="B46" s="211"/>
+      <c r="C46" s="212"/>
+      <c r="D46" s="209">
+        <f>1774.18+778867.29</f>
+        <v>780641.47000000009</v>
+      </c>
+      <c r="E46" s="48">
+        <f>D46*91.91%</f>
+        <v>717487.57507700007</v>
+      </c>
+      <c r="F46" s="48">
+        <f>D46*8.09%</f>
+        <v>63153.894923000007</v>
+      </c>
+      <c r="H46" s="59"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="117" t="s">
         <v>5</v>
       </c>
-      <c r="B45" s="79"/>
-      <c r="C45" s="79"/>
-      <c r="D45" s="215">
+      <c r="B47" s="77"/>
+      <c r="C47" s="77"/>
+      <c r="D47" s="209">
         <f>13204.01+244288.08+118836.05</f>
         <v>376328.14</v>
       </c>
-      <c r="E45" s="49">
-        <f>D45*91.91%</f>
+      <c r="E47" s="48">
+        <f>D47*91.91%</f>
         <v>345883.19347399997</v>
       </c>
-      <c r="F45" s="49">
-        <f>D45*8.09%</f>
+      <c r="F47" s="48">
+        <f>D47*8.09%</f>
         <v>30444.946526</v>
       </c>
-      <c r="H45" s="61"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="119" t="s">
+      <c r="H47" s="59"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="117" t="s">
         <v>103</v>
       </c>
-      <c r="B46" s="101"/>
-      <c r="C46" s="79"/>
-      <c r="D46" s="215">
+      <c r="B48" s="99"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="209">
         <v>1170944.31</v>
       </c>
-      <c r="E46" s="49">
-        <f>D46*91.91%</f>
+      <c r="E48" s="48">
+        <f>D48*91.91%</f>
         <v>1076214.9153209999</v>
       </c>
-      <c r="F46" s="49">
-        <f>D46*8.09%</f>
+      <c r="F48" s="48">
+        <f>D48*8.09%</f>
         <v>94729.394679000005</v>
       </c>
-      <c r="H46" s="61"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="118" t="s">
+      <c r="H48" s="59"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="B47" s="122"/>
-      <c r="C47" s="122"/>
-      <c r="D47" s="33">
-        <f>SUM(D44:D46)</f>
-        <v>1553914.4500000002</v>
-      </c>
-      <c r="E47" s="33">
-        <f t="shared" ref="E47:F47" si="6">SUM(E44:E46)</f>
-        <v>1428202.7709949999</v>
-      </c>
-      <c r="F47" s="33">
+      <c r="B49" s="120"/>
+      <c r="C49" s="120"/>
+      <c r="D49" s="32">
+        <f>SUM(D45:D48)</f>
+        <v>2334555.92</v>
+      </c>
+      <c r="E49" s="32">
+        <f t="shared" ref="E49:F49" si="6">SUM(E45:E48)</f>
+        <v>2145690.346072</v>
+      </c>
+      <c r="F49" s="32">
         <f t="shared" si="6"/>
-        <v>125711.67900500001</v>
-      </c>
-      <c r="G47" s="34">
-        <f>E47+F47</f>
-        <v>1553914.45</v>
-      </c>
-      <c r="H47" s="61" t="str">
-        <f>IF(D47=G47, "", "Error")</f>
+        <v>188865.573928</v>
+      </c>
+      <c r="G49" s="33">
+        <f>E49+F49</f>
+        <v>2334555.92</v>
+      </c>
+      <c r="H49" s="59" t="str">
+        <f>IF(D49=G49, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="79" t="s">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="B48" s="79"/>
-      <c r="C48" s="79"/>
-      <c r="D48" s="104"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="3"/>
-      <c r="H48" s="61"/>
-    </row>
-    <row r="49" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="123" t="s">
+      <c r="B50" s="77"/>
+      <c r="C50" s="77"/>
+      <c r="D50" s="102"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="2"/>
+      <c r="H50" s="59"/>
+    </row>
+    <row r="51" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="121" t="s">
         <v>105</v>
       </c>
-      <c r="B49" s="79"/>
-      <c r="C49" s="79"/>
-      <c r="D49" s="215">
+      <c r="B51" s="77"/>
+      <c r="C51" s="77"/>
+      <c r="D51" s="209">
         <v>520800</v>
       </c>
-      <c r="E49" s="60">
-        <f>D49</f>
+      <c r="E51" s="58">
+        <f>D51</f>
         <v>520800</v>
       </c>
-      <c r="F49" s="3"/>
-      <c r="G49" s="34">
-        <f>D49</f>
+      <c r="F51" s="2"/>
+      <c r="G51" s="33">
+        <f>D51</f>
         <v>520800</v>
       </c>
-      <c r="H49" s="67">
-        <f>E49+F49</f>
+      <c r="H51" s="65">
+        <f>E51+F51</f>
         <v>520800</v>
       </c>
-      <c r="I49" s="76">
-        <f>H49-D49</f>
-        <v>0</v>
-      </c>
-      <c r="J49" s="76"/>
-    </row>
-    <row r="50" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="151" t="s">
-        <v>146</v>
-      </c>
-      <c r="B50" s="79"/>
-      <c r="C50" s="79"/>
-      <c r="D50" s="215">
+      <c r="I51" s="74">
+        <f>H51-D51</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="74"/>
+    </row>
+    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="147" t="s">
+        <v>136</v>
+      </c>
+      <c r="B52" s="77"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="209">
         <v>780000</v>
       </c>
-      <c r="E50" s="60"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="34"/>
-      <c r="H50" s="67"/>
-      <c r="I50" s="76"/>
-      <c r="J50" s="76"/>
-    </row>
-    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="117" t="s">
+      <c r="E52" s="58">
+        <f>D52</f>
+        <v>780000</v>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="33"/>
+      <c r="H52" s="65"/>
+      <c r="I52" s="74"/>
+      <c r="J52" s="74"/>
+    </row>
+    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="B51" s="126"/>
-      <c r="C51" s="79"/>
-      <c r="D51" s="215">
+      <c r="B53" s="124"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="209">
         <v>266112.3</v>
       </c>
-      <c r="E51" s="60">
-        <f t="shared" ref="E51:E56" si="7">D51*91.91%</f>
+      <c r="E53" s="58">
+        <f t="shared" ref="E53:E58" si="7">D53*91.91%</f>
         <v>244583.81492999996</v>
       </c>
-      <c r="F51" s="49">
-        <f t="shared" ref="F51:F56" si="8">D51*8.09%</f>
+      <c r="F53" s="48">
+        <f t="shared" ref="F53:F58" si="8">D53*8.09%</f>
         <v>21528.485069999999</v>
       </c>
-      <c r="G51" s="34">
-        <f t="shared" ref="G51:G53" si="9">D51</f>
+      <c r="G53" s="33">
+        <f t="shared" ref="G53:G55" si="9">D53</f>
         <v>266112.3</v>
       </c>
-      <c r="H51" s="67">
-        <f t="shared" ref="H51:H53" si="10">E51+F51</f>
+      <c r="H53" s="65">
+        <f t="shared" ref="H53:H55" si="10">E53+F53</f>
         <v>266112.3</v>
       </c>
-      <c r="I51" s="76"/>
-      <c r="J51" s="76"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="79" t="s">
-        <v>124</v>
-      </c>
-      <c r="B52" s="79"/>
-      <c r="C52" s="79"/>
-      <c r="D52" s="37">
+      <c r="I53" s="74"/>
+      <c r="J53" s="74"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" s="77"/>
+      <c r="C54" s="77"/>
+      <c r="D54" s="36">
         <v>45000</v>
       </c>
-      <c r="E52" s="60">
-        <f>D52</f>
+      <c r="E54" s="58">
+        <f>D54</f>
         <v>45000</v>
       </c>
-      <c r="F52" s="49">
-        <v>0</v>
-      </c>
-      <c r="G52" s="34">
+      <c r="F54" s="48">
+        <v>0</v>
+      </c>
+      <c r="G54" s="33">
         <f t="shared" si="9"/>
         <v>45000</v>
       </c>
-      <c r="H52" s="67">
+      <c r="H54" s="65">
         <f t="shared" si="10"/>
         <v>45000</v>
       </c>
-      <c r="I52" s="76"/>
-      <c r="J52" s="76"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="119" t="s">
-        <v>144</v>
-      </c>
-      <c r="B53" s="79"/>
-      <c r="C53" s="79"/>
-      <c r="D53" s="215">
+      <c r="I54" s="74"/>
+      <c r="J54" s="74"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="B55" s="77"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="209">
         <v>192118.26</v>
       </c>
-      <c r="E53" s="60">
-        <f t="shared" ref="E53" si="11">D53*91.91%</f>
+      <c r="E55" s="58">
+        <f t="shared" ref="E55" si="11">D55*91.91%</f>
         <v>176575.892766</v>
       </c>
-      <c r="F53" s="49">
-        <f t="shared" ref="F53" si="12">D53*8.09%</f>
+      <c r="F55" s="48">
+        <f t="shared" ref="F55" si="12">D55*8.09%</f>
         <v>15542.367234000001</v>
       </c>
-      <c r="G53" s="34">
+      <c r="G55" s="33">
         <f t="shared" si="9"/>
         <v>192118.26</v>
       </c>
-      <c r="H53" s="67">
+      <c r="H55" s="65">
         <f t="shared" si="10"/>
         <v>192118.26</v>
       </c>
-      <c r="I53" s="76"/>
-      <c r="J53" s="76"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="119" t="s">
+      <c r="I55" s="74"/>
+      <c r="J55" s="74"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="B54" s="79" t="s">
+      <c r="B56" s="77" t="s">
         <v>109</v>
       </c>
-      <c r="C54" s="79"/>
-      <c r="D54" s="37">
+      <c r="C56" s="77"/>
+      <c r="D56" s="209">
         <v>173191</v>
       </c>
-      <c r="E54" s="60">
-        <f>D54*91.91%</f>
+      <c r="E56" s="58">
+        <f>D56*91.91%</f>
         <v>159179.84809999997</v>
       </c>
-      <c r="F54" s="49">
+      <c r="F56" s="48">
         <f t="shared" si="8"/>
         <v>14011.151900000001</v>
       </c>
-      <c r="G54" s="34">
-        <f t="shared" ref="G54:G66" si="13">D54</f>
+      <c r="G56" s="33">
+        <f t="shared" ref="G56:G67" si="13">D56</f>
         <v>173191</v>
       </c>
-      <c r="H54" s="67">
-        <f>E54+F54</f>
+      <c r="H56" s="65">
+        <f>E56+F56</f>
         <v>173190.99999999997</v>
       </c>
-      <c r="I54" s="76">
-        <f t="shared" ref="I54:I66" si="14">H54-D54</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="76">
-        <f t="shared" ref="J54:J66" si="15">G54-D54</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="119" t="s">
+      <c r="I56" s="74">
+        <f t="shared" ref="I56:I67" si="14">H56-D56</f>
+        <v>0</v>
+      </c>
+      <c r="J56" s="74">
+        <f t="shared" ref="J56:J67" si="15">G56-D56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="B55" s="101"/>
-      <c r="C55" s="79"/>
-      <c r="D55" s="37">
+      <c r="B57" s="99"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="209">
         <v>515749.85</v>
       </c>
-      <c r="E55" s="60">
+      <c r="E57" s="58">
         <f t="shared" si="7"/>
         <v>474025.68713499996</v>
       </c>
-      <c r="F55" s="49">
+      <c r="F57" s="48">
         <f t="shared" si="8"/>
         <v>41724.162864999998</v>
       </c>
-      <c r="G55" s="34">
+      <c r="G57" s="33">
         <f t="shared" si="13"/>
         <v>515749.85</v>
       </c>
-      <c r="H55" s="67">
-        <f t="shared" ref="H55:H66" si="16">E55+F55</f>
+      <c r="H57" s="65">
+        <f t="shared" ref="H57:H67" si="16">E57+F57</f>
         <v>515749.85</v>
       </c>
-      <c r="I55" s="76">
+      <c r="I57" s="74">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J55" s="76">
+      <c r="J57" s="74">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="120" t="s">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="B56" s="101"/>
-      <c r="C56" s="101"/>
-      <c r="D56" s="215">
+      <c r="B58" s="99"/>
+      <c r="C58" s="99"/>
+      <c r="D58" s="209">
         <v>1516824.98</v>
       </c>
-      <c r="E56" s="60">
+      <c r="E58" s="58">
         <f t="shared" si="7"/>
         <v>1394113.8391179999</v>
       </c>
-      <c r="F56" s="49">
+      <c r="F58" s="48">
         <f t="shared" si="8"/>
         <v>122711.14088199999</v>
       </c>
-      <c r="G56" s="34">
+      <c r="G58" s="33">
         <f t="shared" si="13"/>
         <v>1516824.98</v>
       </c>
-      <c r="H56" s="67">
+      <c r="H58" s="65">
         <f t="shared" si="16"/>
         <v>1516824.98</v>
       </c>
-      <c r="I56" s="76">
+      <c r="I58" s="74">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J56" s="76">
+      <c r="J58" s="74">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="120" t="s">
-        <v>10</v>
-      </c>
-      <c r="B57" s="140"/>
-      <c r="C57" s="152"/>
-      <c r="D57" s="37">
-        <v>1237365.1000000001</v>
-      </c>
-      <c r="E57" s="60">
-        <f>D57</f>
-        <v>1237365.1000000001</v>
-      </c>
-      <c r="F57" s="49">
-        <v>0</v>
-      </c>
-      <c r="G57" s="34">
-        <f t="shared" si="13"/>
-        <v>1237365.1000000001</v>
-      </c>
-      <c r="H57" s="67">
-        <f t="shared" si="16"/>
-        <v>1237365.1000000001</v>
-      </c>
-      <c r="I57" s="76"/>
-      <c r="J57" s="76"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="127" t="s">
-        <v>135</v>
-      </c>
-      <c r="B58" s="141"/>
-      <c r="C58" s="142"/>
-      <c r="D58" s="37">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="125" t="s">
+        <v>128</v>
+      </c>
+      <c r="B59" s="137"/>
+      <c r="C59" s="138"/>
+      <c r="D59" s="36">
         <v>63300</v>
       </c>
-      <c r="E58" s="60">
-        <f t="shared" ref="E58:E59" si="17">D58</f>
+      <c r="E59" s="58">
+        <f t="shared" ref="E59:E60" si="17">D59</f>
         <v>63300</v>
       </c>
-      <c r="F58" s="49"/>
-      <c r="G58" s="34">
+      <c r="F59" s="48"/>
+      <c r="G59" s="33">
         <f t="shared" si="13"/>
         <v>63300</v>
       </c>
-      <c r="H58" s="67">
+      <c r="H59" s="65">
         <f t="shared" si="16"/>
         <v>63300</v>
       </c>
-      <c r="I58" s="76"/>
-      <c r="J58" s="76">
+      <c r="I59" s="74"/>
+      <c r="J59" s="74">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="151" t="s">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="147" t="s">
         <v>120</v>
       </c>
-      <c r="B59" s="141"/>
-      <c r="C59" s="142"/>
-      <c r="D59" s="37">
+      <c r="B60" s="137"/>
+      <c r="C60" s="138"/>
+      <c r="D60" s="36">
         <v>237000</v>
       </c>
-      <c r="E59" s="60">
+      <c r="E60" s="58">
         <f t="shared" si="17"/>
         <v>237000</v>
       </c>
-      <c r="F59" s="49"/>
-      <c r="G59" s="34">
+      <c r="F60" s="48"/>
+      <c r="G60" s="33">
         <f t="shared" si="13"/>
         <v>237000</v>
       </c>
-      <c r="H59" s="67">
+      <c r="H60" s="65">
         <f t="shared" si="16"/>
         <v>237000</v>
       </c>
-      <c r="I59" s="76"/>
-      <c r="J59" s="76"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="153" t="s">
-        <v>125</v>
-      </c>
-      <c r="B60" s="128"/>
-      <c r="C60" s="129"/>
-      <c r="D60" s="37">
-        <v>85000</v>
-      </c>
-      <c r="E60" s="60">
-        <f t="shared" ref="E60" si="18">D60*91.91%</f>
-        <v>78123.5</v>
-      </c>
-      <c r="F60" s="49">
-        <f t="shared" ref="F60" si="19">D60*8.09%</f>
-        <v>6876.5</v>
-      </c>
-      <c r="G60" s="34">
-        <f t="shared" si="13"/>
-        <v>85000</v>
-      </c>
-      <c r="H60" s="67">
-        <f t="shared" si="16"/>
-        <v>85000</v>
-      </c>
-      <c r="I60" s="76">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="J60" s="76">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="159" t="s">
-        <v>140</v>
-      </c>
-      <c r="B61" s="160"/>
-      <c r="C61" s="161"/>
-      <c r="D61" s="215">
+      <c r="I60" s="74"/>
+      <c r="J60" s="74"/>
+    </row>
+    <row r="61" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="153" t="s">
+        <v>132</v>
+      </c>
+      <c r="B61" s="154"/>
+      <c r="C61" s="155"/>
+      <c r="D61" s="209">
         <v>59169</v>
       </c>
-      <c r="E61" s="60">
+      <c r="E61" s="58">
         <f>D61</f>
         <v>59169</v>
       </c>
-      <c r="F61" s="49"/>
-      <c r="G61" s="34">
+      <c r="F61" s="48"/>
+      <c r="G61" s="33">
         <f t="shared" si="13"/>
         <v>59169</v>
       </c>
-      <c r="H61" s="67"/>
-      <c r="I61" s="76"/>
-      <c r="J61" s="76"/>
-    </row>
-    <row r="62" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="187" t="s">
-        <v>141</v>
-      </c>
-      <c r="B62" s="188"/>
-      <c r="C62" s="189"/>
-      <c r="D62" s="215">
-        <v>320000</v>
-      </c>
-      <c r="E62" s="60">
-        <f t="shared" ref="E62:E64" si="20">D62</f>
-        <v>320000</v>
-      </c>
-      <c r="F62" s="49"/>
-      <c r="G62" s="34">
+      <c r="H61" s="65"/>
+      <c r="I61" s="74"/>
+      <c r="J61" s="74"/>
+    </row>
+    <row r="62" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="181" t="s">
+        <v>139</v>
+      </c>
+      <c r="B62" s="182"/>
+      <c r="C62" s="183"/>
+      <c r="D62" s="209">
+        <v>1150000</v>
+      </c>
+      <c r="E62" s="58">
+        <f>D62</f>
+        <v>1150000</v>
+      </c>
+      <c r="F62" s="48"/>
+      <c r="G62" s="33">
         <f t="shared" si="13"/>
-        <v>320000</v>
-      </c>
-      <c r="H62" s="67">
+        <v>1150000</v>
+      </c>
+      <c r="H62" s="65"/>
+      <c r="I62" s="74"/>
+      <c r="J62" s="74"/>
+    </row>
+    <row r="63" spans="1:10" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="181" t="s">
+        <v>143</v>
+      </c>
+      <c r="B63" s="182"/>
+      <c r="C63" s="183"/>
+      <c r="D63" s="209">
+        <v>650000</v>
+      </c>
+      <c r="E63" s="58">
+        <f t="shared" ref="E63:E64" si="18">D63</f>
+        <v>650000</v>
+      </c>
+      <c r="F63" s="48"/>
+      <c r="G63" s="33">
+        <f t="shared" si="13"/>
+        <v>650000</v>
+      </c>
+      <c r="H63" s="65">
         <f t="shared" si="16"/>
-        <v>320000</v>
-      </c>
-      <c r="I62" s="76"/>
-      <c r="J62" s="76">
+        <v>650000</v>
+      </c>
+      <c r="I63" s="74"/>
+      <c r="J63" s="74">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="159" t="s">
-        <v>145</v>
-      </c>
-      <c r="B63" s="160"/>
-      <c r="C63" s="161"/>
-      <c r="D63" s="215">
+    <row r="64" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="153" t="s">
+        <v>135</v>
+      </c>
+      <c r="B64" s="154"/>
+      <c r="C64" s="155"/>
+      <c r="D64" s="209">
         <v>110000</v>
       </c>
-      <c r="E63" s="60">
-        <f t="shared" si="20"/>
+      <c r="E64" s="58">
+        <f t="shared" si="18"/>
         <v>110000</v>
       </c>
-      <c r="F63" s="49"/>
-      <c r="G63" s="34">
+      <c r="F64" s="48"/>
+      <c r="G64" s="33">
         <f t="shared" si="13"/>
         <v>110000</v>
       </c>
-      <c r="H63" s="67">
+      <c r="H64" s="65">
         <f t="shared" si="16"/>
         <v>110000</v>
       </c>
-      <c r="I63" s="76"/>
-      <c r="J63" s="76">
+      <c r="I64" s="74"/>
+      <c r="J64" s="74">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="159" t="s">
-        <v>123</v>
-      </c>
-      <c r="B64" s="160"/>
-      <c r="C64" s="161"/>
-      <c r="D64" s="37">
-        <v>41000</v>
-      </c>
-      <c r="E64" s="60">
-        <f t="shared" si="20"/>
-        <v>41000</v>
-      </c>
-      <c r="F64" s="49"/>
-      <c r="G64" s="34">
-        <f t="shared" si="13"/>
-        <v>41000</v>
-      </c>
-      <c r="H64" s="67">
-        <f t="shared" si="16"/>
-        <v>41000</v>
-      </c>
-      <c r="I64" s="76"/>
-      <c r="J64" s="76">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="79" t="s">
+    <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="B65" s="124" t="s">
-        <v>136</v>
-      </c>
-      <c r="C65" s="139"/>
-      <c r="D65" s="37">
+      <c r="B65" s="122" t="s">
+        <v>129</v>
+      </c>
+      <c r="C65" s="135"/>
+      <c r="D65" s="36">
         <v>103395</v>
       </c>
-      <c r="E65" s="60">
-        <f t="shared" ref="E65:E66" si="21">D65</f>
+      <c r="E65" s="58">
+        <f t="shared" ref="E65:E67" si="19">D65</f>
         <v>103395</v>
       </c>
-      <c r="F65" s="49"/>
-      <c r="G65" s="34">
+      <c r="F65" s="48"/>
+      <c r="G65" s="33">
         <f t="shared" si="13"/>
         <v>103395</v>
       </c>
-      <c r="H65" s="67">
+      <c r="H65" s="65">
         <f t="shared" si="16"/>
         <v>103395</v>
       </c>
-      <c r="I65" s="76">
+      <c r="I65" s="74">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J65" s="76">
+      <c r="J65" s="74">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="186" t="s">
-        <v>139</v>
-      </c>
-      <c r="B66" s="160"/>
-      <c r="C66" s="161"/>
-      <c r="D66" s="215">
+    <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="220" t="s">
+        <v>144</v>
+      </c>
+      <c r="B66" s="122"/>
+      <c r="C66" s="135"/>
+      <c r="D66" s="209">
+        <v>49600</v>
+      </c>
+      <c r="E66" s="58">
+        <f t="shared" si="19"/>
+        <v>49600</v>
+      </c>
+      <c r="F66" s="48"/>
+      <c r="G66" s="33">
+        <f t="shared" si="13"/>
+        <v>49600</v>
+      </c>
+      <c r="H66" s="65"/>
+      <c r="I66" s="74"/>
+      <c r="J66" s="74"/>
+    </row>
+    <row r="67" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="180" t="s">
+        <v>138</v>
+      </c>
+      <c r="B67" s="154"/>
+      <c r="C67" s="155"/>
+      <c r="D67" s="209">
         <v>938000</v>
       </c>
-      <c r="E66" s="60">
-        <f t="shared" si="21"/>
+      <c r="E67" s="58">
+        <f t="shared" si="19"/>
         <v>938000</v>
       </c>
-      <c r="F66" s="49"/>
-      <c r="G66" s="34">
+      <c r="F67" s="48"/>
+      <c r="G67" s="33">
         <f t="shared" si="13"/>
         <v>938000</v>
       </c>
-      <c r="H66" s="67">
+      <c r="H67" s="65">
         <f t="shared" si="16"/>
         <v>938000</v>
       </c>
-      <c r="I66" s="76">
+      <c r="I67" s="74">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J66" s="76">
+      <c r="J67" s="74">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A67" s="118" t="s">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="116" t="s">
         <v>12</v>
       </c>
-      <c r="B67" s="122"/>
-      <c r="C67" s="122"/>
-      <c r="D67" s="33">
-        <f>SUM(D49:D66)</f>
-        <v>7204025.4900000002</v>
-      </c>
-      <c r="E67" s="33">
-        <f>SUM(E49:E66)</f>
-        <v>6201631.6820490006</v>
-      </c>
-      <c r="F67" s="33">
-        <f>SUM(F49:F66)</f>
-        <v>222393.807951</v>
-      </c>
-      <c r="G67" s="34">
-        <f>E67+F67</f>
-        <v>6424025.4900000002</v>
-      </c>
-      <c r="H67" s="61" t="str">
-        <f>IF(D67=G67, "", "Error")</f>
-        <v>Error</v>
-      </c>
-      <c r="I67" s="76">
-        <f>D67-G67</f>
-        <v>780000</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="79"/>
-      <c r="B68" s="79"/>
-      <c r="C68" s="79"/>
-      <c r="D68" s="104"/>
-      <c r="E68" s="39"/>
-      <c r="F68" s="3"/>
-      <c r="H68" s="61"/>
-    </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="79"/>
-      <c r="B69" s="79"/>
-      <c r="C69" s="79"/>
-      <c r="D69" s="104"/>
+      <c r="B68" s="120"/>
+      <c r="C68" s="120"/>
+      <c r="D68" s="32">
+        <f>SUM(D51:D67)</f>
+        <v>7370260.3900000006</v>
+      </c>
+      <c r="E68" s="32">
+        <f>SUM(E51:E67)</f>
+        <v>7154743.0820490001</v>
+      </c>
+      <c r="F68" s="32">
+        <f>SUM(F51:F67)</f>
+        <v>215517.307951</v>
+      </c>
+      <c r="G68" s="33">
+        <f>E68+F68</f>
+        <v>7370260.3899999997</v>
+      </c>
+      <c r="H68" s="59" t="str">
+        <f>IF(D68=G68, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="I68" s="74">
+        <f>D68-G68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="77"/>
+      <c r="B69" s="77"/>
+      <c r="C69" s="77"/>
+      <c r="D69" s="102"/>
       <c r="E69" s="38"/>
-      <c r="F69" s="3"/>
-      <c r="H69" s="61"/>
-    </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="79"/>
-      <c r="B70" s="79"/>
-      <c r="C70" s="79"/>
-      <c r="D70" s="104"/>
-      <c r="E70" s="38"/>
-      <c r="F70" s="3"/>
-      <c r="H70" s="61"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A71" s="120" t="s">
+      <c r="F69" s="2"/>
+      <c r="H69" s="59"/>
+    </row>
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="77"/>
+      <c r="B70" s="77"/>
+      <c r="C70" s="77"/>
+      <c r="D70" s="102"/>
+      <c r="E70" s="37"/>
+      <c r="F70" s="2"/>
+      <c r="H70" s="59"/>
+    </row>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="77"/>
+      <c r="B71" s="77"/>
+      <c r="C71" s="77"/>
+      <c r="D71" s="102"/>
+      <c r="E71" s="37"/>
+      <c r="F71" s="2"/>
+      <c r="H71" s="59"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="B71" s="101"/>
-      <c r="C71" s="79"/>
-      <c r="D71" s="37">
+      <c r="B72" s="99"/>
+      <c r="C72" s="77"/>
+      <c r="D72" s="36">
         <v>139000</v>
       </c>
-      <c r="E71" s="60">
-        <f>D71*91.91%</f>
+      <c r="E72" s="58">
+        <f>D72*91.91%</f>
         <v>127754.9</v>
       </c>
-      <c r="F71" s="49">
-        <f>D71*8.09%</f>
+      <c r="F72" s="48">
+        <f>D72*8.09%</f>
         <v>11245.1</v>
       </c>
-      <c r="G71" s="66"/>
-      <c r="H71" s="61"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72" s="120" t="s">
+      <c r="G72" s="64"/>
+      <c r="H72" s="59"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="B72" s="140"/>
-      <c r="C72" s="125"/>
-      <c r="D72" s="37">
+      <c r="B73" s="136"/>
+      <c r="C73" s="123"/>
+      <c r="D73" s="36">
         <v>134050</v>
       </c>
-      <c r="E72" s="60">
-        <f>D72*91.91%</f>
+      <c r="E73" s="58">
+        <f>D73*91.91%</f>
         <v>123205.355</v>
       </c>
-      <c r="F72" s="49">
-        <f>D72*8.09%</f>
+      <c r="F73" s="48">
+        <f>D73*8.09%</f>
         <v>10844.645</v>
       </c>
-      <c r="G72" s="66"/>
-      <c r="H72" s="61"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" s="101" t="s">
+      <c r="G73" s="64"/>
+      <c r="H73" s="59"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="99" t="s">
         <v>121</v>
       </c>
-      <c r="B73" s="140"/>
-      <c r="C73" s="125"/>
-      <c r="D73" s="37">
+      <c r="B74" s="136"/>
+      <c r="C74" s="123"/>
+      <c r="D74" s="36">
         <v>112800</v>
       </c>
-      <c r="E73" s="60">
-        <f>D73</f>
+      <c r="E74" s="58">
+        <f>D74</f>
         <v>112800</v>
       </c>
-      <c r="F73" s="49">
-        <v>0</v>
-      </c>
-      <c r="G73" s="66"/>
-      <c r="H73" s="61"/>
-    </row>
-    <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="118" t="s">
+      <c r="F74" s="48">
+        <v>0</v>
+      </c>
+      <c r="G74" s="64"/>
+      <c r="H74" s="59"/>
+    </row>
+    <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="B74" s="118"/>
-      <c r="C74" s="118"/>
-      <c r="D74" s="33">
-        <f>SUM(D71:D73)</f>
+      <c r="B75" s="116"/>
+      <c r="C75" s="116"/>
+      <c r="D75" s="32">
+        <f>SUM(D72:D74)</f>
         <v>385850</v>
       </c>
-      <c r="E74" s="33">
-        <f>SUM(E71:E73)</f>
+      <c r="E75" s="32">
+        <f>SUM(E72:E74)</f>
         <v>363760.255</v>
       </c>
-      <c r="F74" s="33">
-        <f>SUM(F71:F73)</f>
+      <c r="F75" s="32">
+        <f>SUM(F72:F74)</f>
         <v>22089.745000000003</v>
       </c>
-      <c r="G74" s="34">
-        <f>E74+F74</f>
+      <c r="G75" s="33">
+        <f>E75+F75</f>
         <v>385850</v>
       </c>
-      <c r="H74" s="61" t="str">
-        <f>IF(D74=G74, "", "Error")</f>
+      <c r="H75" s="59" t="str">
+        <f>IF(D75=G75, "", "Error")</f>
         <v/>
       </c>
-      <c r="J74" s="34"/>
-    </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="79"/>
-      <c r="B75" s="79"/>
-      <c r="C75" s="79"/>
-      <c r="D75" s="104"/>
-      <c r="E75" s="39"/>
-      <c r="F75" s="3"/>
-      <c r="H75" s="61"/>
-    </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="79"/>
-      <c r="B76" s="79"/>
-      <c r="C76" s="79"/>
-      <c r="D76" s="104"/>
+      <c r="J75" s="33"/>
+    </row>
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="77"/>
+      <c r="B76" s="77"/>
+      <c r="C76" s="77"/>
+      <c r="D76" s="102"/>
       <c r="E76" s="38"/>
-      <c r="F76" s="3"/>
-      <c r="H76" s="61"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="119" t="s">
+      <c r="F76" s="2"/>
+      <c r="H76" s="59"/>
+    </row>
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="77"/>
+      <c r="B77" s="77"/>
+      <c r="C77" s="77"/>
+      <c r="D77" s="102"/>
+      <c r="E77" s="37"/>
+      <c r="F77" s="2"/>
+      <c r="H77" s="59"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="117" t="s">
         <v>13</v>
       </c>
-      <c r="B77" s="79"/>
-      <c r="C77" s="79"/>
-      <c r="D77" s="104"/>
-      <c r="E77" s="38"/>
-      <c r="F77" s="3"/>
-      <c r="H77" s="61"/>
-    </row>
-    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="119" t="s">
+      <c r="B78" s="77"/>
+      <c r="C78" s="77"/>
+      <c r="D78" s="102"/>
+      <c r="E78" s="37"/>
+      <c r="F78" s="2"/>
+      <c r="H78" s="59"/>
+    </row>
+    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="117" t="s">
         <v>14</v>
       </c>
-      <c r="B78" s="79" t="s">
-        <v>137</v>
-      </c>
-      <c r="C78" s="79"/>
-      <c r="D78" s="215">
+      <c r="B79" s="77" t="s">
+        <v>130</v>
+      </c>
+      <c r="C79" s="77"/>
+      <c r="D79" s="209">
         <v>285700</v>
       </c>
-      <c r="E78" s="60">
-        <f>D78*91.91%</f>
+      <c r="E79" s="58">
+        <f>D79*91.91%</f>
         <v>262586.87</v>
       </c>
-      <c r="F78" s="49">
-        <f>D78*8.09%</f>
+      <c r="F79" s="48">
+        <f>D79*8.09%</f>
         <v>23113.13</v>
       </c>
-      <c r="G78" t="s">
+      <c r="G79" t="s">
         <v>112</v>
       </c>
-      <c r="H78" s="61"/>
-    </row>
-    <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="119" t="s">
+      <c r="H79" s="59"/>
+    </row>
+    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="117" t="s">
         <v>14</v>
       </c>
-      <c r="B79" s="79" t="s">
-        <v>143</v>
-      </c>
-      <c r="C79" s="79"/>
-      <c r="D79" s="215">
+      <c r="B80" s="77" t="s">
+        <v>134</v>
+      </c>
+      <c r="C80" s="77"/>
+      <c r="D80" s="209">
         <v>119000</v>
       </c>
-      <c r="E79" s="60">
-        <f>D79*91.91%</f>
+      <c r="E80" s="58">
+        <f>D80*91.91%</f>
         <v>109372.9</v>
       </c>
-      <c r="F79" s="49">
-        <f>D79*8.09%</f>
+      <c r="F80" s="48">
+        <f>D80*8.09%</f>
         <v>9627.1</v>
       </c>
-      <c r="H79" s="61"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="119" t="s">
+      <c r="H80" s="65"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="79"/>
-      <c r="C80" s="79"/>
-      <c r="D80" s="215">
+      <c r="B81" s="77"/>
+      <c r="C81" s="77"/>
+      <c r="D81" s="209">
         <v>50000</v>
       </c>
-      <c r="E80" s="60">
-        <f>D80*91.91%</f>
+      <c r="E81" s="58">
+        <f>D81*91.91%</f>
         <v>45954.999999999993</v>
       </c>
-      <c r="F80" s="49">
-        <f>D80*8.09%</f>
+      <c r="F81" s="48">
+        <f>D81*8.09%</f>
         <v>4045</v>
       </c>
-      <c r="H80" s="61"/>
-      <c r="J80" s="37"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" s="119"/>
-      <c r="B81" s="79"/>
-      <c r="C81" s="79"/>
-      <c r="D81" s="104"/>
-      <c r="E81" s="60">
-        <f>D81*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F81" s="49">
-        <f>D81*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="H81" s="61"/>
-      <c r="J81" s="34"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" s="118"/>
-      <c r="B82" s="118"/>
-      <c r="C82" s="118"/>
-      <c r="D82" s="33">
-        <f>SUM(D78:D81)</f>
+      <c r="H81" s="59"/>
+      <c r="J81" s="36"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="117"/>
+      <c r="B82" s="77"/>
+      <c r="C82" s="77"/>
+      <c r="D82" s="102"/>
+      <c r="E82" s="58">
+        <f>D82*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F82" s="48">
+        <f>D82*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="H82" s="59"/>
+      <c r="J82" s="33"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="116"/>
+      <c r="B83" s="116"/>
+      <c r="C83" s="116"/>
+      <c r="D83" s="32">
+        <f>SUM(D79:D82)</f>
         <v>454700</v>
       </c>
-      <c r="E82" s="33">
-        <f>SUM(E78:E81)</f>
+      <c r="E83" s="32">
+        <f>SUM(E79:E82)</f>
         <v>417914.77</v>
       </c>
-      <c r="F82" s="33">
-        <f>SUM(F78:F81)</f>
+      <c r="F83" s="32">
+        <f>SUM(F79:F82)</f>
         <v>36785.230000000003</v>
       </c>
-      <c r="G82" s="34">
-        <f>E82+F82</f>
+      <c r="G83" s="33">
+        <f>E83+F83</f>
         <v>454700</v>
       </c>
-      <c r="H82" s="61" t="str">
-        <f>IF(D82=G82, "", "Error")</f>
+      <c r="H83" s="59" t="str">
+        <f>IF(D83=G83, "", "Error")</f>
         <v/>
       </c>
-      <c r="J82" s="34"/>
-    </row>
-    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="119" t="s">
+      <c r="J83" s="33"/>
+    </row>
+    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="117" t="s">
         <v>73</v>
       </c>
-      <c r="B83" s="79"/>
-      <c r="C83" s="79"/>
-      <c r="D83" s="37"/>
-      <c r="E83" s="40"/>
-      <c r="F83" s="3"/>
-      <c r="H83" s="61"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" s="119" t="s">
+      <c r="B84" s="77"/>
+      <c r="C84" s="77"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="39"/>
+      <c r="F84" s="2"/>
+      <c r="H84" s="59"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="117" t="s">
         <v>74</v>
       </c>
-      <c r="B84" s="79"/>
-      <c r="C84" s="79"/>
-      <c r="D84" s="37">
+      <c r="B85" s="77"/>
+      <c r="C85" s="77"/>
+      <c r="D85" s="36">
         <f>152+180218.02</f>
         <v>180370.02</v>
       </c>
-      <c r="E84" s="60">
-        <f>D84*91.91%</f>
+      <c r="E85" s="58">
+        <f>D85*91.91%</f>
         <v>165778.08538199996</v>
       </c>
-      <c r="F84" s="49">
-        <f>D84*8.09%</f>
+      <c r="F85" s="48">
+        <f>D85*8.09%</f>
         <v>14591.934617999999</v>
       </c>
-      <c r="H84" s="61"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="119" t="s">
+      <c r="H85" s="59"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="117" t="s">
         <v>75</v>
       </c>
-      <c r="B85" s="79"/>
-      <c r="C85" s="130"/>
-      <c r="D85" s="37">
+      <c r="B86" s="77"/>
+      <c r="C86" s="126"/>
+      <c r="D86" s="36">
         <v>69000</v>
       </c>
-      <c r="E85" s="60">
-        <f>D85*91.91%</f>
+      <c r="E86" s="58">
+        <f>D86*91.91%</f>
         <v>63417.899999999994</v>
       </c>
-      <c r="F85" s="49">
-        <f>D85*8.09%</f>
+      <c r="F86" s="48">
+        <f>D86*8.09%</f>
         <v>5582.1</v>
       </c>
-      <c r="H85" s="61"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="118" t="s">
+      <c r="H86" s="59"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="116" t="s">
         <v>15</v>
       </c>
-      <c r="B86" s="118"/>
-      <c r="C86" s="118"/>
-      <c r="D86" s="64">
-        <f>SUM(D84:D85)</f>
+      <c r="B87" s="116"/>
+      <c r="C87" s="116"/>
+      <c r="D87" s="62">
+        <f>SUM(D85:D86)</f>
         <v>249370.02</v>
       </c>
-      <c r="E86" s="58">
-        <f t="shared" ref="E86:F86" si="22">SUM(E84:E85)</f>
+      <c r="E87" s="56">
+        <f t="shared" ref="E87:F87" si="20">SUM(E85:E86)</f>
         <v>229195.98538199996</v>
       </c>
-      <c r="F86" s="58">
+      <c r="F87" s="56">
+        <f t="shared" si="20"/>
+        <v>20174.034617999998</v>
+      </c>
+      <c r="G87" s="33">
+        <f>E87+F87</f>
+        <v>249370.01999999996</v>
+      </c>
+      <c r="H87" s="59" t="str">
+        <f>IF(D87=G87, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="77"/>
+      <c r="B88" s="77"/>
+      <c r="C88" s="77"/>
+      <c r="D88" s="77"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="2"/>
+      <c r="H88" s="59"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="127" t="s">
+        <v>102</v>
+      </c>
+      <c r="B89" s="127"/>
+      <c r="C89" s="140"/>
+      <c r="D89" s="141"/>
+      <c r="E89" s="139">
+        <f>D89*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F89" s="50">
+        <f>D89*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G89" s="33">
+        <f>E89+F89</f>
+        <v>0</v>
+      </c>
+      <c r="H89" s="59" t="str">
+        <f>IF(D89=G89, "", "Error")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="128"/>
+      <c r="B90" s="76"/>
+      <c r="C90" s="76"/>
+      <c r="D90" s="142"/>
+      <c r="E90" s="143"/>
+      <c r="F90" s="143"/>
+      <c r="G90" s="61"/>
+      <c r="H90" s="59"/>
+    </row>
+    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="129" t="s">
+        <v>76</v>
+      </c>
+      <c r="B91" s="130"/>
+      <c r="C91" s="131"/>
+      <c r="D91" s="78">
+        <f>SUM(D89+D87+D83+D75+D68+D49+D32+D27+D43)</f>
+        <v>12215707.529999999</v>
+      </c>
+      <c r="E91" s="57">
+        <f>SUM(E89+E87+E83+E75+E68+E49+E32+E27+E43)</f>
+        <v>11623292.497903001</v>
+      </c>
+      <c r="F91" s="144">
+        <f>SUM(F27+F43+F49+F68+F75+F83+F87+F89)</f>
+        <v>592415.03209700005</v>
+      </c>
+      <c r="G91" s="33">
+        <f>E91+F91</f>
+        <v>12215707.530000001</v>
+      </c>
+      <c r="H91" s="59" t="str">
+        <f>IF(D91=G91, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="I91" s="74">
+        <f>D91-G91</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="76"/>
+      <c r="B92" s="76"/>
+      <c r="C92" s="76"/>
+      <c r="D92" s="76"/>
+      <c r="E92" s="33"/>
+    </row>
+    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="B93" s="133"/>
+      <c r="C93" s="133"/>
+      <c r="D93" s="76"/>
+      <c r="E93" s="33"/>
+    </row>
+    <row r="94" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="214" t="s">
+        <v>133</v>
+      </c>
+      <c r="B94" s="215"/>
+      <c r="C94" s="221">
+        <v>320000</v>
+      </c>
+      <c r="D94" s="76"/>
+      <c r="E94" s="33"/>
+    </row>
+    <row r="95" spans="1:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="216"/>
+      <c r="B95" s="217"/>
+      <c r="C95" s="222"/>
+      <c r="D95" s="76"/>
+      <c r="E95" s="33"/>
+    </row>
+    <row r="96" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B96" s="55"/>
+      <c r="C96" s="53">
+        <f>SUM(C94:C95)</f>
+        <v>320000</v>
+      </c>
+      <c r="E96" s="33"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E97" s="33"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E98" s="51"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="175" t="s">
+        <v>85</v>
+      </c>
+      <c r="B99" s="176"/>
+      <c r="C99" s="176"/>
+      <c r="D99" s="176"/>
+      <c r="E99" s="71" t="s">
+        <v>19</v>
+      </c>
+      <c r="F99" s="72" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A100" s="172"/>
+      <c r="B100" s="173"/>
+      <c r="C100" s="174"/>
+      <c r="D100" s="36"/>
+      <c r="E100" s="58">
+        <f t="shared" ref="E100:E104" si="21">D100*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F100" s="48">
+        <f t="shared" ref="F100:F104" si="22">D100*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="177"/>
+      <c r="B101" s="178"/>
+      <c r="C101" s="179"/>
+      <c r="D101" s="36"/>
+      <c r="E101" s="58">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="F101" s="48">
         <f t="shared" si="22"/>
-        <v>20174.034617999998</v>
-      </c>
-      <c r="G86" s="34">
-        <f>E86+F86</f>
-        <v>249370.01999999996</v>
-      </c>
-      <c r="H86" s="61" t="str">
-        <f>IF(D86=G86, "", "Error")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="151"/>
+      <c r="B102" s="149"/>
+      <c r="C102" s="150"/>
+      <c r="D102" s="36"/>
+      <c r="E102" s="58">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="F102" s="48">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="151"/>
+      <c r="B103" s="149"/>
+      <c r="C103" s="150"/>
+      <c r="D103" s="36"/>
+      <c r="E103" s="58">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="F103" s="48">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="177"/>
+      <c r="B104" s="178"/>
+      <c r="C104" s="179"/>
+      <c r="D104" s="36"/>
+      <c r="E104" s="58">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="F104" s="48">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="169" t="s">
+        <v>25</v>
+      </c>
+      <c r="B105" s="170"/>
+      <c r="C105" s="171"/>
+      <c r="D105" s="70">
+        <f>SUM(D100:D104)</f>
+        <v>0</v>
+      </c>
+      <c r="E105" s="70">
+        <f>SUM(E100:E104)</f>
+        <v>0</v>
+      </c>
+      <c r="F105" s="70">
+        <f>SUM(F100:F104)</f>
+        <v>0</v>
+      </c>
+      <c r="H105" s="33"/>
+      <c r="I105" s="59" t="str">
+        <f>IF(D105=H105, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A87" s="79"/>
-      <c r="B87" s="79"/>
-      <c r="C87" s="79"/>
-      <c r="D87" s="79"/>
-      <c r="E87" s="6"/>
-      <c r="F87" s="3"/>
-      <c r="H87" s="61"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="131" t="s">
-        <v>102</v>
-      </c>
-      <c r="B88" s="131"/>
-      <c r="C88" s="144"/>
-      <c r="D88" s="145"/>
-      <c r="E88" s="143">
-        <f>D88*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F88" s="51">
-        <f>D88*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G88" s="34">
-        <f>E88+F88</f>
-        <v>0</v>
-      </c>
-      <c r="H88" s="61" t="str">
-        <f>IF(D88=G88, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="132"/>
-      <c r="B89" s="78"/>
-      <c r="C89" s="78"/>
-      <c r="D89" s="146"/>
-      <c r="E89" s="147"/>
-      <c r="F89" s="147"/>
-      <c r="G89" s="63"/>
-      <c r="H89" s="61"/>
-    </row>
-    <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="133" t="s">
-        <v>76</v>
-      </c>
-      <c r="B90" s="134"/>
-      <c r="C90" s="135"/>
-      <c r="D90" s="80">
-        <f>SUM(D88+D86+D82+D74+D67+D47+D32+D27+D42)</f>
-        <v>11981986.960000001</v>
-      </c>
-      <c r="E90" s="59">
-        <f>SUM(E88+E86+E82+E74+E67+E47+E32+E27+E42)</f>
-        <v>10607682.789126001</v>
-      </c>
-      <c r="F90" s="148">
-        <f>SUM(F27+F42+F47+F67+F74+F82+F86+F88)</f>
-        <v>594304.17087400006</v>
-      </c>
-      <c r="G90" s="34">
-        <f>E90+F90</f>
-        <v>11201986.960000001</v>
-      </c>
-      <c r="H90" s="61" t="str">
-        <f>IF(D90=G90, "", "Error")</f>
-        <v>Error</v>
-      </c>
-      <c r="I90" s="76">
-        <f>D90-G90</f>
-        <v>780000</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="78"/>
-      <c r="B91" s="78"/>
-      <c r="C91" s="78"/>
-      <c r="D91" s="78"/>
-      <c r="E91" s="34"/>
-    </row>
-    <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="136" t="s">
-        <v>108</v>
-      </c>
-      <c r="B92" s="137"/>
-      <c r="C92" s="137"/>
-      <c r="D92" s="78"/>
-      <c r="E92" s="34"/>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A93" s="1"/>
-      <c r="C93" s="54"/>
-      <c r="D93" s="78"/>
-      <c r="E93" s="34"/>
-    </row>
-    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="1"/>
-      <c r="C94" s="54"/>
-      <c r="D94" s="78"/>
-      <c r="E94" s="34"/>
-    </row>
-    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="56" t="s">
-        <v>25</v>
-      </c>
-      <c r="B95" s="57"/>
-      <c r="C95" s="55">
-        <f>SUM(C93:C94)</f>
-        <v>0</v>
-      </c>
-      <c r="E95" s="34"/>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E96" s="34"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E97" s="52"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A98" s="181" t="s">
-        <v>85</v>
-      </c>
-      <c r="B98" s="182"/>
-      <c r="C98" s="182"/>
-      <c r="D98" s="182"/>
-      <c r="E98" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="F98" s="74" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A99" s="178" t="s">
-        <v>126</v>
-      </c>
-      <c r="B99" s="179"/>
-      <c r="C99" s="180"/>
-      <c r="D99" s="37">
-        <v>4000000</v>
-      </c>
-      <c r="E99" s="60">
-        <f t="shared" ref="E99:E103" si="23">D99*91.91%</f>
-        <v>3676399.9999999995</v>
-      </c>
-      <c r="F99" s="49">
-        <f t="shared" ref="F99:F103" si="24">D99*8.09%</f>
-        <v>323600</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A100" s="183" t="s">
-        <v>127</v>
-      </c>
-      <c r="B100" s="184"/>
-      <c r="C100" s="185"/>
-      <c r="D100" s="37">
-        <v>891000</v>
-      </c>
-      <c r="E100" s="60">
-        <f t="shared" si="23"/>
-        <v>818918.1</v>
-      </c>
-      <c r="F100" s="49">
-        <f t="shared" si="24"/>
-        <v>72081.899999999994</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A101" s="157" t="s">
-        <v>130</v>
-      </c>
-      <c r="B101" s="155"/>
-      <c r="C101" s="156"/>
-      <c r="D101" s="37">
-        <v>94457.62</v>
-      </c>
-      <c r="E101" s="60">
-        <f t="shared" si="23"/>
-        <v>86815.998541999987</v>
-      </c>
-      <c r="F101" s="49">
-        <f t="shared" si="24"/>
-        <v>7641.6214579999996</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A102" s="157" t="s">
-        <v>129</v>
-      </c>
-      <c r="B102" s="155"/>
-      <c r="C102" s="156"/>
-      <c r="D102" s="37">
-        <v>880000</v>
-      </c>
-      <c r="E102" s="60">
-        <f t="shared" si="23"/>
-        <v>808807.99999999988</v>
-      </c>
-      <c r="F102" s="49">
-        <f t="shared" si="24"/>
-        <v>71192</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="183" t="s">
-        <v>128</v>
-      </c>
-      <c r="B103" s="184"/>
-      <c r="C103" s="185"/>
-      <c r="D103" s="37">
-        <v>713614</v>
-      </c>
-      <c r="E103" s="60">
-        <f t="shared" si="23"/>
-        <v>655882.6274</v>
-      </c>
-      <c r="F103" s="49">
-        <f t="shared" si="24"/>
-        <v>57731.372600000002</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A104" s="175" t="s">
-        <v>25</v>
-      </c>
-      <c r="B104" s="176"/>
-      <c r="C104" s="177"/>
-      <c r="D104" s="72">
-        <f>SUM(D99:D103)</f>
-        <v>6579071.6200000001</v>
-      </c>
-      <c r="E104" s="72">
-        <f>SUM(E99:E103)</f>
-        <v>6046824.7259419989</v>
-      </c>
-      <c r="F104" s="72">
-        <f>SUM(F99:F103)</f>
-        <v>532246.89405800006</v>
-      </c>
-      <c r="H104" s="34">
-        <f>E104+F104</f>
-        <v>6579071.6199999992</v>
-      </c>
-      <c r="I104" s="61" t="str">
-        <f>IF(D104=H104, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D105" s="34"/>
-      <c r="H105" s="34"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" s="190" t="s">
-        <v>131</v>
-      </c>
-      <c r="B106" s="190"/>
-      <c r="C106" s="190"/>
-      <c r="D106" s="190"/>
-      <c r="E106" s="190"/>
-      <c r="F106" s="190"/>
-      <c r="H106" s="34"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A107" s="190"/>
-      <c r="B107" s="190"/>
-      <c r="C107" s="190"/>
-      <c r="D107" s="190"/>
-      <c r="E107" s="190"/>
-      <c r="F107" s="190"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A108" s="190"/>
-      <c r="B108" s="190"/>
-      <c r="C108" s="190"/>
-      <c r="D108" s="190"/>
-      <c r="E108" s="190"/>
-      <c r="F108" s="190"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" s="190"/>
-      <c r="B109" s="190"/>
-      <c r="C109" s="190"/>
-      <c r="D109" s="190"/>
-      <c r="E109" s="190"/>
-      <c r="F109" s="190"/>
-    </row>
-    <row r="110" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E110" s="34"/>
-    </row>
-    <row r="111" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="28" t="s">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D106" s="33"/>
+      <c r="H106" s="33"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="184" t="s">
+        <v>124</v>
+      </c>
+      <c r="B107" s="184"/>
+      <c r="C107" s="184"/>
+      <c r="D107" s="184"/>
+      <c r="E107" s="184"/>
+      <c r="F107" s="184"/>
+      <c r="H107" s="33"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="184"/>
+      <c r="B108" s="184"/>
+      <c r="C108" s="184"/>
+      <c r="D108" s="184"/>
+      <c r="E108" s="184"/>
+      <c r="F108" s="184"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="184"/>
+      <c r="B109" s="184"/>
+      <c r="C109" s="184"/>
+      <c r="D109" s="184"/>
+      <c r="E109" s="184"/>
+      <c r="F109" s="184"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="184"/>
+      <c r="B110" s="184"/>
+      <c r="C110" s="184"/>
+      <c r="D110" s="184"/>
+      <c r="E110" s="184"/>
+      <c r="F110" s="184"/>
+    </row>
+    <row r="111" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E111" s="33"/>
+    </row>
+    <row r="112" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="B111" s="29">
-        <f>D90</f>
-        <v>11981986.960000001</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="30" t="s">
+      <c r="B112" s="28">
+        <f>D91</f>
+        <v>12215707.529999999</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="B112" s="31">
-        <f>D90-D88</f>
-        <v>11981986.960000001</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D113" s="165"/>
-      <c r="E113" s="165"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" s="9" t="s">
+      <c r="B113" s="30">
+        <f>D91-D89</f>
+        <v>12215707.529999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D114" s="159"/>
+      <c r="E114" s="159"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B114" s="10"/>
-      <c r="C114" s="11"/>
-      <c r="D114" s="165"/>
-      <c r="E114" s="165"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" s="12" t="s">
+      <c r="B115" s="9"/>
+      <c r="C115" s="10"/>
+      <c r="D115" s="159"/>
+      <c r="E115" s="159"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B115" s="5">
+      <c r="B116" s="4">
         <v>14089108.26</v>
       </c>
-      <c r="C115" s="13"/>
-      <c r="D115" s="165"/>
-      <c r="E115" s="165"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A116" s="14" t="s">
+      <c r="C116" s="12"/>
+      <c r="D116" s="159"/>
+      <c r="E116" s="159"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B116" s="23">
+      <c r="B117" s="22">
         <f>PRORRATEO!G52</f>
-        <v>8666282.7266246639</v>
-      </c>
-      <c r="C116" s="13" t="s">
+        <v>8264798.2205740046</v>
+      </c>
+      <c r="C117" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D116" s="165"/>
-      <c r="E116" s="165"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" s="14" t="s">
+      <c r="D117" s="159"/>
+      <c r="E117" s="159"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B117" s="75">
-        <f>-B112</f>
-        <v>-11981986.960000001</v>
-      </c>
-      <c r="C117" s="11"/>
-      <c r="D117" s="165"/>
-      <c r="E117" s="165"/>
-      <c r="G117" s="37"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="14" t="s">
+      <c r="B118" s="73">
+        <f>-B113</f>
+        <v>-12215707.529999999</v>
+      </c>
+      <c r="C118" s="10"/>
+      <c r="D118" s="159"/>
+      <c r="E118" s="159"/>
+      <c r="G118" s="36"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B118" s="75">
-        <f>-D104</f>
-        <v>-6579071.6200000001</v>
-      </c>
-      <c r="C118" s="11"/>
-      <c r="D118" s="165"/>
-      <c r="E118" s="165"/>
-      <c r="G118" s="43"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="14" t="s">
+      <c r="B119" s="73">
+        <f>-D105</f>
+        <v>0</v>
+      </c>
+      <c r="C119" s="10"/>
+      <c r="D119" s="159"/>
+      <c r="E119" s="159"/>
+      <c r="G119" s="42"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B119" s="75">
-        <f>-B125</f>
-        <v>0</v>
-      </c>
-      <c r="C119" s="15"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="14" t="s">
+      <c r="B120" s="73">
+        <f>-B126</f>
+        <v>0</v>
+      </c>
+      <c r="C120" s="14"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="B120" s="24">
-        <f>-C95</f>
-        <v>0</v>
-      </c>
-      <c r="C120" s="15"/>
-      <c r="E120" s="34"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="12" t="s">
+      <c r="B121" s="23">
+        <f>-C96</f>
+        <v>-320000</v>
+      </c>
+      <c r="C121" s="14"/>
+      <c r="E121" s="33"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B121" s="16">
-        <f>SUM(B115:B120)</f>
-        <v>4194332.4066246646</v>
-      </c>
-      <c r="C121" s="62"/>
-      <c r="D121" s="34"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="15"/>
-      <c r="C122" s="11"/>
-      <c r="D122" s="18"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C123" s="11"/>
-      <c r="D123" s="34"/>
-      <c r="E123" s="76"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="9" t="s">
+      <c r="B122" s="15">
+        <f>SUM(B116:B121)</f>
+        <v>9818198.950574005</v>
+      </c>
+      <c r="C122" s="60"/>
+      <c r="D122" s="33"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="14"/>
+      <c r="C123" s="10"/>
+      <c r="D123" s="17"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C124" s="10"/>
+      <c r="D124" s="33"/>
+      <c r="E124" s="74"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B124" s="86">
+      <c r="B125" s="84">
         <f>-82694.54</f>
         <v>-82694.539999999994</v>
       </c>
-      <c r="C124" s="17"/>
-      <c r="D124" s="76"/>
-      <c r="E124" s="76"/>
-      <c r="F124" s="76"/>
-    </row>
-    <row r="125" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B125" s="24">
-        <v>0</v>
-      </c>
-      <c r="C125" s="17"/>
-      <c r="D125" s="76"/>
-      <c r="E125" s="81"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="12"/>
-      <c r="B126" s="75"/>
-      <c r="C126" s="17"/>
-      <c r="E126" s="34"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" s="12"/>
-      <c r="B127" s="75"/>
-      <c r="C127" s="17"/>
-      <c r="D127" s="138"/>
-      <c r="E127" s="34"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="26" t="s">
+      <c r="C125" s="16"/>
+      <c r="D125" s="74"/>
+      <c r="E125" s="74"/>
+      <c r="F125" s="74"/>
+    </row>
+    <row r="126" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B126" s="23">
+        <v>0</v>
+      </c>
+      <c r="C126" s="16"/>
+      <c r="D126" s="74"/>
+      <c r="E126" s="79"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="11"/>
+      <c r="B127" s="73"/>
+      <c r="C127" s="16"/>
+      <c r="E127" s="33"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="11"/>
+      <c r="B128" s="73"/>
+      <c r="C128" s="16"/>
+      <c r="D128" s="134"/>
+      <c r="E128" s="33"/>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A129" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B128" s="27">
-        <f>SUM(B124:B127)</f>
+      <c r="B129" s="26">
+        <f>SUM(B125:B128)</f>
         <v>-82694.539999999994</v>
       </c>
-      <c r="C128" s="17"/>
-    </row>
-    <row r="129" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="C129" s="18"/>
-      <c r="D129" s="76"/>
-    </row>
-    <row r="130" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B130" s="15"/>
-      <c r="C130" s="11"/>
-    </row>
-    <row r="132" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="N132" s="6"/>
-    </row>
-    <row r="135" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B135" s="164"/>
-      <c r="C135" s="164"/>
-      <c r="D135" s="164"/>
-      <c r="E135" s="164"/>
-    </row>
-    <row r="136" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B136" s="164"/>
-      <c r="C136" s="164"/>
-      <c r="D136" s="164"/>
-      <c r="E136" s="164"/>
-    </row>
-    <row r="137" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B137" s="164"/>
-      <c r="C137" s="164"/>
-      <c r="D137" s="164"/>
-      <c r="E137" s="164"/>
-    </row>
-    <row r="138" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B138" s="164"/>
-      <c r="C138" s="164"/>
-      <c r="D138" s="164"/>
-      <c r="E138" s="164"/>
-    </row>
-    <row r="139" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B139" s="164"/>
-      <c r="C139" s="164"/>
-      <c r="D139" s="164"/>
-      <c r="E139" s="164"/>
+      <c r="C129" s="16"/>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C130" s="17"/>
+      <c r="D130" s="74"/>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B131" s="14"/>
+      <c r="C131" s="10"/>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N133" s="5"/>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B136" s="158"/>
+      <c r="C136" s="158"/>
+      <c r="D136" s="158"/>
+      <c r="E136" s="158"/>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B137" s="158"/>
+      <c r="C137" s="158"/>
+      <c r="D137" s="158"/>
+      <c r="E137" s="158"/>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B138" s="158"/>
+      <c r="C138" s="158"/>
+      <c r="D138" s="158"/>
+      <c r="E138" s="158"/>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B139" s="158"/>
+      <c r="C139" s="158"/>
+      <c r="D139" s="158"/>
+      <c r="E139" s="158"/>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B140" s="158"/>
+      <c r="C140" s="158"/>
+      <c r="D140" s="158"/>
+      <c r="E140" s="158"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A94:B95"/>
+    <mergeCell ref="C94:C95"/>
     <mergeCell ref="A61:C61"/>
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B135:E139"/>
-    <mergeCell ref="D113:E118"/>
+    <mergeCell ref="B136:E140"/>
+    <mergeCell ref="D114:E119"/>
     <mergeCell ref="B14:D17"/>
+    <mergeCell ref="A105:C105"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A99:D99"/>
     <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A67:C67"/>
     <mergeCell ref="A63:C63"/>
     <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A106:F109"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A107:F110"/>
+    <mergeCell ref="A62:C62"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3864,1995 +3905,1995 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" customWidth="1"/>
-    <col min="6" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
+    <col min="6" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="13.6640625" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="203" t="str">
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="198" t="str">
         <f>RESUMEN!C5</f>
         <v>VTO: 17/08</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="205"/>
-      <c r="K1" s="90" t="s">
+      <c r="B1" s="199"/>
+      <c r="C1" s="199"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="199"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="200"/>
+      <c r="K1" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="194">
-        <f>RESUMEN!D90</f>
-        <v>11981986.960000001</v>
-      </c>
-      <c r="M1" s="195"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="50">
+      <c r="L1" s="190">
+        <f>RESUMEN!D91</f>
+        <v>12215707.529999999</v>
+      </c>
+      <c r="M1" s="191"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="49">
         <f>L1*8.09%</f>
-        <v>969342.74506400002</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="206"/>
-      <c r="B2" s="207"/>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="207"/>
-      <c r="F2" s="207"/>
-      <c r="G2" s="207"/>
-      <c r="H2" s="207"/>
-      <c r="I2" s="207"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="92" t="s">
+        <v>988250.73917699989</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="201"/>
+      <c r="B2" s="202"/>
+      <c r="C2" s="202"/>
+      <c r="D2" s="202"/>
+      <c r="E2" s="202"/>
+      <c r="F2" s="202"/>
+      <c r="G2" s="202"/>
+      <c r="H2" s="202"/>
+      <c r="I2" s="202"/>
+      <c r="J2" s="203"/>
+      <c r="K2" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="93">
+      <c r="L2" s="3"/>
+      <c r="M2" s="91">
         <f>8500000-812600</f>
         <v>7687400</v>
       </c>
-      <c r="N2" s="94"/>
-      <c r="O2" s="50">
+      <c r="N2" s="92"/>
+      <c r="O2" s="49">
         <f>O1-K7-553-50-86-8</f>
-        <v>658222.52510600002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="206"/>
-      <c r="B3" s="207"/>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="207"/>
-      <c r="H3" s="207"/>
-      <c r="I3" s="207"/>
-      <c r="J3" s="208"/>
-      <c r="K3" s="92" t="s">
+        <v>677130.51921899989</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="201"/>
+      <c r="B3" s="202"/>
+      <c r="C3" s="202"/>
+      <c r="D3" s="202"/>
+      <c r="E3" s="202"/>
+      <c r="F3" s="202"/>
+      <c r="G3" s="202"/>
+      <c r="H3" s="202"/>
+      <c r="I3" s="202"/>
+      <c r="J3" s="203"/>
+      <c r="K3" s="90" t="s">
         <v>100</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="95">
-        <f>RESUMEN!D104</f>
-        <v>6579071.6200000001</v>
-      </c>
-      <c r="N3" s="96"/>
-      <c r="O3" s="8"/>
-    </row>
-    <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="209"/>
-      <c r="B4" s="210"/>
-      <c r="C4" s="210"/>
-      <c r="D4" s="210"/>
-      <c r="E4" s="210"/>
-      <c r="F4" s="210"/>
-      <c r="G4" s="210"/>
-      <c r="H4" s="210"/>
-      <c r="I4" s="210"/>
-      <c r="J4" s="211"/>
-      <c r="K4" s="97" t="s">
+      <c r="L3" s="3"/>
+      <c r="M3" s="93">
+        <f>RESUMEN!D105</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="94"/>
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="204"/>
+      <c r="B4" s="205"/>
+      <c r="C4" s="205"/>
+      <c r="D4" s="205"/>
+      <c r="E4" s="205"/>
+      <c r="F4" s="205"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
+      <c r="I4" s="205"/>
+      <c r="J4" s="206"/>
+      <c r="K4" s="95" t="s">
         <v>95</v>
       </c>
-      <c r="L4" s="98"/>
-      <c r="M4" s="99">
+      <c r="L4" s="96"/>
+      <c r="M4" s="97">
         <v>1789535.8099999996</v>
       </c>
-      <c r="N4" s="100"/>
-      <c r="O4" s="50">
+      <c r="N4" s="98"/>
+      <c r="O4" s="49">
         <f>M3/3</f>
-        <v>2193023.8733333335</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="191" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="185" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="212" t="s">
+      <c r="B5" s="207" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="191" t="s">
+      <c r="C5" s="185" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="201" t="s">
+      <c r="D5" s="187" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="191" t="s">
+      <c r="E5" s="185" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="191" t="s">
+      <c r="F5" s="185" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="191" t="s">
+      <c r="G5" s="185" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="198" t="s">
+      <c r="H5" s="194" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="201" t="s">
+      <c r="I5" s="187" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="192" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="196" t="s">
+      <c r="K5" s="192" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="196" t="s">
+      <c r="L5" s="192" t="s">
         <v>114</v>
       </c>
-      <c r="M5" s="196" t="s">
+      <c r="M5" s="192" t="s">
         <v>116</v>
       </c>
-      <c r="N5" s="196" t="s">
+      <c r="N5" s="192" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="192"/>
-      <c r="B6" s="213"/>
-      <c r="C6" s="192"/>
-      <c r="D6" s="214"/>
-      <c r="E6" s="192"/>
-      <c r="F6" s="192"/>
-      <c r="G6" s="192"/>
-      <c r="H6" s="199"/>
-      <c r="I6" s="202"/>
-      <c r="J6" s="200"/>
-      <c r="K6" s="197"/>
-      <c r="L6" s="200"/>
-      <c r="M6" s="197"/>
-      <c r="N6" s="197"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="186"/>
+      <c r="B6" s="208"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="186"/>
+      <c r="F6" s="186"/>
+      <c r="G6" s="186"/>
+      <c r="H6" s="195"/>
+      <c r="I6" s="197"/>
+      <c r="J6" s="196"/>
+      <c r="K6" s="193"/>
+      <c r="L6" s="196"/>
+      <c r="M6" s="193"/>
+      <c r="N6" s="193"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2">
         <v>1</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>8.09</v>
       </c>
-      <c r="F7" s="19">
-        <v>310423.219958</v>
-      </c>
-      <c r="G7" s="154">
+      <c r="F7" s="18">
+        <v>482508.47</v>
+      </c>
+      <c r="G7" s="219">
         <f>F7</f>
-        <v>310423.219958</v>
-      </c>
-      <c r="H7" s="46">
+        <v>482508.47</v>
+      </c>
+      <c r="H7" s="45">
         <f>F7-G7</f>
         <v>0</v>
       </c>
-      <c r="I7" s="32">
-        <v>16</v>
-      </c>
-      <c r="J7" s="19">
+      <c r="I7" s="31">
+        <v>20</v>
+      </c>
+      <c r="J7" s="18">
         <f>M$4*E7%</f>
         <v>144773.44702899997</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="18">
         <v>310423.219958</v>
       </c>
-      <c r="L7" s="25"/>
-      <c r="M7" s="2">
+      <c r="L7" s="24"/>
+      <c r="M7" s="1">
         <f>K7+J7+H7+L7</f>
         <v>455196.66698699998</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="4">
         <f>M7*6% + M7</f>
         <v>482508.46700621996</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2">
         <v>24</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>2.21</v>
       </c>
-      <c r="F8" s="19">
-        <v>167564.47683118255</v>
-      </c>
-      <c r="G8" s="154">
-        <v>180000</v>
-      </c>
-      <c r="H8" s="46">
+      <c r="F8" s="18">
+        <v>197004.75823218253</v>
+      </c>
+      <c r="G8" s="219">
+        <v>200000</v>
+      </c>
+      <c r="H8" s="45">
         <f t="shared" ref="H8:H51" si="0">F8-G8</f>
-        <v>-12435.523168817454</v>
-      </c>
-      <c r="I8" s="32">
-        <v>10</v>
-      </c>
-      <c r="J8" s="19">
+        <v>-2995.2417678174679</v>
+      </c>
+      <c r="I8" s="31">
+        <v>13</v>
+      </c>
+      <c r="J8" s="18">
         <f>M$4*E8%</f>
         <v>39548.741400999985</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="18">
         <f>M$2*E8 /100</f>
         <v>169891.54</v>
       </c>
-      <c r="L8" s="88"/>
-      <c r="M8" s="2">
+      <c r="L8" s="86"/>
+      <c r="M8" s="1">
         <f>K8+J8+H8+L8</f>
-        <v>197004.75823218253</v>
-      </c>
-      <c r="N8" s="5">
+        <v>206445.03963318252</v>
+      </c>
+      <c r="N8" s="4">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>208825.04372611348</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+        <v>218831.74201117345</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2">
         <v>25</v>
       </c>
-      <c r="D9" s="48" t="s">
+      <c r="D9" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>4.21</v>
       </c>
-      <c r="F9" s="19">
-        <v>323639.1428675967</v>
-      </c>
-      <c r="G9" s="105">
-        <f>365151-G34</f>
-        <v>323639.03999999998</v>
-      </c>
-      <c r="H9" s="46">
+      <c r="F9" s="18">
+        <v>398979.10046859668</v>
+      </c>
+      <c r="G9" s="218">
+        <f>450154-G34</f>
+        <v>398978.54662599997</v>
+      </c>
+      <c r="H9" s="45">
         <f t="shared" si="0"/>
-        <v>0.10286759672453627</v>
-      </c>
-      <c r="I9" s="32">
-        <v>9</v>
-      </c>
-      <c r="J9" s="19">
+        <v>0.55384259670972824</v>
+      </c>
+      <c r="I9" s="31">
+        <v>13</v>
+      </c>
+      <c r="J9" s="18">
         <f t="shared" ref="J9:J51" si="2">M$4*E9%</f>
         <v>75339.457600999987</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="18">
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
         <v>323639.53999999998</v>
       </c>
-      <c r="L9" s="88"/>
-      <c r="M9" s="2">
+      <c r="L9" s="86"/>
+      <c r="M9" s="1">
         <f t="shared" ref="M9:M51" si="4">K9+J9+H9+L9</f>
-        <v>398979.10046859668</v>
-      </c>
-      <c r="N9" s="5">
+        <v>398979.55144359666</v>
+      </c>
+      <c r="N9" s="4">
         <f t="shared" si="1"/>
-        <v>422917.84649671247</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+        <v>422918.32453021244</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2">
         <v>26</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>2.84</v>
       </c>
-      <c r="F10" s="19">
-        <v>242122.16</v>
-      </c>
-      <c r="G10" s="154">
+      <c r="F10" s="18">
+        <v>292945.13700400002</v>
+      </c>
+      <c r="G10" s="148">
         <v>218322</v>
       </c>
-      <c r="H10" s="46">
+      <c r="H10" s="45">
         <f t="shared" si="0"/>
-        <v>23800.160000000003</v>
-      </c>
-      <c r="I10" s="32">
+        <v>74623.137004000018</v>
+      </c>
+      <c r="I10" s="31">
         <v>12</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="18">
         <f t="shared" si="2"/>
         <v>50822.817003999982</v>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="18">
         <f t="shared" si="3"/>
         <v>218322.16</v>
       </c>
-      <c r="L10" s="88"/>
-      <c r="M10" s="2">
+      <c r="L10" s="86"/>
+      <c r="M10" s="1">
         <f t="shared" si="4"/>
-        <v>292945.13700400002</v>
-      </c>
-      <c r="N10" s="5">
+        <v>343768.114008</v>
+      </c>
+      <c r="N10" s="4">
         <f t="shared" si="1"/>
-        <v>310521.84522424004</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+        <v>364394.20084847999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2">
         <v>27</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D11" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>3.43</v>
       </c>
-      <c r="F11" s="19">
-        <v>263677.82</v>
-      </c>
-      <c r="G11" s="154">
+      <c r="F11" s="18">
+        <v>325058.89828299999</v>
+      </c>
+      <c r="G11" s="219">
         <f>F11</f>
-        <v>263677.82</v>
-      </c>
-      <c r="H11" s="46">
+        <v>325058.89828299999</v>
+      </c>
+      <c r="H11" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="32">
-        <v>12</v>
-      </c>
-      <c r="J11" s="19">
+      <c r="I11" s="31">
+        <v>13</v>
+      </c>
+      <c r="J11" s="18">
         <f t="shared" si="2"/>
         <v>61381.078282999995</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="18">
         <f t="shared" si="3"/>
         <v>263677.82</v>
       </c>
-      <c r="L11" s="88"/>
-      <c r="M11" s="2">
+      <c r="L11" s="86"/>
+      <c r="M11" s="1">
         <f t="shared" si="4"/>
         <v>325058.89828299999</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N11" s="4">
         <f t="shared" si="1"/>
         <v>344562.43217997998</v>
       </c>
-      <c r="P11" s="34"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="P11" s="33"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2">
         <v>28</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>2.84</v>
       </c>
-      <c r="F12" s="19">
-        <v>218322.16</v>
-      </c>
-      <c r="G12" s="105">
+      <c r="F12" s="18">
+        <v>269144.97700399999</v>
+      </c>
+      <c r="G12" s="218">
         <f>F12</f>
-        <v>218322.16</v>
-      </c>
-      <c r="H12" s="46">
+        <v>269144.97700399999</v>
+      </c>
+      <c r="H12" s="45">
         <f>F12-G12</f>
         <v>0</v>
       </c>
-      <c r="I12" s="32">
-        <v>9</v>
-      </c>
-      <c r="J12" s="19">
+      <c r="I12" s="31">
+        <v>7</v>
+      </c>
+      <c r="J12" s="18">
         <f t="shared" si="2"/>
         <v>50822.817003999982</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="18">
         <f t="shared" si="3"/>
         <v>218322.16</v>
       </c>
-      <c r="L12" s="88"/>
-      <c r="M12" s="2">
+      <c r="L12" s="86"/>
+      <c r="M12" s="1">
         <f t="shared" si="4"/>
         <v>269144.97700399999</v>
       </c>
-      <c r="N12" s="5">
+      <c r="N12" s="4">
         <f t="shared" si="1"/>
         <v>285293.67562423996</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2">
         <v>29</v>
       </c>
-      <c r="D13" s="48" t="s">
+      <c r="D13" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <v>3.43</v>
       </c>
-      <c r="F13" s="19">
-        <v>263677.63741924177</v>
-      </c>
-      <c r="G13" s="105">
-        <f>309034-G50</f>
-        <v>263678.33999999997</v>
-      </c>
-      <c r="H13" s="46">
+      <c r="F13" s="18">
+        <v>325058.19570224179</v>
+      </c>
+      <c r="G13" s="218">
+        <f>380972-G50</f>
+        <v>325058.078721</v>
+      </c>
+      <c r="H13" s="45">
         <f t="shared" si="0"/>
-        <v>-0.7025807581958361</v>
-      </c>
-      <c r="I13" s="32">
-        <v>8</v>
-      </c>
-      <c r="J13" s="19">
+        <v>0.1169812417938374</v>
+      </c>
+      <c r="I13" s="31">
+        <v>7</v>
+      </c>
+      <c r="J13" s="18">
         <f t="shared" si="2"/>
         <v>61381.078282999995</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="18">
         <f t="shared" si="3"/>
         <v>263677.82</v>
       </c>
-      <c r="L13" s="88"/>
-      <c r="M13" s="2">
+      <c r="L13" s="86"/>
+      <c r="M13" s="1">
         <f t="shared" si="4"/>
-        <v>325058.19570224179</v>
-      </c>
-      <c r="N13" s="5">
+        <v>325059.01526424178</v>
+      </c>
+      <c r="N13" s="4">
         <f t="shared" si="1"/>
-        <v>344561.68744437629</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+        <v>344562.55618009629</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2">
         <v>30</v>
       </c>
-      <c r="D14" s="48" t="s">
+      <c r="D14" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <v>2.84</v>
       </c>
-      <c r="F14" s="19">
-        <v>588506.98054666666</v>
-      </c>
-      <c r="G14" s="154">
+      <c r="F14" s="18">
+        <v>639329.95755066664</v>
+      </c>
+      <c r="G14" s="148">
         <v>218322</v>
       </c>
-      <c r="H14" s="46">
+      <c r="H14" s="45">
         <f t="shared" si="0"/>
-        <v>370184.98054666666</v>
-      </c>
-      <c r="I14" s="32">
+        <v>421007.95755066664</v>
+      </c>
+      <c r="I14" s="31">
         <v>27</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="18">
         <f t="shared" si="2"/>
         <v>50822.817003999982</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="18">
         <f t="shared" si="3"/>
         <v>218322.16</v>
       </c>
-      <c r="L14" s="88"/>
-      <c r="M14" s="2">
+      <c r="L14" s="86"/>
+      <c r="M14" s="1">
         <f t="shared" si="4"/>
-        <v>639329.95755066664</v>
-      </c>
-      <c r="N14" s="5">
+        <v>690152.93455466663</v>
+      </c>
+      <c r="N14" s="4">
         <f t="shared" si="1"/>
-        <v>677689.75500370667</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+        <v>731562.11062794668</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2">
         <v>31</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <v>3.43</v>
       </c>
-      <c r="F15" s="19">
-        <v>555227.8832563262</v>
-      </c>
-      <c r="G15" s="105">
-        <f>636165-G35</f>
-        <v>555228</v>
-      </c>
-      <c r="H15" s="46">
+      <c r="F15" s="18">
+        <v>325058.78153932618</v>
+      </c>
+      <c r="G15" s="218">
+        <f>372444-G35</f>
+        <v>325059.32095000002</v>
+      </c>
+      <c r="H15" s="45">
         <f t="shared" si="0"/>
-        <v>-0.11674367380328476</v>
-      </c>
-      <c r="I15" s="32">
-        <v>17</v>
-      </c>
-      <c r="J15" s="19">
+        <v>-0.53941067383857444</v>
+      </c>
+      <c r="I15" s="31">
+        <v>6</v>
+      </c>
+      <c r="J15" s="18">
         <f t="shared" si="2"/>
         <v>61381.078282999995</v>
       </c>
-      <c r="K15" s="19">
+      <c r="K15" s="18">
         <f t="shared" si="3"/>
         <v>263677.82</v>
       </c>
-      <c r="L15" s="88"/>
-      <c r="M15" s="2">
+      <c r="L15" s="86"/>
+      <c r="M15" s="1">
         <f t="shared" si="4"/>
-        <v>325058.78153932618</v>
-      </c>
-      <c r="N15" s="5">
+        <v>325058.35887232615</v>
+      </c>
+      <c r="N15" s="4">
         <f t="shared" si="1"/>
-        <v>344562.30843168573</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+        <v>344561.8604046657</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2">
         <v>32</v>
       </c>
-      <c r="D16" s="48" t="s">
+      <c r="D16" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <v>2.84</v>
       </c>
-      <c r="F16" s="19">
-        <v>218322.23982700004</v>
-      </c>
-      <c r="G16" s="105">
-        <f>255990-G49</f>
-        <v>218321.74</v>
-      </c>
-      <c r="H16" s="46">
+      <c r="F16" s="18">
+        <v>269145.47683100007</v>
+      </c>
+      <c r="G16" s="218">
+        <f>315582-G49</f>
+        <v>269145.01453099999</v>
+      </c>
+      <c r="H16" s="45">
         <f t="shared" si="0"/>
-        <v>0.49982700005057268</v>
-      </c>
-      <c r="I16" s="32">
-        <v>5</v>
-      </c>
-      <c r="J16" s="19">
+        <v>0.46230000007199124</v>
+      </c>
+      <c r="I16" s="31">
+        <v>7</v>
+      </c>
+      <c r="J16" s="18">
         <f t="shared" si="2"/>
         <v>50822.817003999982</v>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="18">
         <f t="shared" si="3"/>
         <v>218322.16</v>
       </c>
-      <c r="L16" s="88"/>
-      <c r="M16" s="2">
+      <c r="L16" s="86"/>
+      <c r="M16" s="1">
         <f t="shared" si="4"/>
-        <v>269145.47683100007</v>
-      </c>
-      <c r="N16" s="5">
+        <v>269145.43930400006</v>
+      </c>
+      <c r="N16" s="4">
         <f t="shared" si="1"/>
-        <v>285294.20544086007</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+        <v>285294.16566224006</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2">
         <v>33</v>
       </c>
-      <c r="D17" s="48" t="s">
+      <c r="D17" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <v>3.43</v>
       </c>
-      <c r="F17" s="19">
-        <v>282068.20578511507</v>
-      </c>
-      <c r="G17" s="154">
-        <f>84739.59-G47-G48+278000</f>
-        <v>286634.33</v>
-      </c>
-      <c r="H17" s="46">
+      <c r="F17" s="18">
+        <v>320492.77406811505</v>
+      </c>
+      <c r="G17" s="219">
+        <f>414315-G47-G48</f>
+        <v>320493.33548100002</v>
+      </c>
+      <c r="H17" s="45">
         <f t="shared" si="0"/>
-        <v>-4566.1242148849415</v>
-      </c>
-      <c r="I17" s="32">
-        <v>17</v>
-      </c>
-      <c r="J17" s="19">
+        <v>-0.56141288497019559</v>
+      </c>
+      <c r="I17" s="31">
+        <v>15</v>
+      </c>
+      <c r="J17" s="18">
         <f t="shared" si="2"/>
         <v>61381.078282999995</v>
       </c>
-      <c r="K17" s="19">
+      <c r="K17" s="18">
         <f t="shared" si="3"/>
         <v>263677.82</v>
       </c>
-      <c r="L17" s="88"/>
-      <c r="M17" s="2">
+      <c r="L17" s="86"/>
+      <c r="M17" s="1">
         <f t="shared" si="4"/>
-        <v>320492.77406811505</v>
-      </c>
-      <c r="N17" s="5">
+        <v>325058.33687011502</v>
+      </c>
+      <c r="N17" s="4">
         <f t="shared" si="1"/>
-        <v>339722.34051220195</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+        <v>344561.83708232193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2">
         <v>34</v>
       </c>
-      <c r="D18" s="48" t="s">
+      <c r="D18" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <v>2.84</v>
       </c>
-      <c r="F18" s="19">
-        <v>218321.66379991794</v>
-      </c>
-      <c r="G18" s="154">
-        <f>262164-G51</f>
-        <v>218345.82</v>
-      </c>
-      <c r="H18" s="46">
+      <c r="F18" s="18">
+        <v>269120.82080391794</v>
+      </c>
+      <c r="G18" s="219">
+        <f>262140-G51</f>
+        <v>208121.465883</v>
+      </c>
+      <c r="H18" s="45">
         <f t="shared" si="0"/>
-        <v>-24.156200082070427</v>
-      </c>
-      <c r="I18" s="32">
-        <v>10</v>
-      </c>
-      <c r="J18" s="19">
+        <v>60999.354920917947</v>
+      </c>
+      <c r="I18" s="31">
+        <v>7</v>
+      </c>
+      <c r="J18" s="18">
         <f t="shared" si="2"/>
         <v>50822.817003999982</v>
       </c>
-      <c r="K18" s="19">
+      <c r="K18" s="18">
         <f t="shared" si="3"/>
         <v>218322.16</v>
       </c>
-      <c r="L18" s="88"/>
-      <c r="M18" s="2">
+      <c r="L18" s="86"/>
+      <c r="M18" s="1">
         <f t="shared" si="4"/>
-        <v>269120.82080391794</v>
-      </c>
-      <c r="N18" s="5">
+        <v>330144.33192491793</v>
+      </c>
+      <c r="N18" s="4">
         <f t="shared" si="1"/>
-        <v>285268.07005215302</v>
+        <v>349952.99184041301</v>
       </c>
       <c r="P18" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2">
         <v>35</v>
       </c>
-      <c r="D19" s="48" t="s">
+      <c r="D19" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <v>3.43</v>
       </c>
-      <c r="F19" s="19">
-        <v>291549.63964850147</v>
-      </c>
-      <c r="G19" s="105">
-        <f>333062-G41</f>
-        <v>291550.03999999998</v>
-      </c>
-      <c r="H19" s="46">
+      <c r="F19" s="18">
+        <v>325058.49793150148</v>
+      </c>
+      <c r="G19" s="218">
+        <f>376233-G41</f>
+        <v>325057.54662599997</v>
+      </c>
+      <c r="H19" s="45">
         <f t="shared" si="0"/>
-        <v>-0.4003514985088259</v>
-      </c>
-      <c r="I19" s="32">
-        <v>5</v>
-      </c>
-      <c r="J19" s="19">
+        <v>0.95130550151225179</v>
+      </c>
+      <c r="I19" s="31">
+        <v>6</v>
+      </c>
+      <c r="J19" s="18">
         <f t="shared" si="2"/>
         <v>61381.078282999995</v>
       </c>
-      <c r="K19" s="19">
+      <c r="K19" s="18">
         <f t="shared" si="3"/>
         <v>263677.82</v>
       </c>
-      <c r="L19" s="88"/>
-      <c r="M19" s="2">
+      <c r="L19" s="86"/>
+      <c r="M19" s="1">
         <f t="shared" si="4"/>
-        <v>325058.49793150148</v>
-      </c>
-      <c r="N19" s="5">
+        <v>325059.8495885015</v>
+      </c>
+      <c r="N19" s="4">
         <f t="shared" si="1"/>
-        <v>344562.00780739158</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+        <v>344563.44056381157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2">
         <v>36</v>
       </c>
-      <c r="D20" s="48" t="s">
+      <c r="D20" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="2">
         <v>2.84</v>
       </c>
-      <c r="F20" s="19">
-        <v>218321.81585707472</v>
-      </c>
-      <c r="G20" s="154">
-        <f>255990-G38</f>
-        <v>218321.74</v>
-      </c>
-      <c r="H20" s="46">
+      <c r="F20" s="18">
+        <v>269145.05286107468</v>
+      </c>
+      <c r="G20" s="219">
+        <f>315582-G38</f>
+        <v>269145.01453099999</v>
+      </c>
+      <c r="H20" s="45">
         <f t="shared" si="0"/>
-        <v>7.585707472753711E-2</v>
-      </c>
-      <c r="I20" s="32">
-        <v>9</v>
-      </c>
-      <c r="J20" s="19">
+        <v>3.8330074690748006E-2</v>
+      </c>
+      <c r="I20" s="31">
+        <v>7</v>
+      </c>
+      <c r="J20" s="18">
         <f t="shared" si="2"/>
         <v>50822.817003999982</v>
       </c>
-      <c r="K20" s="19">
+      <c r="K20" s="18">
         <f t="shared" si="3"/>
         <v>218322.16</v>
       </c>
-      <c r="L20" s="88"/>
-      <c r="M20" s="2">
+      <c r="L20" s="86"/>
+      <c r="M20" s="1">
         <f t="shared" si="4"/>
-        <v>269145.05286107468</v>
-      </c>
-      <c r="N20" s="5">
+        <v>269145.01533407468</v>
+      </c>
+      <c r="N20" s="4">
         <f t="shared" si="1"/>
-        <v>285293.75603273918</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+        <v>285293.71625411918</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2">
         <v>37</v>
       </c>
-      <c r="D21" s="48" t="s">
+      <c r="D21" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="2">
         <v>3.43</v>
       </c>
-      <c r="F21" s="19">
-        <v>263677.8152936371</v>
-      </c>
-      <c r="G21" s="154">
-        <f>305190-G45</f>
-        <v>263678.03999999998</v>
-      </c>
-      <c r="H21" s="46">
+      <c r="F21" s="18">
+        <v>325058.67357663711</v>
+      </c>
+      <c r="G21" s="219">
+        <f>376234-G45</f>
+        <v>325058.54662599997</v>
+      </c>
+      <c r="H21" s="45">
         <f t="shared" si="0"/>
-        <v>-0.2247063628747128</v>
-      </c>
-      <c r="I21" s="32">
-        <v>8</v>
-      </c>
-      <c r="J21" s="19">
+        <v>0.1269506371463649</v>
+      </c>
+      <c r="I21" s="31">
+        <v>7</v>
+      </c>
+      <c r="J21" s="18">
         <f t="shared" si="2"/>
         <v>61381.078282999995</v>
       </c>
-      <c r="K21" s="19">
+      <c r="K21" s="18">
         <f t="shared" si="3"/>
         <v>263677.82</v>
       </c>
-      <c r="L21" s="88"/>
-      <c r="M21" s="2">
+      <c r="L21" s="86"/>
+      <c r="M21" s="1">
         <f t="shared" si="4"/>
-        <v>325058.67357663711</v>
-      </c>
-      <c r="N21" s="5">
+        <v>325059.02523363713</v>
+      </c>
+      <c r="N21" s="4">
         <f t="shared" si="1"/>
-        <v>344562.19399123534</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+        <v>344562.56674765534</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2">
         <v>38</v>
       </c>
-      <c r="D22" s="69" t="s">
+      <c r="D22" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="2">
         <v>2.84</v>
       </c>
-      <c r="F22" s="19">
-        <v>218322.16</v>
-      </c>
-      <c r="G22" s="154">
+      <c r="F22" s="18">
+        <v>269144.97700399999</v>
+      </c>
+      <c r="G22" s="219">
         <f>F22</f>
-        <v>218322.16</v>
-      </c>
-      <c r="H22" s="46">
+        <v>269144.97700399999</v>
+      </c>
+      <c r="H22" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="31">
         <v>7</v>
       </c>
-      <c r="J22" s="19">
+      <c r="J22" s="18">
         <f t="shared" si="2"/>
         <v>50822.817003999982</v>
       </c>
-      <c r="K22" s="19">
+      <c r="K22" s="18">
         <f t="shared" si="3"/>
         <v>218322.16</v>
       </c>
-      <c r="L22" s="88"/>
-      <c r="M22" s="2">
+      <c r="L22" s="86"/>
+      <c r="M22" s="1">
         <f t="shared" si="4"/>
         <v>269144.97700399999</v>
       </c>
-      <c r="N22" s="5">
+      <c r="N22" s="4">
         <f t="shared" si="1"/>
         <v>285293.67562423996</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2">
         <v>39</v>
       </c>
-      <c r="D23" s="48" t="s">
+      <c r="D23" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="2">
         <v>3.43</v>
       </c>
-      <c r="F23" s="19">
-        <v>261926.48790342227</v>
-      </c>
-      <c r="G23" s="105">
+      <c r="F23" s="18">
+        <v>285422.38618642226</v>
+      </c>
+      <c r="G23" s="103">
         <f>340000-G46</f>
-        <v>301563</v>
-      </c>
-      <c r="H23" s="46">
+        <v>292615.32095000002</v>
+      </c>
+      <c r="H23" s="45">
         <f t="shared" si="0"/>
-        <v>-39636.512096577731</v>
-      </c>
-      <c r="I23" s="32">
+        <v>-7192.9347635777667</v>
+      </c>
+      <c r="I23" s="31">
         <v>17</v>
       </c>
-      <c r="J23" s="19">
+      <c r="J23" s="18">
         <f t="shared" si="2"/>
         <v>61381.078282999995</v>
       </c>
-      <c r="K23" s="19">
+      <c r="K23" s="18">
         <f t="shared" si="3"/>
         <v>263677.82</v>
       </c>
-      <c r="L23" s="88"/>
-      <c r="M23" s="2">
+      <c r="L23" s="86"/>
+      <c r="M23" s="1">
         <f t="shared" si="4"/>
-        <v>285422.38618642226</v>
-      </c>
-      <c r="N23" s="5">
+        <v>317865.96351942222</v>
+      </c>
+      <c r="N23" s="4">
         <f t="shared" si="1"/>
-        <v>302547.7293576076</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+        <v>336937.92133058753</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2">
         <v>40</v>
       </c>
-      <c r="D24" s="48" t="s">
+      <c r="D24" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="2">
         <v>2.84</v>
       </c>
-      <c r="F24" s="19">
-        <v>210807.53342107471</v>
-      </c>
-      <c r="G24" s="154">
-        <f>248476-G37</f>
-        <v>210807.74</v>
-      </c>
-      <c r="H24" s="46">
+      <c r="F24" s="18">
+        <v>269144.77042507473</v>
+      </c>
+      <c r="G24" s="219">
+        <f>315582-G37</f>
+        <v>269145.01453099999</v>
+      </c>
+      <c r="H24" s="45">
         <f t="shared" si="0"/>
-        <v>-0.20657892528106458</v>
-      </c>
-      <c r="I24" s="77">
-        <v>7</v>
-      </c>
-      <c r="J24" s="19">
+        <v>-0.24410592525964603</v>
+      </c>
+      <c r="I24" s="75">
+        <v>16</v>
+      </c>
+      <c r="J24" s="18">
         <f t="shared" si="2"/>
         <v>50822.817003999982</v>
       </c>
-      <c r="K24" s="19">
+      <c r="K24" s="18">
         <f t="shared" si="3"/>
         <v>218322.16</v>
       </c>
-      <c r="L24" s="88"/>
-      <c r="M24" s="2">
+      <c r="L24" s="86"/>
+      <c r="M24" s="1">
         <f t="shared" si="4"/>
-        <v>269144.77042507473</v>
-      </c>
-      <c r="N24" s="5">
+        <v>269144.73289807473</v>
+      </c>
+      <c r="N24" s="4">
         <f t="shared" si="1"/>
-        <v>285293.45665057923</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+        <v>285293.41687195923</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3">
+      <c r="B25" s="2"/>
+      <c r="C25" s="2">
         <v>41</v>
       </c>
-      <c r="D25" s="48" t="s">
+      <c r="D25" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="2">
         <v>3.43</v>
       </c>
-      <c r="F25" s="19">
-        <v>247131.77666666667</v>
-      </c>
-      <c r="G25" s="105">
-        <f>F25</f>
-        <v>247131.77666666667</v>
-      </c>
-      <c r="H25" s="46">
+      <c r="F25" s="18">
+        <v>325058.89828299999</v>
+      </c>
+      <c r="G25" s="218">
+        <f>F25+1000</f>
+        <v>326058.89828299999</v>
+      </c>
+      <c r="H25" s="45">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="32">
-        <v>17</v>
-      </c>
-      <c r="J25" s="19">
+        <v>-1000</v>
+      </c>
+      <c r="I25" s="31">
+        <v>6</v>
+      </c>
+      <c r="J25" s="18">
         <f t="shared" si="2"/>
         <v>61381.078282999995</v>
       </c>
-      <c r="K25" s="19">
+      <c r="K25" s="18">
         <f t="shared" si="3"/>
         <v>263677.82</v>
       </c>
-      <c r="L25" s="89"/>
-      <c r="M25" s="2">
+      <c r="L25" s="87"/>
+      <c r="M25" s="1">
         <f t="shared" si="4"/>
-        <v>325058.89828299999</v>
-      </c>
-      <c r="N25" s="5">
+        <v>324058.89828299999</v>
+      </c>
+      <c r="N25" s="4">
         <f t="shared" si="1"/>
-        <v>344562.43217997998</v>
-      </c>
-      <c r="P25" s="53"/>
-      <c r="Q25" s="53"/>
-      <c r="R25" s="53"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+        <v>343502.43217997998</v>
+      </c>
+      <c r="P25" s="52"/>
+      <c r="Q25" s="52"/>
+      <c r="R25" s="52"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2">
         <v>42</v>
       </c>
-      <c r="D26" s="48" t="s">
+      <c r="D26" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="2">
         <v>6</v>
       </c>
-      <c r="F26" s="19">
-        <v>-1647267.3406672962</v>
-      </c>
-      <c r="G26" s="105">
-        <f>600000+900000-G30-G31-G36</f>
-        <v>1377770.34</v>
-      </c>
-      <c r="H26" s="47">
+      <c r="F26" s="18">
+        <v>-2456421.5320672961</v>
+      </c>
+      <c r="G26" s="218">
+        <f>-G30-G31-G36</f>
+        <v>-150683.27937900001</v>
+      </c>
+      <c r="H26" s="46">
         <f t="shared" si="0"/>
-        <v>-3025037.6806672961</v>
-      </c>
-      <c r="I26" s="149">
-        <v>1</v>
-      </c>
-      <c r="J26" s="19">
+        <v>-2305738.2526882961</v>
+      </c>
+      <c r="I26" s="145" t="s">
+        <v>145</v>
+      </c>
+      <c r="J26" s="18">
         <f t="shared" si="2"/>
         <v>107372.14859999997</v>
       </c>
-      <c r="K26" s="19">
+      <c r="K26" s="18">
         <f t="shared" si="3"/>
         <v>461244</v>
       </c>
-      <c r="L26" s="88"/>
-      <c r="M26" s="2">
+      <c r="L26" s="86"/>
+      <c r="M26" s="1">
         <f t="shared" si="4"/>
-        <v>-2456421.5320672961</v>
-      </c>
-      <c r="N26" s="5">
+        <v>-1737122.1040882962</v>
+      </c>
+      <c r="N26" s="4">
         <f t="shared" si="1"/>
-        <v>-2603806.8239913341</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+        <v>-1841349.4303335939</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2">
         <v>43</v>
       </c>
-      <c r="D27" s="48" t="s">
+      <c r="D27" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="2">
         <v>5.89</v>
       </c>
-      <c r="F27" s="19">
-        <v>452038.2312852653</v>
-      </c>
-      <c r="G27" s="154">
-        <f>541100-G39-G40</f>
-        <v>451926.16</v>
-      </c>
-      <c r="H27" s="46">
+      <c r="F27" s="18">
+        <v>558303.59049426531</v>
+      </c>
+      <c r="G27" s="219">
+        <f>668000-G39-G40</f>
+        <v>558067.54460400005</v>
+      </c>
+      <c r="H27" s="45">
         <f t="shared" si="0"/>
-        <v>112.07128526532324</v>
-      </c>
-      <c r="I27" s="32">
-        <v>16</v>
-      </c>
-      <c r="J27" s="19">
+        <v>236.04589026526082</v>
+      </c>
+      <c r="I27" s="31">
+        <v>17</v>
+      </c>
+      <c r="J27" s="18">
         <f t="shared" si="2"/>
         <v>105403.65920899996</v>
       </c>
-      <c r="K27" s="19">
+      <c r="K27" s="18">
         <f t="shared" si="3"/>
         <v>452787.86</v>
       </c>
-      <c r="L27" s="88"/>
-      <c r="M27" s="2">
+      <c r="L27" s="86"/>
+      <c r="M27" s="1">
         <f t="shared" si="4"/>
-        <v>558303.59049426531</v>
-      </c>
-      <c r="N27" s="5">
+        <v>558427.56509926519</v>
+      </c>
+      <c r="N27" s="4">
         <f t="shared" si="1"/>
-        <v>591801.80592392129</v>
-      </c>
-      <c r="R27" s="53"/>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+        <v>591933.21900522115</v>
+      </c>
+      <c r="R27" s="52"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2">
         <v>44</v>
       </c>
-      <c r="D28" s="48" t="s">
+      <c r="D28" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="2">
         <v>5.89</v>
       </c>
-      <c r="F28" s="19">
-        <v>442229.03449320735</v>
-      </c>
-      <c r="G28" s="154">
-        <f>525000-G32-G33</f>
-        <v>443513.56</v>
-      </c>
-      <c r="H28" s="46">
+      <c r="F28" s="18">
+        <v>556906.99370220723</v>
+      </c>
+      <c r="G28" s="219">
+        <f>658000-G32-G33</f>
+        <v>557544.48041400011</v>
+      </c>
+      <c r="H28" s="45">
         <f t="shared" si="0"/>
-        <v>-1284.5255067926482</v>
-      </c>
-      <c r="I28" s="32">
+        <v>-637.48671179288067</v>
+      </c>
+      <c r="I28" s="31">
         <v>8</v>
       </c>
-      <c r="J28" s="19">
+      <c r="J28" s="18">
         <f t="shared" si="2"/>
         <v>105403.65920899996</v>
       </c>
-      <c r="K28" s="19">
+      <c r="K28" s="18">
         <f t="shared" si="3"/>
         <v>452787.86</v>
       </c>
-      <c r="L28" s="88"/>
-      <c r="M28" s="2">
+      <c r="L28" s="86"/>
+      <c r="M28" s="1">
         <f t="shared" si="4"/>
-        <v>556906.99370220723</v>
-      </c>
-      <c r="N28" s="5">
+        <v>557554.03249720705</v>
+      </c>
+      <c r="N28" s="4">
         <f t="shared" si="1"/>
-        <v>590321.41332433966</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
+        <v>591007.27444703947</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2">
         <v>45</v>
       </c>
-      <c r="D29" s="48" t="s">
+      <c r="D29" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="2">
         <v>5.89</v>
       </c>
-      <c r="F29" s="19">
-        <v>427578.60619410186</v>
-      </c>
-      <c r="G29" s="105">
-        <f>551700-G42-G43-G44</f>
-        <v>427932.86</v>
-      </c>
-      <c r="H29" s="47">
+      <c r="F29" s="18">
+        <v>557837.2654031018</v>
+      </c>
+      <c r="G29" s="218">
+        <f>558000+153000-G42-G43-G44</f>
+        <v>558421.3334590001</v>
+      </c>
+      <c r="H29" s="46">
         <f t="shared" si="0"/>
-        <v>-354.25380589812994</v>
-      </c>
-      <c r="I29" s="32">
-        <v>6</v>
-      </c>
-      <c r="J29" s="19">
+        <v>-584.06805589830037</v>
+      </c>
+      <c r="I29" s="31">
+        <v>11</v>
+      </c>
+      <c r="J29" s="18">
         <f t="shared" si="2"/>
         <v>105403.65920899996</v>
       </c>
-      <c r="K29" s="19">
+      <c r="K29" s="18">
         <f t="shared" si="3"/>
         <v>452787.86</v>
       </c>
-      <c r="L29" s="88"/>
-      <c r="M29" s="2">
+      <c r="L29" s="86"/>
+      <c r="M29" s="1">
         <f t="shared" si="4"/>
-        <v>557837.2654031018</v>
-      </c>
-      <c r="N29" s="5">
+        <v>557607.45115310163</v>
+      </c>
+      <c r="N29" s="4">
         <f t="shared" si="1"/>
-        <v>591307.50132728787</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" s="44" t="s">
+        <v>591063.89822228777</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2">
         <v>1</v>
       </c>
-      <c r="D30" s="48" t="s">
+      <c r="D30" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="2">
         <v>0.54</v>
       </c>
-      <c r="F30" s="19">
-        <v>41511.960000000006</v>
-      </c>
-      <c r="G30" s="154">
+      <c r="F30" s="18">
+        <v>51175.453374000004</v>
+      </c>
+      <c r="G30" s="219">
         <f>F30</f>
-        <v>41511.960000000006</v>
-      </c>
-      <c r="H30" s="46">
+        <v>51175.453374000004</v>
+      </c>
+      <c r="H30" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30" s="32"/>
-      <c r="J30" s="19">
+      <c r="I30" s="31"/>
+      <c r="J30" s="18">
         <f t="shared" si="2"/>
         <v>9663.4933739999979</v>
       </c>
-      <c r="K30" s="19">
+      <c r="K30" s="18">
         <f t="shared" si="3"/>
         <v>41511.960000000006</v>
       </c>
-      <c r="L30" s="88"/>
-      <c r="M30" s="2">
+      <c r="L30" s="86"/>
+      <c r="M30" s="1">
         <f t="shared" si="4"/>
         <v>51175.453374000004</v>
       </c>
-      <c r="N30" s="5">
+      <c r="N30" s="4">
         <f t="shared" si="1"/>
         <v>54245.980576440008</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" s="44" t="s">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2">
         <v>2</v>
       </c>
-      <c r="D31" s="48" t="s">
+      <c r="D31" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="2">
         <v>0.55000000000000004</v>
       </c>
-      <c r="F31" s="19">
-        <v>42280.7</v>
-      </c>
-      <c r="G31" s="154">
+      <c r="F31" s="18">
+        <v>52123.146954999997</v>
+      </c>
+      <c r="G31" s="219">
         <f>F31</f>
-        <v>42280.7</v>
-      </c>
-      <c r="H31" s="46">
+        <v>52123.146954999997</v>
+      </c>
+      <c r="H31" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="32"/>
-      <c r="J31" s="19">
+      <c r="I31" s="31"/>
+      <c r="J31" s="18">
         <f t="shared" si="2"/>
         <v>9842.4469549999994</v>
       </c>
-      <c r="K31" s="19">
+      <c r="K31" s="18">
         <f t="shared" si="3"/>
         <v>42280.7</v>
       </c>
-      <c r="L31" s="88"/>
-      <c r="M31" s="2">
+      <c r="L31" s="86"/>
+      <c r="M31" s="1">
         <f t="shared" si="4"/>
         <v>52123.146954999997</v>
       </c>
-      <c r="N31" s="5">
+      <c r="N31" s="4">
         <f t="shared" si="1"/>
         <v>55250.535772299998</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" s="44" t="s">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2">
         <v>3</v>
       </c>
-      <c r="D32" s="48" t="s">
+      <c r="D32" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="2">
         <v>0.45</v>
       </c>
-      <c r="F32" s="19">
-        <v>34593.300000000003</v>
-      </c>
-      <c r="G32" s="154">
+      <c r="F32" s="18">
+        <v>42646.211145000001</v>
+      </c>
+      <c r="G32" s="219">
         <f>F32</f>
-        <v>34593.300000000003</v>
-      </c>
-      <c r="H32" s="46">
+        <v>42646.211145000001</v>
+      </c>
+      <c r="H32" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I32" s="32"/>
-      <c r="J32" s="19">
+      <c r="I32" s="31"/>
+      <c r="J32" s="18">
         <f t="shared" si="2"/>
         <v>8052.9111449999991</v>
       </c>
-      <c r="K32" s="19">
+      <c r="K32" s="18">
         <f t="shared" si="3"/>
         <v>34593.300000000003</v>
       </c>
-      <c r="L32" s="68"/>
-      <c r="M32" s="2">
+      <c r="L32" s="66"/>
+      <c r="M32" s="1">
         <f t="shared" si="4"/>
         <v>42646.211145000001</v>
       </c>
-      <c r="N32" s="5">
+      <c r="N32" s="4">
         <f t="shared" si="1"/>
         <v>45204.983813700004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="44" t="s">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2">
         <v>4</v>
       </c>
-      <c r="D33" s="48" t="s">
+      <c r="D33" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="2">
         <v>0.61</v>
       </c>
-      <c r="F33" s="19">
-        <v>46893.14</v>
-      </c>
-      <c r="G33" s="154">
+      <c r="F33" s="18">
+        <v>57809.308440999994</v>
+      </c>
+      <c r="G33" s="219">
         <f t="shared" ref="G33" si="5">F33</f>
-        <v>46893.14</v>
-      </c>
-      <c r="H33" s="46">
+        <v>57809.308440999994</v>
+      </c>
+      <c r="H33" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I33" s="32"/>
-      <c r="J33" s="19">
+      <c r="I33" s="31"/>
+      <c r="J33" s="18">
         <f t="shared" si="2"/>
         <v>10916.168440999996</v>
       </c>
-      <c r="K33" s="19">
+      <c r="K33" s="18">
         <f t="shared" si="3"/>
         <v>46893.14</v>
       </c>
-      <c r="L33" s="68"/>
-      <c r="M33" s="2">
+      <c r="L33" s="66"/>
+      <c r="M33" s="1">
         <f t="shared" si="4"/>
         <v>57809.308440999994</v>
       </c>
-      <c r="N33" s="5">
+      <c r="N33" s="4">
         <f t="shared" si="1"/>
         <v>61277.866947459996</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="44" t="s">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2">
         <v>5</v>
       </c>
-      <c r="D34" s="48" t="s">
+      <c r="D34" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="2">
         <v>0.54</v>
       </c>
-      <c r="F34" s="19">
-        <v>41511.960000000006</v>
-      </c>
-      <c r="G34" s="154">
+      <c r="F34" s="18">
+        <v>51175.453374000004</v>
+      </c>
+      <c r="G34" s="148">
         <f>F34</f>
-        <v>41511.960000000006</v>
-      </c>
-      <c r="H34" s="46">
+        <v>51175.453374000004</v>
+      </c>
+      <c r="H34" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I34" s="32"/>
-      <c r="J34" s="19">
+      <c r="I34" s="31"/>
+      <c r="J34" s="18">
         <f t="shared" si="2"/>
         <v>9663.4933739999979</v>
       </c>
-      <c r="K34" s="19">
+      <c r="K34" s="18">
         <f t="shared" si="3"/>
         <v>41511.960000000006</v>
       </c>
-      <c r="L34" s="68"/>
-      <c r="M34" s="2">
+      <c r="L34" s="66"/>
+      <c r="M34" s="1">
         <f t="shared" si="4"/>
         <v>51175.453374000004</v>
       </c>
-      <c r="N34" s="5">
+      <c r="N34" s="4">
         <f t="shared" si="1"/>
         <v>54245.980576440008</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="44" t="s">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2">
         <v>6</v>
       </c>
-      <c r="D35" s="48" t="s">
+      <c r="D35" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="2">
         <v>0.5</v>
       </c>
-      <c r="F35" s="158">
-        <v>80937</v>
-      </c>
-      <c r="G35" s="105">
+      <c r="F35" s="152">
+        <v>47384.679049999999</v>
+      </c>
+      <c r="G35" s="218">
         <f>F35</f>
-        <v>80937</v>
-      </c>
-      <c r="H35" s="46">
+        <v>47384.679049999999</v>
+      </c>
+      <c r="H35" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I35" s="32"/>
-      <c r="J35" s="19">
+      <c r="I35" s="31"/>
+      <c r="J35" s="18">
         <f t="shared" si="2"/>
         <v>8947.6790499999988</v>
       </c>
-      <c r="K35" s="19">
+      <c r="K35" s="18">
         <f t="shared" si="3"/>
         <v>38437</v>
       </c>
-      <c r="L35" s="68"/>
-      <c r="M35" s="2">
+      <c r="L35" s="66"/>
+      <c r="M35" s="1">
         <f t="shared" si="4"/>
         <v>47384.679049999999</v>
       </c>
-      <c r="N35" s="5">
+      <c r="N35" s="4">
         <f t="shared" si="1"/>
         <v>50227.759792999997</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A36" s="44" t="s">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2">
         <v>7</v>
       </c>
-      <c r="D36" s="48" t="s">
+      <c r="D36" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="2">
         <v>0.5</v>
       </c>
-      <c r="F36" s="19">
-        <v>38437</v>
-      </c>
-      <c r="G36" s="154">
+      <c r="F36" s="18">
+        <v>47384.679049999999</v>
+      </c>
+      <c r="G36" s="219">
         <f>F36</f>
-        <v>38437</v>
-      </c>
-      <c r="H36" s="46">
+        <v>47384.679049999999</v>
+      </c>
+      <c r="H36" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I36" s="32"/>
-      <c r="J36" s="19">
+      <c r="I36" s="31"/>
+      <c r="J36" s="18">
         <f t="shared" si="2"/>
         <v>8947.6790499999988</v>
       </c>
-      <c r="K36" s="19">
+      <c r="K36" s="18">
         <f t="shared" si="3"/>
         <v>38437</v>
       </c>
-      <c r="L36" s="68"/>
-      <c r="M36" s="2">
+      <c r="L36" s="66"/>
+      <c r="M36" s="1">
         <f t="shared" si="4"/>
         <v>47384.679049999999</v>
       </c>
-      <c r="N36" s="5">
+      <c r="N36" s="4">
         <f t="shared" si="1"/>
         <v>50227.759792999997</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A37" s="44" t="s">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2">
         <v>8</v>
       </c>
-      <c r="D37" s="48" t="s">
+      <c r="D37" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="2">
         <v>0.49</v>
       </c>
-      <c r="F37" s="19">
-        <v>37668.26</v>
-      </c>
-      <c r="G37" s="154">
+      <c r="F37" s="18">
+        <v>46436.985468999999</v>
+      </c>
+      <c r="G37" s="219">
         <f t="shared" ref="G37:G41" si="6">F37</f>
-        <v>37668.26</v>
-      </c>
-      <c r="H37" s="46">
+        <v>46436.985468999999</v>
+      </c>
+      <c r="H37" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I37" s="32"/>
-      <c r="J37" s="19">
+      <c r="I37" s="31"/>
+      <c r="J37" s="18">
         <f t="shared" si="2"/>
         <v>8768.7254689999972</v>
       </c>
-      <c r="K37" s="19">
+      <c r="K37" s="18">
         <f t="shared" si="3"/>
         <v>37668.26</v>
       </c>
-      <c r="L37" s="68"/>
-      <c r="M37" s="2">
+      <c r="L37" s="66"/>
+      <c r="M37" s="1">
         <f t="shared" si="4"/>
         <v>46436.985468999999</v>
       </c>
-      <c r="N37" s="5">
+      <c r="N37" s="4">
         <f t="shared" si="1"/>
         <v>49223.20459714</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A38" s="44" t="s">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2">
         <v>9</v>
       </c>
-      <c r="D38" s="48" t="s">
+      <c r="D38" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="2">
         <v>0.49</v>
       </c>
-      <c r="F38" s="19">
-        <v>37668.26</v>
-      </c>
-      <c r="G38" s="154">
+      <c r="F38" s="18">
+        <v>46436.985468999999</v>
+      </c>
+      <c r="G38" s="219">
         <f t="shared" si="6"/>
-        <v>37668.26</v>
-      </c>
-      <c r="H38" s="46">
+        <v>46436.985468999999</v>
+      </c>
+      <c r="H38" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I38" s="32"/>
-      <c r="J38" s="19">
+      <c r="I38" s="31"/>
+      <c r="J38" s="18">
         <f t="shared" si="2"/>
         <v>8768.7254689999972</v>
       </c>
-      <c r="K38" s="19">
+      <c r="K38" s="18">
         <f t="shared" si="3"/>
         <v>37668.26</v>
       </c>
-      <c r="L38" s="68"/>
-      <c r="M38" s="2">
+      <c r="L38" s="66"/>
+      <c r="M38" s="1">
         <f t="shared" si="4"/>
         <v>46436.985468999999</v>
       </c>
-      <c r="N38" s="5">
+      <c r="N38" s="4">
         <f t="shared" si="1"/>
         <v>49223.20459714</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A39" s="44" t="s">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2">
         <v>10</v>
       </c>
-      <c r="D39" s="48" t="s">
+      <c r="D39" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="2">
         <v>0.59</v>
       </c>
-      <c r="F39" s="19">
-        <v>45355.66</v>
-      </c>
-      <c r="G39" s="154">
+      <c r="F39" s="18">
+        <v>55913.921279000002</v>
+      </c>
+      <c r="G39" s="219">
         <f t="shared" si="6"/>
-        <v>45355.66</v>
-      </c>
-      <c r="H39" s="46">
+        <v>55913.921279000002</v>
+      </c>
+      <c r="H39" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I39" s="32"/>
-      <c r="J39" s="19">
+      <c r="I39" s="31"/>
+      <c r="J39" s="18">
         <f t="shared" si="2"/>
         <v>10558.261278999997</v>
       </c>
-      <c r="K39" s="19">
+      <c r="K39" s="18">
         <f t="shared" si="3"/>
         <v>45355.66</v>
       </c>
-      <c r="L39" s="68"/>
-      <c r="M39" s="2">
+      <c r="L39" s="66"/>
+      <c r="M39" s="1">
         <f t="shared" si="4"/>
         <v>55913.921279000002</v>
       </c>
-      <c r="N39" s="5">
+      <c r="N39" s="4">
         <f t="shared" si="1"/>
         <v>59268.756555740001</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A40" s="44" t="s">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2">
         <v>11</v>
       </c>
-      <c r="D40" s="48" t="s">
+      <c r="D40" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="2">
         <v>0.56999999999999995</v>
       </c>
-      <c r="F40" s="19">
-        <v>43818.18</v>
-      </c>
-      <c r="G40" s="154">
+      <c r="F40" s="18">
+        <v>54018.534116999996</v>
+      </c>
+      <c r="G40" s="219">
         <f t="shared" si="6"/>
-        <v>43818.18</v>
-      </c>
-      <c r="H40" s="46">
+        <v>54018.534116999996</v>
+      </c>
+      <c r="H40" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I40" s="32"/>
-      <c r="J40" s="19">
+      <c r="I40" s="31"/>
+      <c r="J40" s="18">
         <f t="shared" si="2"/>
         <v>10200.354116999997</v>
       </c>
-      <c r="K40" s="19">
+      <c r="K40" s="18">
         <f t="shared" si="3"/>
         <v>43818.18</v>
       </c>
-      <c r="L40" s="68"/>
-      <c r="M40" s="2">
+      <c r="L40" s="66"/>
+      <c r="M40" s="1">
         <f t="shared" si="4"/>
         <v>54018.534116999996</v>
       </c>
-      <c r="N40" s="5">
+      <c r="N40" s="4">
         <f t="shared" si="1"/>
         <v>57259.646164019992</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A41" s="44" t="s">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2">
         <v>12</v>
       </c>
-      <c r="D41" s="48" t="s">
+      <c r="D41" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41" s="2">
         <v>0.54</v>
       </c>
-      <c r="F41" s="19">
-        <v>41511.960000000006</v>
-      </c>
-      <c r="G41" s="154">
+      <c r="F41" s="18">
+        <v>51175.453374000004</v>
+      </c>
+      <c r="G41" s="219">
         <f t="shared" si="6"/>
-        <v>41511.960000000006</v>
-      </c>
-      <c r="H41" s="46">
+        <v>51175.453374000004</v>
+      </c>
+      <c r="H41" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I41" s="32"/>
-      <c r="J41" s="19">
+      <c r="I41" s="31"/>
+      <c r="J41" s="18">
         <f t="shared" si="2"/>
         <v>9663.4933739999979</v>
       </c>
-      <c r="K41" s="19">
+      <c r="K41" s="18">
         <f t="shared" si="3"/>
         <v>41511.960000000006</v>
       </c>
-      <c r="L41" s="68"/>
-      <c r="M41" s="2">
+      <c r="L41" s="66"/>
+      <c r="M41" s="1">
         <f t="shared" si="4"/>
         <v>51175.453374000004</v>
       </c>
-      <c r="N41" s="5">
+      <c r="N41" s="4">
         <f t="shared" si="1"/>
         <v>54245.980576440008</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A42" s="44" t="s">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3">
+      <c r="B42" s="2"/>
+      <c r="C42" s="2">
         <v>13</v>
       </c>
-      <c r="D42" s="48" t="s">
+      <c r="D42" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="2">
         <v>0.55000000000000004</v>
       </c>
-      <c r="F42" s="19">
-        <v>42280.7</v>
-      </c>
-      <c r="G42" s="154">
+      <c r="F42" s="18">
+        <v>52123.146954999997</v>
+      </c>
+      <c r="G42" s="219">
         <f>F42</f>
-        <v>42280.7</v>
-      </c>
-      <c r="H42" s="46">
+        <v>52123.146954999997</v>
+      </c>
+      <c r="H42" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I42" s="32"/>
-      <c r="J42" s="19">
+      <c r="I42" s="31"/>
+      <c r="J42" s="18">
         <f t="shared" si="2"/>
         <v>9842.4469549999994</v>
       </c>
-      <c r="K42" s="19">
+      <c r="K42" s="18">
         <f t="shared" si="3"/>
         <v>42280.7</v>
       </c>
-      <c r="L42" s="68"/>
-      <c r="M42" s="2">
+      <c r="L42" s="66"/>
+      <c r="M42" s="1">
         <f t="shared" si="4"/>
         <v>52123.146954999997</v>
       </c>
-      <c r="N42" s="5">
+      <c r="N42" s="4">
         <f t="shared" si="1"/>
         <v>55250.535772299998</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A43" s="44" t="s">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3">
+      <c r="B43" s="2"/>
+      <c r="C43" s="2">
         <v>14</v>
       </c>
-      <c r="D43" s="48" t="s">
+      <c r="D43" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="2">
         <v>0.45</v>
       </c>
-      <c r="F43" s="19">
-        <v>34593.300000000003</v>
-      </c>
-      <c r="G43" s="154">
+      <c r="F43" s="18">
+        <v>42646.211145000001</v>
+      </c>
+      <c r="G43" s="219">
         <f>F43</f>
-        <v>34593.300000000003</v>
-      </c>
-      <c r="H43" s="46">
+        <v>42646.211145000001</v>
+      </c>
+      <c r="H43" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I43" s="32"/>
-      <c r="J43" s="19">
+      <c r="I43" s="31"/>
+      <c r="J43" s="18">
         <f t="shared" si="2"/>
         <v>8052.9111449999991</v>
       </c>
-      <c r="K43" s="19">
+      <c r="K43" s="18">
         <f t="shared" si="3"/>
         <v>34593.300000000003</v>
       </c>
-      <c r="L43" s="68"/>
-      <c r="M43" s="2">
+      <c r="L43" s="66"/>
+      <c r="M43" s="1">
         <f t="shared" si="4"/>
         <v>42646.211145000001</v>
       </c>
-      <c r="N43" s="5">
+      <c r="N43" s="4">
         <f t="shared" si="1"/>
         <v>45204.983813700004</v>
       </c>
-      <c r="P43" s="34">
+      <c r="P43" s="33">
         <f>L1-K52</f>
-        <v>4606074.4000420021</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A44" s="44" t="s">
+        <v>4839794.9700420005</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3">
+      <c r="B44" s="2"/>
+      <c r="C44" s="2">
         <v>15</v>
       </c>
-      <c r="D44" s="48" t="s">
+      <c r="D44" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="2">
         <v>0.61</v>
       </c>
-      <c r="F44" s="19">
-        <v>46893.14</v>
-      </c>
-      <c r="G44" s="154">
+      <c r="F44" s="18">
+        <v>57809.308440999994</v>
+      </c>
+      <c r="G44" s="219">
         <f>F44</f>
-        <v>46893.14</v>
-      </c>
-      <c r="H44" s="46">
+        <v>57809.308440999994</v>
+      </c>
+      <c r="H44" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I44" s="32"/>
-      <c r="J44" s="19">
+      <c r="I44" s="31"/>
+      <c r="J44" s="18">
         <f t="shared" si="2"/>
         <v>10916.168440999996</v>
       </c>
-      <c r="K44" s="19">
+      <c r="K44" s="18">
         <f t="shared" si="3"/>
         <v>46893.14</v>
       </c>
-      <c r="L44" s="68"/>
-      <c r="M44" s="2">
+      <c r="L44" s="66"/>
+      <c r="M44" s="1">
         <f t="shared" si="4"/>
         <v>57809.308440999994</v>
       </c>
-      <c r="N44" s="5">
+      <c r="N44" s="4">
         <f t="shared" si="1"/>
         <v>61277.866947459996</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A45" s="44" t="s">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3">
+      <c r="B45" s="2"/>
+      <c r="C45" s="2">
         <v>16</v>
       </c>
-      <c r="D45" s="48" t="s">
+      <c r="D45" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="2">
         <v>0.54</v>
       </c>
-      <c r="F45" s="19">
-        <v>41511.960000000006</v>
-      </c>
-      <c r="G45" s="154">
+      <c r="F45" s="18">
+        <v>51175.453374000004</v>
+      </c>
+      <c r="G45" s="219">
         <f t="shared" ref="G45" si="7">F45</f>
-        <v>41511.960000000006</v>
-      </c>
-      <c r="H45" s="46">
+        <v>51175.453374000004</v>
+      </c>
+      <c r="H45" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I45" s="32"/>
-      <c r="J45" s="19">
+      <c r="I45" s="31"/>
+      <c r="J45" s="18">
         <f t="shared" si="2"/>
         <v>9663.4933739999979</v>
       </c>
-      <c r="K45" s="19">
+      <c r="K45" s="18">
         <f t="shared" si="3"/>
         <v>41511.960000000006</v>
       </c>
-      <c r="L45" s="68"/>
-      <c r="M45" s="2">
+      <c r="L45" s="66"/>
+      <c r="M45" s="1">
         <f t="shared" si="4"/>
         <v>51175.453374000004</v>
       </c>
-      <c r="N45" s="5">
+      <c r="N45" s="4">
         <f t="shared" si="1"/>
         <v>54245.980576440008</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A46" s="44" t="s">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3">
+      <c r="B46" s="2"/>
+      <c r="C46" s="2">
         <v>17</v>
       </c>
-      <c r="D46" s="48" t="s">
+      <c r="D46" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="2">
         <v>0.5</v>
       </c>
-      <c r="F46" s="19">
-        <v>38437</v>
-      </c>
-      <c r="G46" s="154">
+      <c r="F46" s="18">
+        <v>47384.679049999999</v>
+      </c>
+      <c r="G46" s="219">
         <f t="shared" ref="G46:G51" si="8">F46</f>
-        <v>38437</v>
-      </c>
-      <c r="H46" s="46">
+        <v>47384.679049999999</v>
+      </c>
+      <c r="H46" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I46" s="32"/>
-      <c r="J46" s="19">
+      <c r="I46" s="31"/>
+      <c r="J46" s="18">
         <f t="shared" si="2"/>
         <v>8947.6790499999988</v>
       </c>
-      <c r="K46" s="19">
+      <c r="K46" s="18">
         <f t="shared" si="3"/>
         <v>38437</v>
       </c>
-      <c r="L46" s="68"/>
-      <c r="M46" s="2">
+      <c r="L46" s="66"/>
+      <c r="M46" s="1">
         <f t="shared" si="4"/>
         <v>47384.679049999999</v>
       </c>
-      <c r="N46" s="5">
+      <c r="N46" s="4">
         <f t="shared" si="1"/>
         <v>50227.759792999997</v>
       </c>
@@ -5860,429 +5901,423 @@
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A47" s="44" t="s">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3">
+      <c r="B47" s="2"/>
+      <c r="C47" s="2">
         <v>18</v>
       </c>
-      <c r="D47" s="48" t="s">
+      <c r="D47" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="2">
         <v>0.5</v>
       </c>
-      <c r="F47" s="19">
-        <v>38437</v>
-      </c>
-      <c r="G47" s="154">
+      <c r="F47" s="18">
+        <v>47384.679049999999</v>
+      </c>
+      <c r="G47" s="219">
         <f t="shared" si="8"/>
-        <v>38437</v>
-      </c>
-      <c r="H47" s="46">
+        <v>47384.679049999999</v>
+      </c>
+      <c r="H47" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I47" s="32"/>
-      <c r="J47" s="19">
+      <c r="I47" s="31"/>
+      <c r="J47" s="18">
         <f t="shared" si="2"/>
         <v>8947.6790499999988</v>
       </c>
-      <c r="K47" s="19">
+      <c r="K47" s="18">
         <f t="shared" si="3"/>
         <v>38437</v>
       </c>
-      <c r="L47" s="68"/>
-      <c r="M47" s="2">
+      <c r="L47" s="66"/>
+      <c r="M47" s="1">
         <f t="shared" si="4"/>
         <v>47384.679049999999</v>
       </c>
-      <c r="N47" s="5">
+      <c r="N47" s="4">
         <f t="shared" si="1"/>
         <v>50227.759792999997</v>
       </c>
-      <c r="O47" s="53"/>
-      <c r="Q47" s="50">
+      <c r="O47" s="52"/>
+      <c r="Q47" s="49">
         <f>M3-J52</f>
-        <v>4934309.2570290007</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A48" s="44" t="s">
+        <v>-1644762.3629709994</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3">
+      <c r="B48" s="2"/>
+      <c r="C48" s="2">
         <v>19</v>
       </c>
-      <c r="D48" s="48" t="s">
+      <c r="D48" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="2">
         <v>0.49</v>
       </c>
-      <c r="F48" s="19">
-        <v>37668.26</v>
-      </c>
-      <c r="G48" s="154">
+      <c r="F48" s="18">
+        <v>46436.985468999999</v>
+      </c>
+      <c r="G48" s="148">
         <f t="shared" si="8"/>
-        <v>37668.26</v>
-      </c>
-      <c r="H48" s="46">
+        <v>46436.985468999999</v>
+      </c>
+      <c r="H48" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I48" s="32"/>
-      <c r="J48" s="19">
+      <c r="I48" s="31"/>
+      <c r="J48" s="18">
         <f t="shared" si="2"/>
         <v>8768.7254689999972</v>
       </c>
-      <c r="K48" s="19">
+      <c r="K48" s="18">
         <f t="shared" si="3"/>
         <v>37668.26</v>
       </c>
-      <c r="L48" s="68"/>
-      <c r="M48" s="2">
+      <c r="L48" s="66"/>
+      <c r="M48" s="1">
         <f t="shared" si="4"/>
         <v>46436.985468999999</v>
       </c>
-      <c r="N48" s="5">
+      <c r="N48" s="4">
         <f t="shared" si="1"/>
         <v>49223.20459714</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A49" s="44" t="s">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2">
         <v>20</v>
       </c>
-      <c r="D49" s="48" t="str">
+      <c r="D49" s="47" t="str">
         <f>D16</f>
         <v>FEUILLANT, GASTON</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="2">
         <v>0.49</v>
       </c>
-      <c r="F49" s="19">
-        <v>37668.26</v>
-      </c>
-      <c r="G49" s="154">
+      <c r="F49" s="18">
+        <v>46436.985468999999</v>
+      </c>
+      <c r="G49" s="219">
         <f t="shared" si="8"/>
-        <v>37668.26</v>
-      </c>
-      <c r="H49" s="46">
+        <v>46436.985468999999</v>
+      </c>
+      <c r="H49" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I49" s="32"/>
-      <c r="J49" s="19">
+      <c r="I49" s="31"/>
+      <c r="J49" s="18">
         <f t="shared" si="2"/>
         <v>8768.7254689999972</v>
       </c>
-      <c r="K49" s="19">
+      <c r="K49" s="18">
         <f t="shared" si="3"/>
         <v>37668.26</v>
       </c>
-      <c r="L49" s="68"/>
-      <c r="M49" s="2">
+      <c r="L49" s="66"/>
+      <c r="M49" s="1">
         <f t="shared" si="4"/>
         <v>46436.985468999999</v>
       </c>
-      <c r="N49" s="5">
+      <c r="N49" s="4">
         <f t="shared" si="1"/>
         <v>49223.20459714</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A50" s="44" t="s">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A50" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3">
+      <c r="B50" s="2"/>
+      <c r="C50" s="2">
         <v>21</v>
       </c>
-      <c r="D50" s="48" t="s">
+      <c r="D50" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50" s="2">
         <v>0.59</v>
       </c>
-      <c r="F50" s="19">
-        <v>45355.66</v>
-      </c>
-      <c r="G50" s="105">
+      <c r="F50" s="18">
+        <v>55913.921279000002</v>
+      </c>
+      <c r="G50" s="218">
         <f t="shared" si="8"/>
-        <v>45355.66</v>
-      </c>
-      <c r="H50" s="46">
+        <v>55913.921279000002</v>
+      </c>
+      <c r="H50" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I50" s="32"/>
-      <c r="J50" s="19">
+      <c r="I50" s="31"/>
+      <c r="J50" s="18">
         <f t="shared" si="2"/>
         <v>10558.261278999997</v>
       </c>
-      <c r="K50" s="19">
+      <c r="K50" s="18">
         <f t="shared" si="3"/>
         <v>45355.66</v>
       </c>
-      <c r="L50" s="68"/>
-      <c r="M50" s="2">
+      <c r="L50" s="66"/>
+      <c r="M50" s="1">
         <f t="shared" si="4"/>
         <v>55913.921279000002</v>
       </c>
-      <c r="N50" s="5">
+      <c r="N50" s="4">
         <f t="shared" si="1"/>
         <v>59268.756555740001</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A51" s="44" t="s">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3">
+      <c r="B51" s="2"/>
+      <c r="C51" s="2">
         <v>22</v>
       </c>
-      <c r="D51" s="48" t="s">
+      <c r="D51" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="2">
         <v>0.56999999999999995</v>
       </c>
-      <c r="F51" s="19">
-        <v>43818.18</v>
-      </c>
-      <c r="G51" s="154">
+      <c r="F51" s="18">
+        <v>54018.534116999996</v>
+      </c>
+      <c r="G51" s="219">
         <f t="shared" si="8"/>
-        <v>43818.18</v>
-      </c>
-      <c r="H51" s="46">
+        <v>54018.534116999996</v>
+      </c>
+      <c r="H51" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I51" s="32"/>
-      <c r="J51" s="19">
+      <c r="I51" s="31"/>
+      <c r="J51" s="18">
         <f t="shared" si="2"/>
         <v>10200.354116999997</v>
       </c>
-      <c r="K51" s="19">
+      <c r="K51" s="18">
         <f t="shared" si="3"/>
         <v>43818.18</v>
       </c>
-      <c r="L51" s="68"/>
-      <c r="M51" s="2">
+      <c r="L51" s="66"/>
+      <c r="M51" s="1">
         <f t="shared" si="4"/>
         <v>54018.534116999996</v>
       </c>
-      <c r="N51" s="5">
+      <c r="N51" s="4">
         <f t="shared" si="1"/>
         <v>57259.646164019992</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="20"/>
-      <c r="B52" s="20"/>
-      <c r="C52" s="20"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20">
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="19"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19">
         <f>SUM(E7:E51)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F52" s="85">
+      <c r="F52" s="83">
         <f>SUM(F7:F51)</f>
-        <v>5977040.1903867004</v>
-      </c>
-      <c r="G52" s="85">
+        <v>6503517.6367330411</v>
+      </c>
+      <c r="G52" s="83">
         <f>SUM(G7:G51)</f>
-        <v>8666282.7266246639</v>
-      </c>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="45">
+        <v>8264798.2205740046</v>
+      </c>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="44">
         <f>SUM(J8:J51)</f>
         <v>1644762.3629709994</v>
       </c>
-      <c r="K52" s="21">
+      <c r="K52" s="20">
         <f>SUM(K7:K51)</f>
         <v>7375912.5599579988</v>
       </c>
-      <c r="L52" s="87">
+      <c r="L52" s="85">
         <f>SUM(L7:L51)</f>
         <v>0</v>
       </c>
-      <c r="M52" s="22">
+      <c r="M52" s="21">
         <f>SUM(M7:M51)</f>
-        <v>6476205.8337200405</v>
-      </c>
-      <c r="N52" s="21">
+        <v>7404167.7861170406</v>
+      </c>
+      <c r="N52" s="20">
         <f>SUM(N7:N51)</f>
-        <v>6864778.1837432366</v>
-      </c>
-      <c r="P52" s="50"/>
-    </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="K53" s="53">
+        <v>7848417.8532840572</v>
+      </c>
+      <c r="P52" s="49"/>
+    </row>
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K53" s="52">
         <f>K52-L1</f>
-        <v>-4606074.4000420021</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C54" s="193"/>
-      <c r="D54" s="193"/>
-      <c r="E54" s="193"/>
-      <c r="F54" s="193"/>
-      <c r="G54" s="193"/>
-      <c r="H54" s="193"/>
-      <c r="I54" s="193"/>
-      <c r="J54" s="193"/>
-      <c r="K54" s="193"/>
-      <c r="L54" s="193"/>
-      <c r="M54" s="193"/>
-      <c r="N54" s="193"/>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C55" s="193"/>
-      <c r="D55" s="193"/>
-      <c r="E55" s="193"/>
-      <c r="F55" s="193"/>
-      <c r="G55" s="193"/>
-      <c r="H55" s="193"/>
-      <c r="I55" s="193"/>
-      <c r="J55" s="193"/>
-      <c r="K55" s="193"/>
-      <c r="L55" s="193"/>
-      <c r="M55" s="193"/>
-      <c r="N55" s="193"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C56" s="70"/>
-      <c r="D56" s="70"/>
-      <c r="E56" s="70"/>
-      <c r="F56" s="70"/>
-      <c r="G56" s="70"/>
-      <c r="H56" s="70"/>
-      <c r="I56" s="70"/>
-      <c r="J56" s="70"/>
-      <c r="K56" s="70"/>
-      <c r="L56" s="70"/>
-      <c r="M56" s="70"/>
-      <c r="N56" s="70"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C57" s="193" t="s">
+        <v>-4839794.9700420005</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="189"/>
+      <c r="D54" s="189"/>
+      <c r="E54" s="189"/>
+      <c r="F54" s="189"/>
+      <c r="G54" s="189"/>
+      <c r="H54" s="189"/>
+      <c r="I54" s="189"/>
+      <c r="J54" s="189"/>
+      <c r="K54" s="189"/>
+      <c r="L54" s="189"/>
+      <c r="M54" s="189"/>
+      <c r="N54" s="189"/>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="189"/>
+      <c r="D55" s="189"/>
+      <c r="E55" s="189"/>
+      <c r="F55" s="189"/>
+      <c r="G55" s="189"/>
+      <c r="H55" s="189"/>
+      <c r="I55" s="189"/>
+      <c r="J55" s="189"/>
+      <c r="K55" s="189"/>
+      <c r="L55" s="189"/>
+      <c r="M55" s="189"/>
+      <c r="N55" s="189"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C56" s="68"/>
+      <c r="D56" s="68"/>
+      <c r="E56" s="68"/>
+      <c r="F56" s="68"/>
+      <c r="G56" s="68"/>
+      <c r="H56" s="68"/>
+      <c r="I56" s="68"/>
+      <c r="J56" s="68"/>
+      <c r="K56" s="68"/>
+      <c r="L56" s="68"/>
+      <c r="M56" s="68"/>
+      <c r="N56" s="68"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C57" s="189" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="193"/>
-      <c r="E57" s="193"/>
-      <c r="F57" s="193"/>
-      <c r="G57" s="193"/>
-      <c r="H57" s="193"/>
-      <c r="I57" s="193"/>
-      <c r="J57" s="193"/>
-      <c r="K57" s="193"/>
-      <c r="L57" s="193"/>
-      <c r="M57" s="193"/>
-      <c r="N57" s="193"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C58" s="193"/>
-      <c r="D58" s="193"/>
-      <c r="E58" s="193"/>
-      <c r="F58" s="193"/>
-      <c r="G58" s="193"/>
-      <c r="H58" s="193"/>
-      <c r="I58" s="193"/>
-      <c r="J58" s="193"/>
-      <c r="K58" s="193"/>
-      <c r="L58" s="193"/>
-      <c r="M58" s="193"/>
-      <c r="N58" s="193"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C59" s="193"/>
-      <c r="D59" s="193"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
-      <c r="G59" s="193"/>
-      <c r="H59" s="193"/>
-      <c r="I59" s="193"/>
-      <c r="J59" s="193"/>
-      <c r="K59" s="193"/>
-      <c r="L59" s="193"/>
-      <c r="M59" s="193"/>
-      <c r="N59" s="193"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C60" s="193"/>
-      <c r="D60" s="193"/>
-      <c r="E60" s="193"/>
-      <c r="F60" s="193"/>
-      <c r="G60" s="193"/>
-      <c r="H60" s="193"/>
-      <c r="I60" s="193"/>
-      <c r="J60" s="193"/>
-      <c r="K60" s="193"/>
-      <c r="L60" s="193"/>
-      <c r="M60" s="193"/>
-      <c r="N60" s="193"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C61" s="193"/>
-      <c r="D61" s="193"/>
-      <c r="E61" s="193"/>
-      <c r="F61" s="193"/>
-      <c r="G61" s="193"/>
-      <c r="H61" s="193"/>
-      <c r="I61" s="193"/>
-      <c r="J61" s="193"/>
-      <c r="K61" s="193"/>
-      <c r="L61" s="193"/>
-      <c r="M61" s="193"/>
-      <c r="N61" s="193"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C62" s="193"/>
-      <c r="D62" s="193"/>
-      <c r="E62" s="193"/>
-      <c r="F62" s="193"/>
-      <c r="G62" s="193"/>
-      <c r="H62" s="193"/>
-      <c r="I62" s="193"/>
-      <c r="J62" s="193"/>
-      <c r="K62" s="193"/>
-      <c r="L62" s="193"/>
-      <c r="M62" s="193"/>
-      <c r="N62" s="193"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C63" s="193"/>
-      <c r="D63" s="193"/>
-      <c r="E63" s="193"/>
-      <c r="F63" s="193"/>
-      <c r="G63" s="193"/>
-      <c r="H63" s="193"/>
-      <c r="I63" s="193"/>
-      <c r="J63" s="193"/>
-      <c r="K63" s="193"/>
-      <c r="L63" s="193"/>
-      <c r="M63" s="193"/>
-      <c r="N63" s="193"/>
+      <c r="D57" s="189"/>
+      <c r="E57" s="189"/>
+      <c r="F57" s="189"/>
+      <c r="G57" s="189"/>
+      <c r="H57" s="189"/>
+      <c r="I57" s="189"/>
+      <c r="J57" s="189"/>
+      <c r="K57" s="189"/>
+      <c r="L57" s="189"/>
+      <c r="M57" s="189"/>
+      <c r="N57" s="189"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C58" s="189"/>
+      <c r="D58" s="189"/>
+      <c r="E58" s="189"/>
+      <c r="F58" s="189"/>
+      <c r="G58" s="189"/>
+      <c r="H58" s="189"/>
+      <c r="I58" s="189"/>
+      <c r="J58" s="189"/>
+      <c r="K58" s="189"/>
+      <c r="L58" s="189"/>
+      <c r="M58" s="189"/>
+      <c r="N58" s="189"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C59" s="189"/>
+      <c r="D59" s="189"/>
+      <c r="E59" s="189"/>
+      <c r="F59" s="189"/>
+      <c r="G59" s="189"/>
+      <c r="H59" s="189"/>
+      <c r="I59" s="189"/>
+      <c r="J59" s="189"/>
+      <c r="K59" s="189"/>
+      <c r="L59" s="189"/>
+      <c r="M59" s="189"/>
+      <c r="N59" s="189"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C60" s="189"/>
+      <c r="D60" s="189"/>
+      <c r="E60" s="189"/>
+      <c r="F60" s="189"/>
+      <c r="G60" s="189"/>
+      <c r="H60" s="189"/>
+      <c r="I60" s="189"/>
+      <c r="J60" s="189"/>
+      <c r="K60" s="189"/>
+      <c r="L60" s="189"/>
+      <c r="M60" s="189"/>
+      <c r="N60" s="189"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C61" s="189"/>
+      <c r="D61" s="189"/>
+      <c r="E61" s="189"/>
+      <c r="F61" s="189"/>
+      <c r="G61" s="189"/>
+      <c r="H61" s="189"/>
+      <c r="I61" s="189"/>
+      <c r="J61" s="189"/>
+      <c r="K61" s="189"/>
+      <c r="L61" s="189"/>
+      <c r="M61" s="189"/>
+      <c r="N61" s="189"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C62" s="189"/>
+      <c r="D62" s="189"/>
+      <c r="E62" s="189"/>
+      <c r="F62" s="189"/>
+      <c r="G62" s="189"/>
+      <c r="H62" s="189"/>
+      <c r="I62" s="189"/>
+      <c r="J62" s="189"/>
+      <c r="K62" s="189"/>
+      <c r="L62" s="189"/>
+      <c r="M62" s="189"/>
+      <c r="N62" s="189"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C63" s="189"/>
+      <c r="D63" s="189"/>
+      <c r="E63" s="189"/>
+      <c r="F63" s="189"/>
+      <c r="G63" s="189"/>
+      <c r="H63" s="189"/>
+      <c r="I63" s="189"/>
+      <c r="J63" s="189"/>
+      <c r="K63" s="189"/>
+      <c r="L63" s="189"/>
+      <c r="M63" s="189"/>
+      <c r="N63" s="189"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="C57:N63"/>
-    <mergeCell ref="C54:N55"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="G5:G6"/>
@@ -6295,6 +6330,12 @@
     <mergeCell ref="A1:J4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="C57:N63"/>
+    <mergeCell ref="C54:N55"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6304,9 +6345,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2666E70F-CDC7-456F-AF96-2906778A9145}">
   <dimension ref="C4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>119</v>
       </c>

--- a/2026/BELGRANO 1646/Julio/Julio-BLG1646.xlsx
+++ b/2026/BELGRANO 1646/Julio/Julio-BLG1646.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF79FA4F-F6DF-4F79-B6AB-B7E927FC5007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E0C408-32E3-4F92-A162-43C0DB952AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$130</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$129</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="146">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -434,9 +434,6 @@
     <t xml:space="preserve">Articulos de limpieza </t>
   </si>
   <si>
-    <t>Cerrajeria - Servicio de cerrajeria sobre control de acceso</t>
-  </si>
-  <si>
     <t>Entendiendo que en su momento, se le habia cobrado al Sr. Simonassi $3.000.000, la diferencia entre lo gastado ($6.579.071,62) y el monto mencionado se prorrateara como extraordinario en los proximos dos meses ($1.789.535)</t>
   </si>
   <si>
@@ -470,9 +467,6 @@
     <t>Mediacion Sr. Simonassi</t>
   </si>
   <si>
-    <t>Doartero julio - Rreparacion techo de baño - Mano de obra y materiales</t>
-  </si>
-  <si>
     <t>Contessi - Provision y colocacion de 40 litros de aceite hidraulico a la central del montaautos</t>
   </si>
   <si>
@@ -497,10 +491,16 @@
     <t>Gastañaga Sebastian - Desinstalacion e instalacion del paño metalico con soldaduras laterales - Sustitucion de 6 barillas metalicas galvaizadas microperforadas - Cambio de flejes y renovacion de paños</t>
   </si>
   <si>
-    <t xml:space="preserve">Casa Ruan - compra de materiales electricos   </t>
-  </si>
-  <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Servisur - Colocacion 2 plafones 12W en escaleras</t>
+  </si>
+  <si>
+    <t>Casa Ruan - compra de luces 12w plafones y pilas</t>
+  </si>
+  <si>
+    <t>Doartero julio - Reparacion techo de baño - Mano de obra y materiales</t>
   </si>
 </sst>
 </file>
@@ -692,7 +692,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -744,12 +744,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1096,7 +1090,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="223">
+  <cellXfs count="219">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1388,108 +1382,104 @@
     <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="10" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1891,7 +1881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N140"/>
+  <dimension ref="A1:N139"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.42578125" customWidth="1"/>
@@ -1953,10 +1943,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="104" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" s="104" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D5" s="104"/>
       <c r="E5" s="104"/>
@@ -2081,7 +2071,7 @@
         <v>107</v>
       </c>
       <c r="B22" s="77" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C22" s="77"/>
       <c r="D22" s="146"/>
@@ -2094,7 +2084,7 @@
       </c>
       <c r="B23" s="77"/>
       <c r="C23" s="77"/>
-      <c r="D23" s="213">
+      <c r="D23" s="100">
         <v>1721576.91</v>
       </c>
       <c r="E23" s="48">
@@ -2112,7 +2102,7 @@
       </c>
       <c r="B24" s="77"/>
       <c r="C24" s="77"/>
-      <c r="D24" s="213">
+      <c r="D24" s="100">
         <v>-374442.91</v>
       </c>
       <c r="E24" s="48">
@@ -2376,11 +2366,11 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="77" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B41" s="77"/>
       <c r="C41" s="99"/>
-      <c r="D41" s="209">
+      <c r="D41" s="36">
         <v>68000</v>
       </c>
       <c r="E41" s="48">
@@ -2392,11 +2382,11 @@
     </row>
     <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="77" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B42" s="77"/>
       <c r="C42" s="99"/>
-      <c r="D42" s="213">
+      <c r="D42" s="100">
         <v>5837.2</v>
       </c>
       <c r="E42" s="48">
@@ -2441,13 +2431,13 @@
       <c r="F44" s="25"/>
       <c r="H44" s="59"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="117" t="s">
         <v>110</v>
       </c>
       <c r="B45" s="77"/>
       <c r="C45" s="99"/>
-      <c r="D45" s="209">
+      <c r="D45" s="36">
         <v>6642</v>
       </c>
       <c r="E45" s="48">
@@ -2460,13 +2450,13 @@
       </c>
       <c r="H45" s="59"/>
     </row>
-    <row r="46" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="210" t="s">
-        <v>140</v>
-      </c>
-      <c r="B46" s="211"/>
-      <c r="C46" s="212"/>
-      <c r="D46" s="209">
+    <row r="46" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="214" t="s">
+        <v>138</v>
+      </c>
+      <c r="B46" s="215"/>
+      <c r="C46" s="216"/>
+      <c r="D46" s="36">
         <f>1774.18+778867.29</f>
         <v>780641.47000000009</v>
       </c>
@@ -2480,13 +2470,13 @@
       </c>
       <c r="H46" s="59"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="117" t="s">
         <v>5</v>
       </c>
       <c r="B47" s="77"/>
       <c r="C47" s="77"/>
-      <c r="D47" s="209">
+      <c r="D47" s="36">
         <f>13204.01+244288.08+118836.05</f>
         <v>376328.14</v>
       </c>
@@ -2506,7 +2496,7 @@
       </c>
       <c r="B48" s="99"/>
       <c r="C48" s="77"/>
-      <c r="D48" s="209">
+      <c r="D48" s="36">
         <v>1170944.31</v>
       </c>
       <c r="E48" s="48">
@@ -2552,7 +2542,7 @@
       </c>
       <c r="B50" s="77"/>
       <c r="C50" s="77"/>
-      <c r="D50" s="102"/>
+      <c r="D50" s="36"/>
       <c r="E50" s="38"/>
       <c r="F50" s="2"/>
       <c r="H50" s="59"/>
@@ -2563,7 +2553,7 @@
       </c>
       <c r="B51" s="77"/>
       <c r="C51" s="77"/>
-      <c r="D51" s="209">
+      <c r="D51" s="36">
         <v>520800</v>
       </c>
       <c r="E51" s="58">
@@ -2587,11 +2577,11 @@
     </row>
     <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="147" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B52" s="77"/>
       <c r="C52" s="77"/>
-      <c r="D52" s="209">
+      <c r="D52" s="36">
         <v>780000</v>
       </c>
       <c r="E52" s="58">
@@ -2610,143 +2600,150 @@
       </c>
       <c r="B53" s="124"/>
       <c r="C53" s="77"/>
-      <c r="D53" s="209">
+      <c r="D53" s="36">
         <v>266112.3</v>
       </c>
       <c r="E53" s="58">
-        <f t="shared" ref="E53:E58" si="7">D53*91.91%</f>
+        <f t="shared" ref="E53:E57" si="7">D53*91.91%</f>
         <v>244583.81492999996</v>
       </c>
       <c r="F53" s="48">
-        <f t="shared" ref="F53:F58" si="8">D53*8.09%</f>
+        <f t="shared" ref="F53:F57" si="8">D53*8.09%</f>
         <v>21528.485069999999</v>
       </c>
       <c r="G53" s="33">
-        <f t="shared" ref="G53:G55" si="9">D53</f>
+        <f t="shared" ref="G53:G54" si="9">D53</f>
         <v>266112.3</v>
       </c>
       <c r="H53" s="65">
-        <f t="shared" ref="H53:H55" si="10">E53+F53</f>
+        <f t="shared" ref="H53:H54" si="10">E53+F53</f>
         <v>266112.3</v>
       </c>
       <c r="I53" s="74"/>
       <c r="J53" s="74"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="77" t="s">
-        <v>123</v>
+      <c r="A54" s="117" t="s">
+        <v>135</v>
       </c>
       <c r="B54" s="77"/>
       <c r="C54" s="77"/>
       <c r="D54" s="36">
-        <v>45000</v>
+        <v>192118.26</v>
       </c>
       <c r="E54" s="58">
-        <f>D54</f>
-        <v>45000</v>
+        <f t="shared" ref="E54" si="11">D54*91.91%</f>
+        <v>176575.892766</v>
       </c>
       <c r="F54" s="48">
-        <v>0</v>
+        <f t="shared" ref="F54" si="12">D54*8.09%</f>
+        <v>15542.367234000001</v>
       </c>
       <c r="G54" s="33">
         <f t="shared" si="9"/>
-        <v>45000</v>
+        <v>192118.26</v>
       </c>
       <c r="H54" s="65">
         <f t="shared" si="10"/>
-        <v>45000</v>
+        <v>192118.26</v>
       </c>
       <c r="I54" s="74"/>
       <c r="J54" s="74"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="117" t="s">
-        <v>137</v>
-      </c>
-      <c r="B55" s="77"/>
+        <v>9</v>
+      </c>
+      <c r="B55" s="77" t="s">
+        <v>109</v>
+      </c>
       <c r="C55" s="77"/>
-      <c r="D55" s="209">
-        <v>192118.26</v>
+      <c r="D55" s="36">
+        <v>173191</v>
       </c>
       <c r="E55" s="58">
-        <f t="shared" ref="E55" si="11">D55*91.91%</f>
-        <v>176575.892766</v>
+        <f>D55*91.91%</f>
+        <v>159179.84809999997</v>
       </c>
       <c r="F55" s="48">
-        <f t="shared" ref="F55" si="12">D55*8.09%</f>
-        <v>15542.367234000001</v>
+        <f t="shared" si="8"/>
+        <v>14011.151900000001</v>
       </c>
       <c r="G55" s="33">
-        <f t="shared" si="9"/>
-        <v>192118.26</v>
+        <f t="shared" ref="G55:G67" si="13">D55</f>
+        <v>173191</v>
       </c>
       <c r="H55" s="65">
-        <f t="shared" si="10"/>
-        <v>192118.26</v>
-      </c>
-      <c r="I55" s="74"/>
-      <c r="J55" s="74"/>
+        <f>E55+F55</f>
+        <v>173190.99999999997</v>
+      </c>
+      <c r="I55" s="74">
+        <f t="shared" ref="I55:I67" si="14">H55-D55</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="74">
+        <f t="shared" ref="J55:J67" si="15">G55-D55</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="117" t="s">
-        <v>9</v>
-      </c>
-      <c r="B56" s="77" t="s">
-        <v>109</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B56" s="99"/>
       <c r="C56" s="77"/>
-      <c r="D56" s="209">
-        <v>173191</v>
+      <c r="D56" s="36">
+        <v>515749.85</v>
       </c>
       <c r="E56" s="58">
-        <f>D56*91.91%</f>
-        <v>159179.84809999997</v>
+        <f t="shared" si="7"/>
+        <v>474025.68713499996</v>
       </c>
       <c r="F56" s="48">
         <f t="shared" si="8"/>
-        <v>14011.151900000001</v>
+        <v>41724.162864999998</v>
       </c>
       <c r="G56" s="33">
-        <f t="shared" ref="G56:G67" si="13">D56</f>
-        <v>173191</v>
+        <f t="shared" si="13"/>
+        <v>515749.85</v>
       </c>
       <c r="H56" s="65">
-        <f>E56+F56</f>
-        <v>173190.99999999997</v>
+        <f t="shared" ref="H56:H67" si="16">E56+F56</f>
+        <v>515749.85</v>
       </c>
       <c r="I56" s="74">
-        <f t="shared" ref="I56:I67" si="14">H56-D56</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="J56" s="74">
-        <f t="shared" ref="J56:J67" si="15">G56-D56</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="117" t="s">
-        <v>11</v>
+      <c r="A57" s="118" t="s">
+        <v>10</v>
       </c>
       <c r="B57" s="99"/>
-      <c r="C57" s="77"/>
-      <c r="D57" s="209">
-        <v>515749.85</v>
+      <c r="C57" s="99"/>
+      <c r="D57" s="36">
+        <v>1516824.98</v>
       </c>
       <c r="E57" s="58">
         <f t="shared" si="7"/>
-        <v>474025.68713499996</v>
+        <v>1394113.8391179999</v>
       </c>
       <c r="F57" s="48">
         <f t="shared" si="8"/>
-        <v>41724.162864999998</v>
+        <v>122711.14088199999</v>
       </c>
       <c r="G57" s="33">
         <f t="shared" si="13"/>
-        <v>515749.85</v>
+        <v>1516824.98</v>
       </c>
       <c r="H57" s="65">
-        <f t="shared" ref="H57:H67" si="16">E57+F57</f>
-        <v>515749.85</v>
+        <f t="shared" si="16"/>
+        <v>1516824.98</v>
       </c>
       <c r="I57" s="74">
         <f t="shared" si="14"/>
@@ -2758,157 +2755,154 @@
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="118" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58" s="99"/>
-      <c r="C58" s="99"/>
-      <c r="D58" s="209">
-        <v>1516824.98</v>
+      <c r="A58" s="125" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" s="137"/>
+      <c r="C58" s="138"/>
+      <c r="D58" s="36">
+        <v>64500</v>
       </c>
       <c r="E58" s="58">
-        <f t="shared" si="7"/>
-        <v>1394113.8391179999</v>
-      </c>
-      <c r="F58" s="48">
-        <f t="shared" si="8"/>
-        <v>122711.14088199999</v>
-      </c>
+        <f t="shared" ref="E58:E59" si="17">D58</f>
+        <v>64500</v>
+      </c>
+      <c r="F58" s="48"/>
       <c r="G58" s="33">
         <f t="shared" si="13"/>
-        <v>1516824.98</v>
+        <v>64500</v>
       </c>
       <c r="H58" s="65">
         <f t="shared" si="16"/>
-        <v>1516824.98</v>
-      </c>
-      <c r="I58" s="74">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
+        <v>64500</v>
+      </c>
+      <c r="I58" s="74"/>
       <c r="J58" s="74">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="125" t="s">
-        <v>128</v>
+      <c r="A59" s="147" t="s">
+        <v>120</v>
       </c>
       <c r="B59" s="137"/>
       <c r="C59" s="138"/>
       <c r="D59" s="36">
-        <v>63300</v>
+        <v>0</v>
       </c>
       <c r="E59" s="58">
-        <f t="shared" ref="E59:E60" si="17">D59</f>
-        <v>63300</v>
+        <f t="shared" si="17"/>
+        <v>0</v>
       </c>
       <c r="F59" s="48"/>
       <c r="G59" s="33">
         <f t="shared" si="13"/>
-        <v>63300</v>
+        <v>0</v>
       </c>
       <c r="H59" s="65">
         <f t="shared" si="16"/>
-        <v>63300</v>
+        <v>0</v>
       </c>
       <c r="I59" s="74"/>
-      <c r="J59" s="74">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="147" t="s">
-        <v>120</v>
-      </c>
-      <c r="B60" s="137"/>
-      <c r="C60" s="138"/>
+      <c r="J59" s="74"/>
+    </row>
+    <row r="60" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="153" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" s="154"/>
+      <c r="C60" s="155"/>
       <c r="D60" s="36">
-        <v>237000</v>
+        <v>59169</v>
       </c>
       <c r="E60" s="58">
-        <f t="shared" si="17"/>
-        <v>237000</v>
+        <f>D60</f>
+        <v>59169</v>
       </c>
       <c r="F60" s="48"/>
       <c r="G60" s="33">
         <f t="shared" si="13"/>
-        <v>237000</v>
-      </c>
-      <c r="H60" s="65">
-        <f t="shared" si="16"/>
-        <v>237000</v>
-      </c>
+        <v>59169</v>
+      </c>
+      <c r="H60" s="65"/>
       <c r="I60" s="74"/>
       <c r="J60" s="74"/>
     </row>
     <row r="61" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="153" t="s">
-        <v>132</v>
-      </c>
-      <c r="B61" s="154"/>
-      <c r="C61" s="155"/>
-      <c r="D61" s="209">
-        <v>59169</v>
+      <c r="A61" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="B61" s="182"/>
+      <c r="C61" s="183"/>
+      <c r="D61" s="36">
+        <v>1150000</v>
       </c>
       <c r="E61" s="58">
         <f>D61</f>
-        <v>59169</v>
+        <v>1150000</v>
       </c>
       <c r="F61" s="48"/>
       <c r="G61" s="33">
         <f t="shared" si="13"/>
-        <v>59169</v>
+        <v>1150000</v>
       </c>
       <c r="H61" s="65"/>
       <c r="I61" s="74"/>
       <c r="J61" s="74"/>
     </row>
-    <row r="62" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="181" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B62" s="182"/>
       <c r="C62" s="183"/>
-      <c r="D62" s="209">
-        <v>1150000</v>
+      <c r="D62" s="36">
+        <v>650000</v>
       </c>
       <c r="E62" s="58">
-        <f>D62</f>
-        <v>1150000</v>
+        <f t="shared" ref="E62:E63" si="18">D62</f>
+        <v>650000</v>
       </c>
       <c r="F62" s="48"/>
       <c r="G62" s="33">
         <f t="shared" si="13"/>
-        <v>1150000</v>
-      </c>
-      <c r="H62" s="65"/>
+        <v>650000</v>
+      </c>
+      <c r="H62" s="65">
+        <f t="shared" si="16"/>
+        <v>650000</v>
+      </c>
       <c r="I62" s="74"/>
-      <c r="J62" s="74"/>
-    </row>
-    <row r="63" spans="1:10" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="181" t="s">
-        <v>143</v>
-      </c>
-      <c r="B63" s="182"/>
-      <c r="C63" s="183"/>
-      <c r="D63" s="209">
-        <v>650000</v>
+      <c r="J62" s="74">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="153" t="s">
+        <v>145</v>
+      </c>
+      <c r="B63" s="154"/>
+      <c r="C63" s="155"/>
+      <c r="D63" s="36">
+        <v>110000</v>
       </c>
       <c r="E63" s="58">
-        <f t="shared" ref="E63:E64" si="18">D63</f>
-        <v>650000</v>
-      </c>
-      <c r="F63" s="48"/>
+        <f t="shared" ref="E63" si="19">D63*91.91%</f>
+        <v>101100.99999999999</v>
+      </c>
+      <c r="F63" s="48">
+        <f t="shared" ref="F63" si="20">D63*8.09%</f>
+        <v>8899</v>
+      </c>
       <c r="G63" s="33">
         <f t="shared" si="13"/>
-        <v>650000</v>
+        <v>110000</v>
       </c>
       <c r="H63" s="65">
         <f t="shared" si="16"/>
-        <v>650000</v>
+        <v>109999.99999999999</v>
       </c>
       <c r="I63" s="74"/>
       <c r="J63" s="74">
@@ -2916,84 +2910,78 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="153" t="s">
-        <v>135</v>
-      </c>
-      <c r="B64" s="154"/>
-      <c r="C64" s="155"/>
-      <c r="D64" s="209">
-        <v>110000</v>
+    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="77" t="s">
+        <v>90</v>
+      </c>
+      <c r="B64" s="122" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64" s="135"/>
+      <c r="D64" s="36">
+        <v>105359.51</v>
       </c>
       <c r="E64" s="58">
-        <f t="shared" si="18"/>
-        <v>110000</v>
+        <f t="shared" ref="E64:E67" si="21">D64</f>
+        <v>105359.51</v>
       </c>
       <c r="F64" s="48"/>
       <c r="G64" s="33">
         <f t="shared" si="13"/>
-        <v>110000</v>
+        <v>105359.51</v>
       </c>
       <c r="H64" s="65">
         <f t="shared" si="16"/>
-        <v>110000</v>
-      </c>
-      <c r="I64" s="74"/>
+        <v>105359.51</v>
+      </c>
+      <c r="I64" s="74">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="J64" s="74">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="77" t="s">
-        <v>90</v>
-      </c>
-      <c r="B65" s="122" t="s">
-        <v>129</v>
-      </c>
+      <c r="A65" s="209" t="s">
+        <v>143</v>
+      </c>
+      <c r="B65" s="122"/>
       <c r="C65" s="135"/>
       <c r="D65" s="36">
-        <v>103395</v>
+        <v>40000</v>
       </c>
       <c r="E65" s="58">
-        <f t="shared" ref="E65:E67" si="19">D65</f>
-        <v>103395</v>
+        <f t="shared" si="21"/>
+        <v>40000</v>
       </c>
       <c r="F65" s="48"/>
       <c r="G65" s="33">
         <f t="shared" si="13"/>
-        <v>103395</v>
-      </c>
-      <c r="H65" s="65">
-        <f t="shared" si="16"/>
-        <v>103395</v>
-      </c>
-      <c r="I65" s="74">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="J65" s="74">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
+        <v>40000</v>
+      </c>
+      <c r="H65" s="65"/>
+      <c r="I65" s="74"/>
+      <c r="J65" s="74"/>
     </row>
     <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="220" t="s">
+      <c r="A66" s="209" t="s">
         <v>144</v>
       </c>
       <c r="B66" s="122"/>
       <c r="C66" s="135"/>
-      <c r="D66" s="209">
-        <v>49600</v>
+      <c r="D66" s="36">
+        <v>9600</v>
       </c>
       <c r="E66" s="58">
-        <f t="shared" si="19"/>
-        <v>49600</v>
+        <f t="shared" si="21"/>
+        <v>9600</v>
       </c>
       <c r="F66" s="48"/>
       <c r="G66" s="33">
         <f t="shared" si="13"/>
-        <v>49600</v>
+        <v>9600</v>
       </c>
       <c r="H66" s="65"/>
       <c r="I66" s="74"/>
@@ -3001,15 +2989,15 @@
     </row>
     <row r="67" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="180" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B67" s="154"/>
       <c r="C67" s="155"/>
-      <c r="D67" s="209">
+      <c r="D67" s="36">
         <v>938000</v>
       </c>
       <c r="E67" s="58">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>938000</v>
       </c>
       <c r="F67" s="48"/>
@@ -3038,19 +3026,19 @@
       <c r="C68" s="120"/>
       <c r="D68" s="32">
         <f>SUM(D51:D67)</f>
-        <v>7370260.3900000006</v>
+        <v>7091424.9000000004</v>
       </c>
       <c r="E68" s="32">
         <f>SUM(E51:E67)</f>
-        <v>7154743.0820490001</v>
+        <v>6867008.5920489999</v>
       </c>
       <c r="F68" s="32">
         <f>SUM(F51:F67)</f>
-        <v>215517.307951</v>
+        <v>224416.307951</v>
       </c>
       <c r="G68" s="33">
         <f>E68+F68</f>
-        <v>7370260.3899999997</v>
+        <v>7091424.8999999994</v>
       </c>
       <c r="H68" s="59" t="str">
         <f>IF(D68=G68, "", "Error")</f>
@@ -3094,98 +3082,85 @@
       </c>
       <c r="B72" s="99"/>
       <c r="C72" s="77"/>
-      <c r="D72" s="36">
-        <v>139000</v>
-      </c>
+      <c r="D72" s="36"/>
       <c r="E72" s="58">
         <f>D72*91.91%</f>
-        <v>127754.9</v>
+        <v>0</v>
       </c>
       <c r="F72" s="48">
         <f>D72*8.09%</f>
-        <v>11245.1</v>
+        <v>0</v>
       </c>
       <c r="G72" s="64"/>
       <c r="H72" s="59"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="118" t="s">
-        <v>122</v>
+      <c r="A73" s="99" t="s">
+        <v>121</v>
       </c>
       <c r="B73" s="136"/>
       <c r="C73" s="123"/>
-      <c r="D73" s="36">
-        <v>134050</v>
-      </c>
+      <c r="D73" s="36"/>
       <c r="E73" s="58">
-        <f>D73*91.91%</f>
-        <v>123205.355</v>
+        <f>D73</f>
+        <v>0</v>
       </c>
       <c r="F73" s="48">
-        <f>D73*8.09%</f>
-        <v>10844.645</v>
+        <v>0</v>
       </c>
       <c r="G73" s="64"/>
       <c r="H73" s="59"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="99" t="s">
-        <v>121</v>
-      </c>
-      <c r="B74" s="136"/>
-      <c r="C74" s="123"/>
-      <c r="D74" s="36">
-        <v>112800</v>
-      </c>
-      <c r="E74" s="58">
-        <f>D74</f>
-        <v>112800</v>
-      </c>
-      <c r="F74" s="48">
-        <v>0</v>
-      </c>
-      <c r="G74" s="64"/>
-      <c r="H74" s="59"/>
-    </row>
-    <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="116" t="s">
+    <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="B75" s="116"/>
-      <c r="C75" s="116"/>
-      <c r="D75" s="32">
-        <f>SUM(D72:D74)</f>
-        <v>385850</v>
-      </c>
-      <c r="E75" s="32">
-        <f>SUM(E72:E74)</f>
-        <v>363760.255</v>
-      </c>
-      <c r="F75" s="32">
-        <f>SUM(F72:F74)</f>
-        <v>22089.745000000003</v>
-      </c>
-      <c r="G75" s="33">
-        <f>E75+F75</f>
-        <v>385850</v>
-      </c>
-      <c r="H75" s="59" t="str">
-        <f>IF(D75=G75, "", "Error")</f>
+      <c r="B74" s="116"/>
+      <c r="C74" s="116"/>
+      <c r="D74" s="32">
+        <f>SUM(D72:D73)</f>
+        <v>0</v>
+      </c>
+      <c r="E74" s="32">
+        <f>SUM(E72:E73)</f>
+        <v>0</v>
+      </c>
+      <c r="F74" s="32">
+        <f>SUM(F72:F73)</f>
+        <v>0</v>
+      </c>
+      <c r="G74" s="33">
+        <f>E74+F74</f>
+        <v>0</v>
+      </c>
+      <c r="H74" s="59" t="str">
+        <f>IF(D74=G74, "", "Error")</f>
         <v/>
       </c>
-      <c r="J75" s="33"/>
+      <c r="J74" s="33"/>
+    </row>
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="77"/>
+      <c r="B75" s="77"/>
+      <c r="C75" s="77"/>
+      <c r="D75" s="102"/>
+      <c r="E75" s="38"/>
+      <c r="F75" s="2"/>
+      <c r="H75" s="59"/>
     </row>
     <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="77"/>
       <c r="B76" s="77"/>
       <c r="C76" s="77"/>
       <c r="D76" s="102"/>
-      <c r="E76" s="38"/>
+      <c r="E76" s="37"/>
       <c r="F76" s="2"/>
       <c r="H76" s="59"/>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="77"/>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="117" t="s">
+        <v>13</v>
+      </c>
       <c r="B77" s="77"/>
       <c r="C77" s="77"/>
       <c r="D77" s="102"/>
@@ -3193,15 +3168,28 @@
       <c r="F77" s="2"/>
       <c r="H77" s="59"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="117" t="s">
-        <v>13</v>
-      </c>
-      <c r="B78" s="77"/>
+        <v>14</v>
+      </c>
+      <c r="B78" s="77" t="s">
+        <v>129</v>
+      </c>
       <c r="C78" s="77"/>
-      <c r="D78" s="102"/>
-      <c r="E78" s="37"/>
-      <c r="F78" s="2"/>
+      <c r="D78" s="36">
+        <v>285700</v>
+      </c>
+      <c r="E78" s="58">
+        <f>D78*91.91%</f>
+        <v>262586.87</v>
+      </c>
+      <c r="F78" s="48">
+        <f>D78*8.09%</f>
+        <v>23113.13</v>
+      </c>
+      <c r="G78" t="s">
+        <v>112</v>
+      </c>
       <c r="H78" s="59"/>
     </row>
     <row r="79" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3209,349 +3197,339 @@
         <v>14</v>
       </c>
       <c r="B79" s="77" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C79" s="77"/>
-      <c r="D79" s="209">
-        <v>285700</v>
+      <c r="D79" s="36">
+        <v>119000</v>
       </c>
       <c r="E79" s="58">
         <f>D79*91.91%</f>
-        <v>262586.87</v>
+        <v>109372.9</v>
       </c>
       <c r="F79" s="48">
         <f>D79*8.09%</f>
-        <v>23113.13</v>
-      </c>
-      <c r="G79" t="s">
-        <v>112</v>
-      </c>
-      <c r="H79" s="59"/>
-    </row>
-    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9627.1</v>
+      </c>
+      <c r="H79" s="65"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="117" t="s">
-        <v>14</v>
-      </c>
-      <c r="B80" s="77" t="s">
-        <v>134</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="B80" s="77"/>
       <c r="C80" s="77"/>
-      <c r="D80" s="209">
-        <v>119000</v>
+      <c r="D80" s="36">
+        <v>50000</v>
       </c>
       <c r="E80" s="58">
         <f>D80*91.91%</f>
-        <v>109372.9</v>
+        <v>45954.999999999993</v>
       </c>
       <c r="F80" s="48">
         <f>D80*8.09%</f>
-        <v>9627.1</v>
-      </c>
-      <c r="H80" s="65"/>
+        <v>4045</v>
+      </c>
+      <c r="H80" s="59"/>
+      <c r="J80" s="36"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" s="117" t="s">
-        <v>80</v>
-      </c>
+      <c r="A81" s="117"/>
       <c r="B81" s="77"/>
       <c r="C81" s="77"/>
-      <c r="D81" s="209">
-        <v>50000</v>
-      </c>
+      <c r="D81" s="102"/>
       <c r="E81" s="58">
         <f>D81*91.91%</f>
-        <v>45954.999999999993</v>
+        <v>0</v>
       </c>
       <c r="F81" s="48">
         <f>D81*8.09%</f>
-        <v>4045</v>
+        <v>0</v>
       </c>
       <c r="H81" s="59"/>
-      <c r="J81" s="36"/>
+      <c r="J81" s="33"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" s="117"/>
-      <c r="B82" s="77"/>
-      <c r="C82" s="77"/>
-      <c r="D82" s="102"/>
-      <c r="E82" s="58">
-        <f>D82*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F82" s="48">
-        <f>D82*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="H82" s="59"/>
+      <c r="A82" s="116"/>
+      <c r="B82" s="116"/>
+      <c r="C82" s="116"/>
+      <c r="D82" s="32">
+        <f>SUM(D78:D81)</f>
+        <v>454700</v>
+      </c>
+      <c r="E82" s="32">
+        <f>SUM(E78:E81)</f>
+        <v>417914.77</v>
+      </c>
+      <c r="F82" s="32">
+        <f>SUM(F78:F81)</f>
+        <v>36785.230000000003</v>
+      </c>
+      <c r="G82" s="33">
+        <f>E82+F82</f>
+        <v>454700</v>
+      </c>
+      <c r="H82" s="59" t="str">
+        <f>IF(D82=G82, "", "Error")</f>
+        <v/>
+      </c>
       <c r="J82" s="33"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="116"/>
-      <c r="B83" s="116"/>
-      <c r="C83" s="116"/>
-      <c r="D83" s="32">
-        <f>SUM(D79:D82)</f>
-        <v>454700</v>
-      </c>
-      <c r="E83" s="32">
-        <f>SUM(E79:E82)</f>
-        <v>417914.77</v>
-      </c>
-      <c r="F83" s="32">
-        <f>SUM(F79:F82)</f>
-        <v>36785.230000000003</v>
-      </c>
-      <c r="G83" s="33">
-        <f>E83+F83</f>
-        <v>454700</v>
-      </c>
-      <c r="H83" s="59" t="str">
-        <f>IF(D83=G83, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J83" s="33"/>
-    </row>
-    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="117" t="s">
+        <v>73</v>
+      </c>
+      <c r="B83" s="77"/>
+      <c r="C83" s="77"/>
+      <c r="D83" s="36"/>
+      <c r="E83" s="39"/>
+      <c r="F83" s="2"/>
+      <c r="H83" s="59"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="117" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B84" s="77"/>
       <c r="C84" s="77"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="39"/>
-      <c r="F84" s="2"/>
+      <c r="D84" s="36">
+        <f>-7402+149994.47</f>
+        <v>142592.47</v>
+      </c>
+      <c r="E84" s="58">
+        <f>D84*91.91%</f>
+        <v>131056.739177</v>
+      </c>
+      <c r="F84" s="48">
+        <f>D84*8.09%</f>
+        <v>11535.730823</v>
+      </c>
       <c r="H84" s="59"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="117" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B85" s="77"/>
-      <c r="C85" s="77"/>
+      <c r="C85" s="126"/>
       <c r="D85" s="36">
-        <f>152+180218.02</f>
-        <v>180370.02</v>
+        <v>69000</v>
       </c>
       <c r="E85" s="58">
         <f>D85*91.91%</f>
-        <v>165778.08538199996</v>
+        <v>63417.899999999994</v>
       </c>
       <c r="F85" s="48">
         <f>D85*8.09%</f>
-        <v>14591.934617999999</v>
+        <v>5582.1</v>
       </c>
       <c r="H85" s="59"/>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="117" t="s">
-        <v>75</v>
-      </c>
-      <c r="B86" s="77"/>
-      <c r="C86" s="126"/>
-      <c r="D86" s="36">
-        <v>69000</v>
-      </c>
-      <c r="E86" s="58">
-        <f>D86*91.91%</f>
-        <v>63417.899999999994</v>
-      </c>
-      <c r="F86" s="48">
-        <f>D86*8.09%</f>
-        <v>5582.1</v>
-      </c>
-      <c r="H86" s="59"/>
+      <c r="A86" s="116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" s="116"/>
+      <c r="C86" s="116"/>
+      <c r="D86" s="62">
+        <f>SUM(D84:D85)</f>
+        <v>211592.47</v>
+      </c>
+      <c r="E86" s="56">
+        <f t="shared" ref="E86:F86" si="22">SUM(E84:E85)</f>
+        <v>194474.63917699998</v>
+      </c>
+      <c r="F86" s="56">
+        <f t="shared" si="22"/>
+        <v>17117.830823</v>
+      </c>
+      <c r="G86" s="33">
+        <f>E86+F86</f>
+        <v>211592.46999999997</v>
+      </c>
+      <c r="H86" s="59" t="str">
+        <f>IF(D86=G86, "", "Error")</f>
+        <v/>
+      </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" s="116"/>
-      <c r="C87" s="116"/>
-      <c r="D87" s="62">
-        <f>SUM(D85:D86)</f>
-        <v>249370.02</v>
-      </c>
-      <c r="E87" s="56">
-        <f t="shared" ref="E87:F87" si="20">SUM(E85:E86)</f>
-        <v>229195.98538199996</v>
-      </c>
-      <c r="F87" s="56">
-        <f t="shared" si="20"/>
-        <v>20174.034617999998</v>
-      </c>
-      <c r="G87" s="33">
-        <f>E87+F87</f>
-        <v>249370.01999999996</v>
-      </c>
-      <c r="H87" s="59" t="str">
-        <f>IF(D87=G87, "", "Error")</f>
+      <c r="A87" s="77"/>
+      <c r="B87" s="77"/>
+      <c r="C87" s="77"/>
+      <c r="D87" s="77"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="2"/>
+      <c r="H87" s="59"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="127" t="s">
+        <v>102</v>
+      </c>
+      <c r="B88" s="127"/>
+      <c r="C88" s="140"/>
+      <c r="D88" s="141"/>
+      <c r="E88" s="139">
+        <f>D88*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F88" s="50">
+        <f>D88*8.09%</f>
+        <v>0</v>
+      </c>
+      <c r="G88" s="33">
+        <f>E88+F88</f>
+        <v>0</v>
+      </c>
+      <c r="H88" s="59" t="str">
+        <f>IF(D88=G88, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="77"/>
-      <c r="B88" s="77"/>
-      <c r="C88" s="77"/>
-      <c r="D88" s="77"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="2"/>
-      <c r="H88" s="59"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="127" t="s">
-        <v>102</v>
-      </c>
-      <c r="B89" s="127"/>
-      <c r="C89" s="140"/>
-      <c r="D89" s="141"/>
-      <c r="E89" s="139">
-        <f>D89*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F89" s="50">
-        <f>D89*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G89" s="33">
-        <f>E89+F89</f>
-        <v>0</v>
-      </c>
-      <c r="H89" s="59" t="str">
-        <f>IF(D89=G89, "", "Error")</f>
+    <row r="89" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="128"/>
+      <c r="B89" s="76"/>
+      <c r="C89" s="76"/>
+      <c r="D89" s="142"/>
+      <c r="E89" s="143"/>
+      <c r="F89" s="143"/>
+      <c r="G89" s="61"/>
+      <c r="H89" s="59"/>
+    </row>
+    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="129" t="s">
+        <v>76</v>
+      </c>
+      <c r="B90" s="130"/>
+      <c r="C90" s="131"/>
+      <c r="D90" s="78">
+        <f>SUM(D88+D86+D82+D74+D68+D49+D32+D27+D43)</f>
+        <v>11513244.489999998</v>
+      </c>
+      <c r="E90" s="57">
+        <f>SUM(E88+E86+E82+E74+E68+E49+E32+E27+E43)</f>
+        <v>10937076.406698</v>
+      </c>
+      <c r="F90" s="144">
+        <f>SUM(F27+F43+F49+F68+F74+F82+F86+F88)</f>
+        <v>576168.08330200007</v>
+      </c>
+      <c r="G90" s="33">
+        <f>E90+F90</f>
+        <v>11513244.49</v>
+      </c>
+      <c r="H90" s="59" t="str">
+        <f>IF(D90=G90, "", "Error")</f>
         <v/>
       </c>
-    </row>
-    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="128"/>
-      <c r="B90" s="76"/>
-      <c r="C90" s="76"/>
-      <c r="D90" s="142"/>
-      <c r="E90" s="143"/>
-      <c r="F90" s="143"/>
-      <c r="G90" s="61"/>
-      <c r="H90" s="59"/>
+      <c r="I90" s="74">
+        <f>D90-G90</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="129" t="s">
-        <v>76</v>
-      </c>
-      <c r="B91" s="130"/>
-      <c r="C91" s="131"/>
-      <c r="D91" s="78">
-        <f>SUM(D89+D87+D83+D75+D68+D49+D32+D27+D43)</f>
-        <v>12215707.529999999</v>
-      </c>
-      <c r="E91" s="57">
-        <f>SUM(E89+E87+E83+E75+E68+E49+E32+E27+E43)</f>
-        <v>11623292.497903001</v>
-      </c>
-      <c r="F91" s="144">
-        <f>SUM(F27+F43+F49+F68+F75+F83+F87+F89)</f>
-        <v>592415.03209700005</v>
-      </c>
-      <c r="G91" s="33">
-        <f>E91+F91</f>
-        <v>12215707.530000001</v>
-      </c>
-      <c r="H91" s="59" t="str">
-        <f>IF(D91=G91, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="I91" s="74">
-        <f>D91-G91</f>
-        <v>0</v>
-      </c>
+      <c r="A91" s="76"/>
+      <c r="B91" s="76"/>
+      <c r="C91" s="76"/>
+      <c r="D91" s="76"/>
+      <c r="E91" s="33"/>
     </row>
     <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="76"/>
-      <c r="B92" s="76"/>
-      <c r="C92" s="76"/>
+      <c r="A92" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="B92" s="133"/>
+      <c r="C92" s="133"/>
       <c r="D92" s="76"/>
       <c r="E92" s="33"/>
     </row>
-    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="132" t="s">
-        <v>108</v>
-      </c>
-      <c r="B93" s="133"/>
-      <c r="C93" s="133"/>
+    <row r="93" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="210" t="s">
+        <v>132</v>
+      </c>
+      <c r="B93" s="211"/>
+      <c r="C93" s="217">
+        <v>320000</v>
+      </c>
       <c r="D93" s="76"/>
       <c r="E93" s="33"/>
     </row>
-    <row r="94" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="214" t="s">
-        <v>133</v>
-      </c>
-      <c r="B94" s="215"/>
-      <c r="C94" s="221">
-        <v>320000</v>
-      </c>
+    <row r="94" spans="1:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="212"/>
+      <c r="B94" s="213"/>
+      <c r="C94" s="218"/>
       <c r="D94" s="76"/>
       <c r="E94" s="33"/>
     </row>
-    <row r="95" spans="1:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="216"/>
-      <c r="B95" s="217"/>
-      <c r="C95" s="222"/>
-      <c r="D95" s="76"/>
+    <row r="95" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B95" s="55"/>
+      <c r="C95" s="53">
+        <f>SUM(C93:C94)</f>
+        <v>320000</v>
+      </c>
       <c r="E95" s="33"/>
     </row>
-    <row r="96" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="B96" s="55"/>
-      <c r="C96" s="53">
-        <f>SUM(C94:C95)</f>
-        <v>320000</v>
-      </c>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E96" s="33"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E97" s="33"/>
+      <c r="E97" s="51"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E98" s="51"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="175" t="s">
+      <c r="A98" s="175" t="s">
         <v>85</v>
       </c>
-      <c r="B99" s="176"/>
-      <c r="C99" s="176"/>
-      <c r="D99" s="176"/>
-      <c r="E99" s="71" t="s">
+      <c r="B98" s="176"/>
+      <c r="C98" s="176"/>
+      <c r="D98" s="176"/>
+      <c r="E98" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="F99" s="72" t="s">
+      <c r="F98" s="72" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A100" s="172"/>
-      <c r="B100" s="173"/>
-      <c r="C100" s="174"/>
+    <row r="99" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A99" s="172"/>
+      <c r="B99" s="173"/>
+      <c r="C99" s="174"/>
+      <c r="D99" s="36"/>
+      <c r="E99" s="58">
+        <f t="shared" ref="E99:E103" si="23">D99*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F99" s="48">
+        <f t="shared" ref="F99:F103" si="24">D99*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="177"/>
+      <c r="B100" s="178"/>
+      <c r="C100" s="179"/>
       <c r="D100" s="36"/>
       <c r="E100" s="58">
-        <f t="shared" ref="E100:E104" si="21">D100*91.91%</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="F100" s="48">
-        <f t="shared" ref="F100:F104" si="22">D100*8.09%</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="177"/>
-      <c r="B101" s="178"/>
-      <c r="C101" s="179"/>
+      <c r="A101" s="151"/>
+      <c r="B101" s="149"/>
+      <c r="C101" s="150"/>
       <c r="D101" s="36"/>
       <c r="E101" s="58">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="F101" s="48">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
     </row>
@@ -3561,80 +3539,74 @@
       <c r="C102" s="150"/>
       <c r="D102" s="36"/>
       <c r="E102" s="58">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="F102" s="48">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="151"/>
-      <c r="B103" s="149"/>
-      <c r="C103" s="150"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="177"/>
+      <c r="B103" s="178"/>
+      <c r="C103" s="179"/>
       <c r="D103" s="36"/>
       <c r="E103" s="58">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="F103" s="48">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="177"/>
-      <c r="B104" s="178"/>
-      <c r="C104" s="179"/>
-      <c r="D104" s="36"/>
-      <c r="E104" s="58">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="F104" s="48">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="169" t="s">
+        <v>25</v>
+      </c>
+      <c r="B104" s="170"/>
+      <c r="C104" s="171"/>
+      <c r="D104" s="70">
+        <f>SUM(D99:D103)</f>
+        <v>0</v>
+      </c>
+      <c r="E104" s="70">
+        <f>SUM(E99:E103)</f>
+        <v>0</v>
+      </c>
+      <c r="F104" s="70">
+        <f>SUM(F99:F103)</f>
+        <v>0</v>
+      </c>
+      <c r="H104" s="33"/>
+      <c r="I104" s="59" t="str">
+        <f>IF(D104=H104, "", "Error")</f>
+        <v/>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="169" t="s">
-        <v>25</v>
-      </c>
-      <c r="B105" s="170"/>
-      <c r="C105" s="171"/>
-      <c r="D105" s="70">
-        <f>SUM(D100:D104)</f>
-        <v>0</v>
-      </c>
-      <c r="E105" s="70">
-        <f>SUM(E100:E104)</f>
-        <v>0</v>
-      </c>
-      <c r="F105" s="70">
-        <f>SUM(F100:F104)</f>
-        <v>0</v>
-      </c>
+      <c r="D105" s="33"/>
       <c r="H105" s="33"/>
-      <c r="I105" s="59" t="str">
-        <f>IF(D105=H105, "", "Error")</f>
-        <v/>
-      </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D106" s="33"/>
+      <c r="A106" s="184" t="s">
+        <v>123</v>
+      </c>
+      <c r="B106" s="184"/>
+      <c r="C106" s="184"/>
+      <c r="D106" s="184"/>
+      <c r="E106" s="184"/>
+      <c r="F106" s="184"/>
       <c r="H106" s="33"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="184" t="s">
-        <v>124</v>
-      </c>
+      <c r="A107" s="184"/>
       <c r="B107" s="184"/>
       <c r="C107" s="184"/>
       <c r="D107" s="184"/>
       <c r="E107" s="184"/>
       <c r="F107" s="184"/>
-      <c r="H107" s="33"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="184"/>
@@ -3652,249 +3624,241 @@
       <c r="E109" s="184"/>
       <c r="F109" s="184"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="184"/>
-      <c r="B110" s="184"/>
-      <c r="C110" s="184"/>
-      <c r="D110" s="184"/>
-      <c r="E110" s="184"/>
-      <c r="F110" s="184"/>
+    <row r="110" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E110" s="33"/>
     </row>
     <row r="111" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E111" s="33"/>
+      <c r="A111" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B111" s="28">
+        <f>D90</f>
+        <v>11513244.489999998</v>
+      </c>
     </row>
     <row r="112" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="B112" s="28">
-        <f>D91</f>
-        <v>12215707.529999999</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="29" t="s">
+      <c r="A112" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="B113" s="30">
-        <f>D91-D89</f>
-        <v>12215707.529999999</v>
-      </c>
+      <c r="B112" s="30">
+        <f>D90-D88</f>
+        <v>11513244.489999998</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D113" s="159"/>
+      <c r="E113" s="159"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B114" s="9"/>
+      <c r="C114" s="10"/>
       <c r="D114" s="159"/>
       <c r="E114" s="159"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B115" s="9"/>
-      <c r="C115" s="10"/>
+      <c r="A115" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B115" s="4">
+        <v>7356485.1466246648</v>
+      </c>
+      <c r="C115" s="12"/>
       <c r="D115" s="159"/>
       <c r="E115" s="159"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B116" s="4">
-        <v>14089108.26</v>
-      </c>
-      <c r="C116" s="12"/>
+      <c r="A116" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B116" s="22">
+        <f>PRORRATEO!G52</f>
+        <v>7788154.2205740046</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>66</v>
+      </c>
       <c r="D116" s="159"/>
       <c r="E116" s="159"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B117" s="22">
-        <f>PRORRATEO!G52</f>
-        <v>8264798.2205740046</v>
-      </c>
-      <c r="C117" s="12" t="s">
-        <v>66</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="B117" s="73">
+        <f>-B112</f>
+        <v>-11513244.489999998</v>
+      </c>
+      <c r="C117" s="10"/>
       <c r="D117" s="159"/>
       <c r="E117" s="159"/>
+      <c r="G117" s="36"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B118" s="73">
-        <f>-B113</f>
-        <v>-12215707.529999999</v>
+        <f>-D104</f>
+        <v>0</v>
       </c>
       <c r="C118" s="10"/>
       <c r="D118" s="159"/>
       <c r="E118" s="159"/>
-      <c r="G118" s="36"/>
+      <c r="G118" s="42"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="13" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B119" s="73">
-        <f>-D105</f>
-        <v>0</v>
-      </c>
-      <c r="C119" s="10"/>
-      <c r="D119" s="159"/>
-      <c r="E119" s="159"/>
-      <c r="G119" s="42"/>
+        <f>-B125</f>
+        <v>0</v>
+      </c>
+      <c r="C119" s="14"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B120" s="73">
-        <f>-B126</f>
-        <v>0</v>
+        <v>91</v>
+      </c>
+      <c r="B120" s="23">
+        <f>-C95</f>
+        <v>-320000</v>
       </c>
       <c r="C120" s="14"/>
+      <c r="E120" s="33"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="B121" s="23">
-        <f>-C96</f>
-        <v>-320000</v>
-      </c>
-      <c r="C121" s="14"/>
-      <c r="E121" s="33"/>
+      <c r="A121" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B121" s="15">
+        <f>SUM(B115:B120)</f>
+        <v>3311394.8771986701</v>
+      </c>
+      <c r="C121" s="60"/>
+      <c r="D121" s="33"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B122" s="15">
-        <f>SUM(B116:B121)</f>
-        <v>9818198.950574005</v>
-      </c>
-      <c r="C122" s="60"/>
-      <c r="D122" s="33"/>
+      <c r="A122" s="14"/>
+      <c r="C122" s="10"/>
+      <c r="D122" s="17"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="14"/>
       <c r="C123" s="10"/>
-      <c r="D123" s="17"/>
+      <c r="D123" s="33"/>
+      <c r="E123" s="74"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C124" s="10"/>
-      <c r="D124" s="33"/>
-      <c r="E124" s="74"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="8" t="s">
+      <c r="A124" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B125" s="84">
+      <c r="B124" s="84">
         <f>-82694.54</f>
         <v>-82694.539999999994</v>
       </c>
+      <c r="C124" s="16"/>
+      <c r="D124" s="74"/>
+      <c r="E124" s="74"/>
+      <c r="F124" s="74"/>
+    </row>
+    <row r="125" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B125" s="23">
+        <v>0</v>
+      </c>
       <c r="C125" s="16"/>
       <c r="D125" s="74"/>
-      <c r="E125" s="74"/>
-      <c r="F125" s="74"/>
-    </row>
-    <row r="126" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B126" s="23">
-        <v>0</v>
-      </c>
+      <c r="E125" s="79"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="11"/>
+      <c r="B126" s="73"/>
       <c r="C126" s="16"/>
-      <c r="D126" s="74"/>
-      <c r="E126" s="79"/>
+      <c r="E126" s="33"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="11"/>
       <c r="B127" s="73"/>
       <c r="C127" s="16"/>
+      <c r="D127" s="134"/>
       <c r="E127" s="33"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="11"/>
-      <c r="B128" s="73"/>
+      <c r="A128" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B128" s="26">
+        <f>SUM(B124:B127)</f>
+        <v>-82694.539999999994</v>
+      </c>
       <c r="C128" s="16"/>
-      <c r="D128" s="134"/>
-      <c r="E128" s="33"/>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A129" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B129" s="26">
-        <f>SUM(B125:B128)</f>
-        <v>-82694.539999999994</v>
-      </c>
-      <c r="C129" s="16"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C130" s="17"/>
-      <c r="D130" s="74"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B131" s="14"/>
-      <c r="C131" s="10"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="N133" s="5"/>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C129" s="17"/>
+      <c r="D129" s="74"/>
+    </row>
+    <row r="130" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B130" s="14"/>
+      <c r="C130" s="10"/>
+    </row>
+    <row r="132" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N132" s="5"/>
+    </row>
+    <row r="135" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B135" s="158"/>
+      <c r="C135" s="158"/>
+      <c r="D135" s="158"/>
+      <c r="E135" s="158"/>
+    </row>
+    <row r="136" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B136" s="158"/>
       <c r="C136" s="158"/>
       <c r="D136" s="158"/>
       <c r="E136" s="158"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B137" s="158"/>
       <c r="C137" s="158"/>
       <c r="D137" s="158"/>
       <c r="E137" s="158"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B138" s="158"/>
       <c r="C138" s="158"/>
       <c r="D138" s="158"/>
       <c r="E138" s="158"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B139" s="158"/>
       <c r="C139" s="158"/>
       <c r="D139" s="158"/>
       <c r="E139" s="158"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B140" s="158"/>
-      <c r="C140" s="158"/>
-      <c r="D140" s="158"/>
-      <c r="E140" s="158"/>
-    </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B135:E139"/>
+    <mergeCell ref="D113:E118"/>
+    <mergeCell ref="B14:D17"/>
+    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A106:F109"/>
+    <mergeCell ref="A61:C61"/>
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A93:B94"/>
+    <mergeCell ref="C93:C94"/>
+    <mergeCell ref="A60:C60"/>
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B136:E140"/>
-    <mergeCell ref="D114:E119"/>
-    <mergeCell ref="B14:D17"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A107:F110"/>
-    <mergeCell ref="A62:C62"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3922,95 +3886,96 @@
     <col min="14" max="14" width="13.7109375" customWidth="1"/>
     <col min="15" max="15" width="11.42578125" customWidth="1"/>
     <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.85546875" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="198" t="str">
+      <c r="A1" s="196" t="str">
         <f>RESUMEN!C5</f>
         <v>VTO: 17/08</v>
       </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="200"/>
+      <c r="B1" s="197"/>
+      <c r="C1" s="197"/>
+      <c r="D1" s="197"/>
+      <c r="E1" s="197"/>
+      <c r="F1" s="197"/>
+      <c r="G1" s="197"/>
+      <c r="H1" s="197"/>
+      <c r="I1" s="197"/>
+      <c r="J1" s="198"/>
       <c r="K1" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="190">
-        <f>RESUMEN!D91</f>
-        <v>12215707.529999999</v>
-      </c>
-      <c r="M1" s="191"/>
+      <c r="L1" s="185">
+        <f>RESUMEN!D90</f>
+        <v>11513244.489999998</v>
+      </c>
+      <c r="M1" s="186"/>
       <c r="N1" s="89"/>
       <c r="O1" s="49">
         <f>L1*8.09%</f>
-        <v>988250.73917699989</v>
+        <v>931421.47924099991</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="201"/>
-      <c r="B2" s="202"/>
-      <c r="C2" s="202"/>
-      <c r="D2" s="202"/>
-      <c r="E2" s="202"/>
-      <c r="F2" s="202"/>
-      <c r="G2" s="202"/>
-      <c r="H2" s="202"/>
-      <c r="I2" s="202"/>
-      <c r="J2" s="203"/>
+      <c r="A2" s="199"/>
+      <c r="B2" s="200"/>
+      <c r="C2" s="200"/>
+      <c r="D2" s="200"/>
+      <c r="E2" s="200"/>
+      <c r="F2" s="200"/>
+      <c r="G2" s="200"/>
+      <c r="H2" s="200"/>
+      <c r="I2" s="200"/>
+      <c r="J2" s="201"/>
       <c r="K2" s="90" t="s">
         <v>95</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="91">
-        <f>8500000-812600</f>
-        <v>7687400</v>
+        <f>9000000</f>
+        <v>9000000</v>
       </c>
       <c r="N2" s="92"/>
       <c r="O2" s="49">
         <f>O1-K7-553-50-86-8</f>
-        <v>677130.51921899989</v>
+        <v>354556.39593899983</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="201"/>
-      <c r="B3" s="202"/>
-      <c r="C3" s="202"/>
-      <c r="D3" s="202"/>
-      <c r="E3" s="202"/>
-      <c r="F3" s="202"/>
-      <c r="G3" s="202"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="202"/>
-      <c r="J3" s="203"/>
+      <c r="A3" s="199"/>
+      <c r="B3" s="200"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="200"/>
+      <c r="I3" s="200"/>
+      <c r="J3" s="201"/>
       <c r="K3" s="90" t="s">
         <v>100</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="93">
-        <f>RESUMEN!D105</f>
+        <f>RESUMEN!D104</f>
         <v>0</v>
       </c>
       <c r="N3" s="94"/>
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="204"/>
-      <c r="B4" s="205"/>
-      <c r="C4" s="205"/>
-      <c r="D4" s="205"/>
-      <c r="E4" s="205"/>
-      <c r="F4" s="205"/>
-      <c r="G4" s="205"/>
-      <c r="H4" s="205"/>
-      <c r="I4" s="205"/>
-      <c r="J4" s="206"/>
+      <c r="A4" s="202"/>
+      <c r="B4" s="203"/>
+      <c r="C4" s="203"/>
+      <c r="D4" s="203"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="203"/>
+      <c r="G4" s="203"/>
+      <c r="H4" s="203"/>
+      <c r="I4" s="203"/>
+      <c r="J4" s="204"/>
       <c r="K4" s="95" t="s">
         <v>95</v>
       </c>
@@ -4025,64 +3990,64 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="185" t="s">
+      <c r="A5" s="189" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="207" t="s">
+      <c r="B5" s="205" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="185" t="s">
+      <c r="C5" s="189" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="187" t="s">
+      <c r="D5" s="194" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="185" t="s">
+      <c r="E5" s="189" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="185" t="s">
+      <c r="F5" s="189" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="185" t="s">
+      <c r="G5" s="189" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="194" t="s">
+      <c r="H5" s="191" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="187" t="s">
+      <c r="I5" s="194" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="192" t="s">
+      <c r="J5" s="187" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="192" t="s">
+      <c r="K5" s="187" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="192" t="s">
+      <c r="L5" s="187" t="s">
         <v>114</v>
       </c>
-      <c r="M5" s="192" t="s">
+      <c r="M5" s="187" t="s">
         <v>116</v>
       </c>
-      <c r="N5" s="192" t="s">
+      <c r="N5" s="187" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="186"/>
-      <c r="B6" s="208"/>
-      <c r="C6" s="186"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="186"/>
-      <c r="H6" s="195"/>
-      <c r="I6" s="197"/>
-      <c r="J6" s="196"/>
-      <c r="K6" s="193"/>
-      <c r="L6" s="196"/>
-      <c r="M6" s="193"/>
-      <c r="N6" s="193"/>
+      <c r="A6" s="190"/>
+      <c r="B6" s="206"/>
+      <c r="C6" s="190"/>
+      <c r="D6" s="207"/>
+      <c r="E6" s="190"/>
+      <c r="F6" s="190"/>
+      <c r="G6" s="190"/>
+      <c r="H6" s="192"/>
+      <c r="I6" s="195"/>
+      <c r="J6" s="193"/>
+      <c r="K6" s="188"/>
+      <c r="L6" s="193"/>
+      <c r="M6" s="188"/>
+      <c r="N6" s="188"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
@@ -4101,7 +4066,7 @@
       <c r="F7" s="18">
         <v>482508.47</v>
       </c>
-      <c r="G7" s="219">
+      <c r="G7" s="148">
         <f>F7</f>
         <v>482508.47</v>
       </c>
@@ -4117,16 +4082,16 @@
         <v>144773.44702899997</v>
       </c>
       <c r="K7" s="18">
-        <v>310423.219958</v>
+        <v>576168.08330200007</v>
       </c>
       <c r="L7" s="24"/>
       <c r="M7" s="1">
         <f>K7+J7+H7+L7</f>
-        <v>455196.66698699998</v>
+        <v>720941.53033099999</v>
       </c>
       <c r="N7" s="4">
         <f>M7*6% + M7</f>
-        <v>482508.46700621996</v>
+        <v>764198.02215085994</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -4146,7 +4111,7 @@
       <c r="F8" s="18">
         <v>197004.75823218253</v>
       </c>
-      <c r="G8" s="219">
+      <c r="G8" s="148">
         <v>200000</v>
       </c>
       <c r="H8" s="45">
@@ -4162,16 +4127,16 @@
       </c>
       <c r="K8" s="18">
         <f>M$2*E8 /100</f>
-        <v>169891.54</v>
+        <v>198900</v>
       </c>
       <c r="L8" s="86"/>
       <c r="M8" s="1">
         <f>K8+J8+H8+L8</f>
-        <v>206445.03963318252</v>
+        <v>235453.49963318251</v>
       </c>
       <c r="N8" s="4">
         <f t="shared" ref="N8:N51" si="1">M8*6% + M8</f>
-        <v>218831.74201117345</v>
+        <v>249580.70961117346</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -4191,7 +4156,7 @@
       <c r="F9" s="18">
         <v>398979.10046859668</v>
       </c>
-      <c r="G9" s="218">
+      <c r="G9" s="103">
         <f>450154-G34</f>
         <v>398978.54662599997</v>
       </c>
@@ -4208,16 +4173,18 @@
       </c>
       <c r="K9" s="18">
         <f t="shared" ref="K9:K51" si="3">M$2*E9 /100</f>
-        <v>323639.53999999998</v>
-      </c>
-      <c r="L9" s="86"/>
+        <v>378900</v>
+      </c>
+      <c r="L9" s="86">
+        <v>20000</v>
+      </c>
       <c r="M9" s="1">
         <f t="shared" ref="M9:M51" si="4">K9+J9+H9+L9</f>
-        <v>398979.55144359666</v>
+        <v>474240.01144359668</v>
       </c>
       <c r="N9" s="4">
         <f t="shared" si="1"/>
-        <v>422918.32453021244</v>
+        <v>502694.41213021247</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -4238,31 +4205,29 @@
         <v>292945.13700400002</v>
       </c>
       <c r="G10" s="148">
-        <v>218322</v>
+        <v>0</v>
       </c>
       <c r="H10" s="45">
         <f t="shared" si="0"/>
-        <v>74623.137004000018</v>
-      </c>
-      <c r="I10" s="31">
-        <v>12</v>
-      </c>
+        <v>292945.13700400002</v>
+      </c>
+      <c r="I10" s="31"/>
       <c r="J10" s="18">
         <f t="shared" si="2"/>
         <v>50822.817003999982</v>
       </c>
       <c r="K10" s="18">
         <f t="shared" si="3"/>
-        <v>218322.16</v>
+        <v>255600</v>
       </c>
       <c r="L10" s="86"/>
       <c r="M10" s="1">
         <f t="shared" si="4"/>
-        <v>343768.114008</v>
+        <v>599367.95400799997</v>
       </c>
       <c r="N10" s="4">
         <f t="shared" si="1"/>
-        <v>364394.20084847999</v>
+        <v>635330.03124847997</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -4282,7 +4247,7 @@
       <c r="F11" s="18">
         <v>325058.89828299999</v>
       </c>
-      <c r="G11" s="219">
+      <c r="G11" s="148">
         <f>F11</f>
         <v>325058.89828299999</v>
       </c>
@@ -4299,16 +4264,16 @@
       </c>
       <c r="K11" s="18">
         <f t="shared" si="3"/>
-        <v>263677.82</v>
+        <v>308700</v>
       </c>
       <c r="L11" s="86"/>
       <c r="M11" s="1">
         <f t="shared" si="4"/>
-        <v>325058.89828299999</v>
+        <v>370081.07828299998</v>
       </c>
       <c r="N11" s="4">
         <f t="shared" si="1"/>
-        <v>344562.43217997998</v>
+        <v>392285.94297997997</v>
       </c>
       <c r="P11" s="33"/>
     </row>
@@ -4329,7 +4294,7 @@
       <c r="F12" s="18">
         <v>269144.97700399999</v>
       </c>
-      <c r="G12" s="218">
+      <c r="G12" s="103">
         <f>F12</f>
         <v>269144.97700399999</v>
       </c>
@@ -4346,16 +4311,16 @@
       </c>
       <c r="K12" s="18">
         <f t="shared" si="3"/>
-        <v>218322.16</v>
+        <v>255600</v>
       </c>
       <c r="L12" s="86"/>
       <c r="M12" s="1">
         <f t="shared" si="4"/>
-        <v>269144.97700399999</v>
+        <v>306422.81700399995</v>
       </c>
       <c r="N12" s="4">
         <f t="shared" si="1"/>
-        <v>285293.67562423996</v>
+        <v>324808.18602423993</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -4375,7 +4340,7 @@
       <c r="F13" s="18">
         <v>325058.19570224179</v>
       </c>
-      <c r="G13" s="218">
+      <c r="G13" s="103">
         <f>380972-G50</f>
         <v>325058.078721</v>
       </c>
@@ -4392,16 +4357,16 @@
       </c>
       <c r="K13" s="18">
         <f t="shared" si="3"/>
-        <v>263677.82</v>
+        <v>308700</v>
       </c>
       <c r="L13" s="86"/>
       <c r="M13" s="1">
         <f t="shared" si="4"/>
-        <v>325059.01526424178</v>
+        <v>370081.19526424177</v>
       </c>
       <c r="N13" s="4">
         <f t="shared" si="1"/>
-        <v>344562.55618009629</v>
+        <v>392286.06698009628</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -4422,31 +4387,29 @@
         <v>639329.95755066664</v>
       </c>
       <c r="G14" s="148">
-        <v>218322</v>
+        <v>0</v>
       </c>
       <c r="H14" s="45">
         <f t="shared" si="0"/>
-        <v>421007.95755066664</v>
-      </c>
-      <c r="I14" s="31">
-        <v>27</v>
-      </c>
+        <v>639329.95755066664</v>
+      </c>
+      <c r="I14" s="31"/>
       <c r="J14" s="18">
         <f t="shared" si="2"/>
         <v>50822.817003999982</v>
       </c>
       <c r="K14" s="18">
         <f t="shared" si="3"/>
-        <v>218322.16</v>
+        <v>255600</v>
       </c>
       <c r="L14" s="86"/>
       <c r="M14" s="1">
         <f t="shared" si="4"/>
-        <v>690152.93455466663</v>
+        <v>945752.7745546666</v>
       </c>
       <c r="N14" s="4">
         <f t="shared" si="1"/>
-        <v>731562.11062794668</v>
+        <v>1002497.9410279465</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -4466,7 +4429,7 @@
       <c r="F15" s="18">
         <v>325058.78153932618</v>
       </c>
-      <c r="G15" s="218">
+      <c r="G15" s="103">
         <f>372444-G35</f>
         <v>325059.32095000002</v>
       </c>
@@ -4483,16 +4446,18 @@
       </c>
       <c r="K15" s="18">
         <f t="shared" si="3"/>
-        <v>263677.82</v>
-      </c>
-      <c r="L15" s="86"/>
+        <v>308700</v>
+      </c>
+      <c r="L15" s="86">
+        <v>320000</v>
+      </c>
       <c r="M15" s="1">
         <f t="shared" si="4"/>
-        <v>325058.35887232615</v>
+        <v>690080.53887232614</v>
       </c>
       <c r="N15" s="4">
         <f t="shared" si="1"/>
-        <v>344561.8604046657</v>
+        <v>731485.37120466575</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -4512,7 +4477,7 @@
       <c r="F16" s="18">
         <v>269145.47683100007</v>
       </c>
-      <c r="G16" s="218">
+      <c r="G16" s="103">
         <f>315582-G49</f>
         <v>269145.01453099999</v>
       </c>
@@ -4529,16 +4494,16 @@
       </c>
       <c r="K16" s="18">
         <f t="shared" si="3"/>
-        <v>218322.16</v>
+        <v>255600</v>
       </c>
       <c r="L16" s="86"/>
       <c r="M16" s="1">
         <f t="shared" si="4"/>
-        <v>269145.43930400006</v>
+        <v>306423.27930400003</v>
       </c>
       <c r="N16" s="4">
         <f t="shared" si="1"/>
-        <v>285294.16566224006</v>
+        <v>324808.67606224003</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -4558,7 +4523,7 @@
       <c r="F17" s="18">
         <v>320492.77406811505</v>
       </c>
-      <c r="G17" s="219">
+      <c r="G17" s="148">
         <f>414315-G47-G48</f>
         <v>320493.33548100002</v>
       </c>
@@ -4575,16 +4540,16 @@
       </c>
       <c r="K17" s="18">
         <f t="shared" si="3"/>
-        <v>263677.82</v>
+        <v>308700</v>
       </c>
       <c r="L17" s="86"/>
       <c r="M17" s="1">
         <f t="shared" si="4"/>
-        <v>325058.33687011502</v>
+        <v>370080.51687011501</v>
       </c>
       <c r="N17" s="4">
         <f t="shared" si="1"/>
-        <v>344561.83708232193</v>
+        <v>392285.34788232192</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -4604,7 +4569,7 @@
       <c r="F18" s="18">
         <v>269120.82080391794</v>
       </c>
-      <c r="G18" s="219">
+      <c r="G18" s="148">
         <f>262140-G51</f>
         <v>208121.465883</v>
       </c>
@@ -4621,16 +4586,16 @@
       </c>
       <c r="K18" s="18">
         <f t="shared" si="3"/>
-        <v>218322.16</v>
+        <v>255600</v>
       </c>
       <c r="L18" s="86"/>
       <c r="M18" s="1">
         <f t="shared" si="4"/>
-        <v>330144.33192491793</v>
+        <v>367422.1719249179</v>
       </c>
       <c r="N18" s="4">
         <f t="shared" si="1"/>
-        <v>349952.99184041301</v>
+        <v>389467.50224041298</v>
       </c>
       <c r="P18" t="s">
         <v>111</v>
@@ -4653,7 +4618,7 @@
       <c r="F19" s="18">
         <v>325058.49793150148</v>
       </c>
-      <c r="G19" s="218">
+      <c r="G19" s="103">
         <f>376233-G41</f>
         <v>325057.54662599997</v>
       </c>
@@ -4670,16 +4635,18 @@
       </c>
       <c r="K19" s="18">
         <f t="shared" si="3"/>
-        <v>263677.82</v>
-      </c>
-      <c r="L19" s="86"/>
+        <v>308700</v>
+      </c>
+      <c r="L19" s="86">
+        <v>20000</v>
+      </c>
       <c r="M19" s="1">
         <f t="shared" si="4"/>
-        <v>325059.8495885015</v>
+        <v>390082.02958850149</v>
       </c>
       <c r="N19" s="4">
         <f t="shared" si="1"/>
-        <v>344563.44056381157</v>
+        <v>413486.95136381156</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -4699,7 +4666,7 @@
       <c r="F20" s="18">
         <v>269145.05286107468</v>
       </c>
-      <c r="G20" s="219">
+      <c r="G20" s="148">
         <f>315582-G38</f>
         <v>269145.01453099999</v>
       </c>
@@ -4716,16 +4683,16 @@
       </c>
       <c r="K20" s="18">
         <f t="shared" si="3"/>
-        <v>218322.16</v>
+        <v>255600</v>
       </c>
       <c r="L20" s="86"/>
       <c r="M20" s="1">
         <f t="shared" si="4"/>
-        <v>269145.01533407468</v>
+        <v>306422.85533407464</v>
       </c>
       <c r="N20" s="4">
         <f t="shared" si="1"/>
-        <v>285293.71625411918</v>
+        <v>324808.22665411909</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -4745,7 +4712,7 @@
       <c r="F21" s="18">
         <v>325058.67357663711</v>
       </c>
-      <c r="G21" s="219">
+      <c r="G21" s="148">
         <f>376234-G45</f>
         <v>325058.54662599997</v>
       </c>
@@ -4762,16 +4729,16 @@
       </c>
       <c r="K21" s="18">
         <f t="shared" si="3"/>
-        <v>263677.82</v>
+        <v>308700</v>
       </c>
       <c r="L21" s="86"/>
       <c r="M21" s="1">
         <f t="shared" si="4"/>
-        <v>325059.02523363713</v>
+        <v>370081.20523363713</v>
       </c>
       <c r="N21" s="4">
         <f t="shared" si="1"/>
-        <v>344562.56674765534</v>
+        <v>392286.07754765532</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -4791,7 +4758,7 @@
       <c r="F22" s="18">
         <v>269144.97700399999</v>
       </c>
-      <c r="G22" s="219">
+      <c r="G22" s="148">
         <f>F22</f>
         <v>269144.97700399999</v>
       </c>
@@ -4808,16 +4775,16 @@
       </c>
       <c r="K22" s="18">
         <f t="shared" si="3"/>
-        <v>218322.16</v>
+        <v>255600</v>
       </c>
       <c r="L22" s="86"/>
       <c r="M22" s="1">
         <f t="shared" si="4"/>
-        <v>269144.97700399999</v>
+        <v>306422.81700399995</v>
       </c>
       <c r="N22" s="4">
         <f t="shared" si="1"/>
-        <v>285293.67562423996</v>
+        <v>324808.18602423993</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -4835,18 +4802,18 @@
         <v>3.43</v>
       </c>
       <c r="F23" s="18">
-        <v>285422.38618642226</v>
+        <v>302547.7293576076</v>
       </c>
       <c r="G23" s="103">
-        <f>340000-G46</f>
-        <v>292615.32095000002</v>
+        <f>300000-G46</f>
+        <v>249772.240207</v>
       </c>
       <c r="H23" s="45">
         <f t="shared" si="0"/>
-        <v>-7192.9347635777667</v>
+        <v>52775.489150607609</v>
       </c>
       <c r="I23" s="31">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J23" s="18">
         <f t="shared" si="2"/>
@@ -4854,16 +4821,18 @@
       </c>
       <c r="K23" s="18">
         <f t="shared" si="3"/>
-        <v>263677.82</v>
-      </c>
-      <c r="L23" s="86"/>
+        <v>308700</v>
+      </c>
+      <c r="L23" s="86">
+        <v>20000</v>
+      </c>
       <c r="M23" s="1">
         <f t="shared" si="4"/>
-        <v>317865.96351942222</v>
+        <v>442856.56743360759</v>
       </c>
       <c r="N23" s="4">
         <f t="shared" si="1"/>
-        <v>336937.92133058753</v>
+        <v>469427.96147962403</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -4883,7 +4852,7 @@
       <c r="F24" s="18">
         <v>269144.77042507473</v>
       </c>
-      <c r="G24" s="219">
+      <c r="G24" s="148">
         <f>315582-G37</f>
         <v>269145.01453099999</v>
       </c>
@@ -4900,16 +4869,16 @@
       </c>
       <c r="K24" s="18">
         <f t="shared" si="3"/>
-        <v>218322.16</v>
+        <v>255600</v>
       </c>
       <c r="L24" s="86"/>
       <c r="M24" s="1">
         <f t="shared" si="4"/>
-        <v>269144.73289807473</v>
+        <v>306422.57289807469</v>
       </c>
       <c r="N24" s="4">
         <f t="shared" si="1"/>
-        <v>285293.41687195923</v>
+        <v>324807.9272719592</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -4929,7 +4898,7 @@
       <c r="F25" s="18">
         <v>325058.89828299999</v>
       </c>
-      <c r="G25" s="218">
+      <c r="G25" s="103">
         <f>F25+1000</f>
         <v>326058.89828299999</v>
       </c>
@@ -4946,16 +4915,16 @@
       </c>
       <c r="K25" s="18">
         <f t="shared" si="3"/>
-        <v>263677.82</v>
+        <v>308700</v>
       </c>
       <c r="L25" s="87"/>
       <c r="M25" s="1">
         <f t="shared" si="4"/>
-        <v>324058.89828299999</v>
+        <v>369081.07828299998</v>
       </c>
       <c r="N25" s="4">
         <f t="shared" si="1"/>
-        <v>343502.43217997998</v>
+        <v>391225.94297997997</v>
       </c>
       <c r="P25" s="52"/>
       <c r="Q25" s="52"/>
@@ -4978,7 +4947,7 @@
       <c r="F26" s="18">
         <v>-2456421.5320672961</v>
       </c>
-      <c r="G26" s="218">
+      <c r="G26" s="103">
         <f>-G30-G31-G36</f>
         <v>-150683.27937900001</v>
       </c>
@@ -4987,7 +4956,7 @@
         <v>-2305738.2526882961</v>
       </c>
       <c r="I26" s="145" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J26" s="18">
         <f t="shared" si="2"/>
@@ -4995,16 +4964,16 @@
       </c>
       <c r="K26" s="18">
         <f t="shared" si="3"/>
-        <v>461244</v>
+        <v>540000</v>
       </c>
       <c r="L26" s="86"/>
       <c r="M26" s="1">
         <f t="shared" si="4"/>
-        <v>-1737122.1040882962</v>
+        <v>-1658366.1040882962</v>
       </c>
       <c r="N26" s="4">
         <f t="shared" si="1"/>
-        <v>-1841349.4303335939</v>
+        <v>-1757868.070333594</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -5024,7 +4993,7 @@
       <c r="F27" s="18">
         <v>558303.59049426531</v>
       </c>
-      <c r="G27" s="219">
+      <c r="G27" s="148">
         <f>668000-G39-G40</f>
         <v>558067.54460400005</v>
       </c>
@@ -5041,16 +5010,16 @@
       </c>
       <c r="K27" s="18">
         <f t="shared" si="3"/>
-        <v>452787.86</v>
+        <v>530100</v>
       </c>
       <c r="L27" s="86"/>
       <c r="M27" s="1">
         <f t="shared" si="4"/>
-        <v>558427.56509926519</v>
+        <v>635739.70509926521</v>
       </c>
       <c r="N27" s="4">
         <f t="shared" si="1"/>
-        <v>591933.21900522115</v>
+        <v>673884.08740522107</v>
       </c>
       <c r="R27" s="52"/>
     </row>
@@ -5071,7 +5040,7 @@
       <c r="F28" s="18">
         <v>556906.99370220723</v>
       </c>
-      <c r="G28" s="219">
+      <c r="G28" s="148">
         <f>658000-G32-G33</f>
         <v>557544.48041400011</v>
       </c>
@@ -5088,16 +5057,16 @@
       </c>
       <c r="K28" s="18">
         <f t="shared" si="3"/>
-        <v>452787.86</v>
+        <v>530100</v>
       </c>
       <c r="L28" s="86"/>
       <c r="M28" s="1">
         <f t="shared" si="4"/>
-        <v>557554.03249720705</v>
+        <v>634866.17249720707</v>
       </c>
       <c r="N28" s="4">
         <f t="shared" si="1"/>
-        <v>591007.27444703947</v>
+        <v>672958.1428470395</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -5117,7 +5086,7 @@
       <c r="F29" s="18">
         <v>557837.2654031018</v>
       </c>
-      <c r="G29" s="218">
+      <c r="G29" s="103">
         <f>558000+153000-G42-G43-G44</f>
         <v>558421.3334590001</v>
       </c>
@@ -5134,16 +5103,16 @@
       </c>
       <c r="K29" s="18">
         <f t="shared" si="3"/>
-        <v>452787.86</v>
+        <v>530100</v>
       </c>
       <c r="L29" s="86"/>
       <c r="M29" s="1">
         <f t="shared" si="4"/>
-        <v>557607.45115310163</v>
+        <v>634919.59115310165</v>
       </c>
       <c r="N29" s="4">
         <f t="shared" si="1"/>
-        <v>591063.89822228777</v>
+        <v>673014.76662228769</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -5163,7 +5132,7 @@
       <c r="F30" s="18">
         <v>51175.453374000004</v>
       </c>
-      <c r="G30" s="219">
+      <c r="G30" s="148">
         <f>F30</f>
         <v>51175.453374000004</v>
       </c>
@@ -5178,16 +5147,16 @@
       </c>
       <c r="K30" s="18">
         <f t="shared" si="3"/>
-        <v>41511.960000000006</v>
+        <v>48600</v>
       </c>
       <c r="L30" s="86"/>
       <c r="M30" s="1">
         <f t="shared" si="4"/>
-        <v>51175.453374000004</v>
+        <v>58263.493373999998</v>
       </c>
       <c r="N30" s="4">
         <f t="shared" si="1"/>
-        <v>54245.980576440008</v>
+        <v>61759.302976439998</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -5207,7 +5176,7 @@
       <c r="F31" s="18">
         <v>52123.146954999997</v>
       </c>
-      <c r="G31" s="219">
+      <c r="G31" s="148">
         <f>F31</f>
         <v>52123.146954999997</v>
       </c>
@@ -5222,16 +5191,16 @@
       </c>
       <c r="K31" s="18">
         <f t="shared" si="3"/>
-        <v>42280.7</v>
+        <v>49500</v>
       </c>
       <c r="L31" s="86"/>
       <c r="M31" s="1">
         <f t="shared" si="4"/>
-        <v>52123.146954999997</v>
+        <v>59342.446954999999</v>
       </c>
       <c r="N31" s="4">
         <f t="shared" si="1"/>
-        <v>55250.535772299998</v>
+        <v>62902.993772299997</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -5251,7 +5220,7 @@
       <c r="F32" s="18">
         <v>42646.211145000001</v>
       </c>
-      <c r="G32" s="219">
+      <c r="G32" s="148">
         <f>F32</f>
         <v>42646.211145000001</v>
       </c>
@@ -5266,16 +5235,16 @@
       </c>
       <c r="K32" s="18">
         <f t="shared" si="3"/>
-        <v>34593.300000000003</v>
+        <v>40500</v>
       </c>
       <c r="L32" s="66"/>
       <c r="M32" s="1">
         <f t="shared" si="4"/>
-        <v>42646.211145000001</v>
+        <v>48552.911144999998</v>
       </c>
       <c r="N32" s="4">
         <f t="shared" si="1"/>
-        <v>45204.983813700004</v>
+        <v>51466.085813699996</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -5295,7 +5264,7 @@
       <c r="F33" s="18">
         <v>57809.308440999994</v>
       </c>
-      <c r="G33" s="219">
+      <c r="G33" s="148">
         <f t="shared" ref="G33" si="5">F33</f>
         <v>57809.308440999994</v>
       </c>
@@ -5310,16 +5279,16 @@
       </c>
       <c r="K33" s="18">
         <f t="shared" si="3"/>
-        <v>46893.14</v>
+        <v>54900</v>
       </c>
       <c r="L33" s="66"/>
       <c r="M33" s="1">
         <f t="shared" si="4"/>
-        <v>57809.308440999994</v>
+        <v>65816.168441000002</v>
       </c>
       <c r="N33" s="4">
         <f t="shared" si="1"/>
-        <v>61277.866947459996</v>
+        <v>69765.138547459996</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -5354,16 +5323,16 @@
       </c>
       <c r="K34" s="18">
         <f t="shared" si="3"/>
-        <v>41511.960000000006</v>
+        <v>48600</v>
       </c>
       <c r="L34" s="66"/>
       <c r="M34" s="1">
         <f t="shared" si="4"/>
-        <v>51175.453374000004</v>
+        <v>58263.493373999998</v>
       </c>
       <c r="N34" s="4">
         <f t="shared" si="1"/>
-        <v>54245.980576440008</v>
+        <v>61759.302976439998</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -5383,7 +5352,7 @@
       <c r="F35" s="152">
         <v>47384.679049999999</v>
       </c>
-      <c r="G35" s="218">
+      <c r="G35" s="103">
         <f>F35</f>
         <v>47384.679049999999</v>
       </c>
@@ -5398,16 +5367,16 @@
       </c>
       <c r="K35" s="18">
         <f t="shared" si="3"/>
-        <v>38437</v>
+        <v>45000</v>
       </c>
       <c r="L35" s="66"/>
       <c r="M35" s="1">
         <f t="shared" si="4"/>
-        <v>47384.679049999999</v>
+        <v>53947.679049999999</v>
       </c>
       <c r="N35" s="4">
         <f t="shared" si="1"/>
-        <v>50227.759792999997</v>
+        <v>57184.539792999996</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -5427,7 +5396,7 @@
       <c r="F36" s="18">
         <v>47384.679049999999</v>
       </c>
-      <c r="G36" s="219">
+      <c r="G36" s="148">
         <f>F36</f>
         <v>47384.679049999999</v>
       </c>
@@ -5442,16 +5411,16 @@
       </c>
       <c r="K36" s="18">
         <f t="shared" si="3"/>
-        <v>38437</v>
+        <v>45000</v>
       </c>
       <c r="L36" s="66"/>
       <c r="M36" s="1">
         <f t="shared" si="4"/>
-        <v>47384.679049999999</v>
+        <v>53947.679049999999</v>
       </c>
       <c r="N36" s="4">
         <f t="shared" si="1"/>
-        <v>50227.759792999997</v>
+        <v>57184.539792999996</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -5471,7 +5440,7 @@
       <c r="F37" s="18">
         <v>46436.985468999999</v>
       </c>
-      <c r="G37" s="219">
+      <c r="G37" s="148">
         <f t="shared" ref="G37:G41" si="6">F37</f>
         <v>46436.985468999999</v>
       </c>
@@ -5486,16 +5455,16 @@
       </c>
       <c r="K37" s="18">
         <f t="shared" si="3"/>
-        <v>37668.26</v>
+        <v>44100</v>
       </c>
       <c r="L37" s="66"/>
       <c r="M37" s="1">
         <f t="shared" si="4"/>
-        <v>46436.985468999999</v>
+        <v>52868.725468999997</v>
       </c>
       <c r="N37" s="4">
         <f t="shared" si="1"/>
-        <v>49223.20459714</v>
+        <v>56040.848997139998</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -5515,7 +5484,7 @@
       <c r="F38" s="18">
         <v>46436.985468999999</v>
       </c>
-      <c r="G38" s="219">
+      <c r="G38" s="148">
         <f t="shared" si="6"/>
         <v>46436.985468999999</v>
       </c>
@@ -5530,16 +5499,16 @@
       </c>
       <c r="K38" s="18">
         <f t="shared" si="3"/>
-        <v>37668.26</v>
+        <v>44100</v>
       </c>
       <c r="L38" s="66"/>
       <c r="M38" s="1">
         <f t="shared" si="4"/>
-        <v>46436.985468999999</v>
+        <v>52868.725468999997</v>
       </c>
       <c r="N38" s="4">
         <f t="shared" si="1"/>
-        <v>49223.20459714</v>
+        <v>56040.848997139998</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -5559,7 +5528,7 @@
       <c r="F39" s="18">
         <v>55913.921279000002</v>
       </c>
-      <c r="G39" s="219">
+      <c r="G39" s="148">
         <f t="shared" si="6"/>
         <v>55913.921279000002</v>
       </c>
@@ -5574,16 +5543,16 @@
       </c>
       <c r="K39" s="18">
         <f t="shared" si="3"/>
-        <v>45355.66</v>
+        <v>53100</v>
       </c>
       <c r="L39" s="66"/>
       <c r="M39" s="1">
         <f t="shared" si="4"/>
-        <v>55913.921279000002</v>
+        <v>63658.261278999998</v>
       </c>
       <c r="N39" s="4">
         <f t="shared" si="1"/>
-        <v>59268.756555740001</v>
+        <v>67477.756955739998</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -5603,7 +5572,7 @@
       <c r="F40" s="18">
         <v>54018.534116999996</v>
       </c>
-      <c r="G40" s="219">
+      <c r="G40" s="148">
         <f t="shared" si="6"/>
         <v>54018.534116999996</v>
       </c>
@@ -5618,16 +5587,16 @@
       </c>
       <c r="K40" s="18">
         <f t="shared" si="3"/>
-        <v>43818.18</v>
+        <v>51300</v>
       </c>
       <c r="L40" s="66"/>
       <c r="M40" s="1">
         <f t="shared" si="4"/>
-        <v>54018.534116999996</v>
+        <v>61500.354116999995</v>
       </c>
       <c r="N40" s="4">
         <f t="shared" si="1"/>
-        <v>57259.646164019992</v>
+        <v>65190.375364019994</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -5647,7 +5616,7 @@
       <c r="F41" s="18">
         <v>51175.453374000004</v>
       </c>
-      <c r="G41" s="219">
+      <c r="G41" s="148">
         <f t="shared" si="6"/>
         <v>51175.453374000004</v>
       </c>
@@ -5662,16 +5631,16 @@
       </c>
       <c r="K41" s="18">
         <f t="shared" si="3"/>
-        <v>41511.960000000006</v>
+        <v>48600</v>
       </c>
       <c r="L41" s="66"/>
       <c r="M41" s="1">
         <f t="shared" si="4"/>
-        <v>51175.453374000004</v>
+        <v>58263.493373999998</v>
       </c>
       <c r="N41" s="4">
         <f t="shared" si="1"/>
-        <v>54245.980576440008</v>
+        <v>61759.302976439998</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -5691,7 +5660,7 @@
       <c r="F42" s="18">
         <v>52123.146954999997</v>
       </c>
-      <c r="G42" s="219">
+      <c r="G42" s="148">
         <f>F42</f>
         <v>52123.146954999997</v>
       </c>
@@ -5706,16 +5675,16 @@
       </c>
       <c r="K42" s="18">
         <f t="shared" si="3"/>
-        <v>42280.7</v>
+        <v>49500</v>
       </c>
       <c r="L42" s="66"/>
       <c r="M42" s="1">
         <f t="shared" si="4"/>
-        <v>52123.146954999997</v>
+        <v>59342.446954999999</v>
       </c>
       <c r="N42" s="4">
         <f t="shared" si="1"/>
-        <v>55250.535772299998</v>
+        <v>62902.993772299997</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -5735,7 +5704,7 @@
       <c r="F43" s="18">
         <v>42646.211145000001</v>
       </c>
-      <c r="G43" s="219">
+      <c r="G43" s="148">
         <f>F43</f>
         <v>42646.211145000001</v>
       </c>
@@ -5750,20 +5719,20 @@
       </c>
       <c r="K43" s="18">
         <f t="shared" si="3"/>
-        <v>34593.300000000003</v>
+        <v>40500</v>
       </c>
       <c r="L43" s="66"/>
       <c r="M43" s="1">
         <f t="shared" si="4"/>
-        <v>42646.211145000001</v>
+        <v>48552.911144999998</v>
       </c>
       <c r="N43" s="4">
         <f t="shared" si="1"/>
-        <v>45204.983813700004</v>
+        <v>51466.085813699996</v>
       </c>
       <c r="P43" s="33">
         <f>L1-K52</f>
-        <v>4839794.9700420005</v>
+        <v>2665176.4066979978</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -5783,7 +5752,7 @@
       <c r="F44" s="18">
         <v>57809.308440999994</v>
       </c>
-      <c r="G44" s="219">
+      <c r="G44" s="148">
         <f>F44</f>
         <v>57809.308440999994</v>
       </c>
@@ -5798,16 +5767,16 @@
       </c>
       <c r="K44" s="18">
         <f t="shared" si="3"/>
-        <v>46893.14</v>
+        <v>54900</v>
       </c>
       <c r="L44" s="66"/>
       <c r="M44" s="1">
         <f t="shared" si="4"/>
-        <v>57809.308440999994</v>
+        <v>65816.168441000002</v>
       </c>
       <c r="N44" s="4">
         <f t="shared" si="1"/>
-        <v>61277.866947459996</v>
+        <v>69765.138547459996</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -5827,7 +5796,7 @@
       <c r="F45" s="18">
         <v>51175.453374000004</v>
       </c>
-      <c r="G45" s="219">
+      <c r="G45" s="148">
         <f t="shared" ref="G45" si="7">F45</f>
         <v>51175.453374000004</v>
       </c>
@@ -5842,16 +5811,16 @@
       </c>
       <c r="K45" s="18">
         <f t="shared" si="3"/>
-        <v>41511.960000000006</v>
+        <v>48600</v>
       </c>
       <c r="L45" s="66"/>
       <c r="M45" s="1">
         <f t="shared" si="4"/>
-        <v>51175.453374000004</v>
+        <v>58263.493373999998</v>
       </c>
       <c r="N45" s="4">
         <f t="shared" si="1"/>
-        <v>54245.980576440008</v>
+        <v>61759.302976439998</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -5869,11 +5838,11 @@
         <v>0.5</v>
       </c>
       <c r="F46" s="18">
-        <v>47384.679049999999</v>
-      </c>
-      <c r="G46" s="219">
+        <v>50227.759792999997</v>
+      </c>
+      <c r="G46" s="148">
         <f t="shared" ref="G46:G51" si="8">F46</f>
-        <v>47384.679049999999</v>
+        <v>50227.759792999997</v>
       </c>
       <c r="H46" s="45">
         <f t="shared" si="0"/>
@@ -5886,16 +5855,16 @@
       </c>
       <c r="K46" s="18">
         <f t="shared" si="3"/>
-        <v>38437</v>
+        <v>45000</v>
       </c>
       <c r="L46" s="66"/>
       <c r="M46" s="1">
         <f t="shared" si="4"/>
-        <v>47384.679049999999</v>
+        <v>53947.679049999999</v>
       </c>
       <c r="N46" s="4">
         <f t="shared" si="1"/>
-        <v>50227.759792999997</v>
+        <v>57184.539792999996</v>
       </c>
       <c r="Q46" t="s">
         <v>101</v>
@@ -5918,7 +5887,7 @@
       <c r="F47" s="18">
         <v>47384.679049999999</v>
       </c>
-      <c r="G47" s="219">
+      <c r="G47" s="148">
         <f t="shared" si="8"/>
         <v>47384.679049999999</v>
       </c>
@@ -5933,16 +5902,16 @@
       </c>
       <c r="K47" s="18">
         <f t="shared" si="3"/>
-        <v>38437</v>
+        <v>45000</v>
       </c>
       <c r="L47" s="66"/>
       <c r="M47" s="1">
         <f t="shared" si="4"/>
-        <v>47384.679049999999</v>
+        <v>53947.679049999999</v>
       </c>
       <c r="N47" s="4">
         <f t="shared" si="1"/>
-        <v>50227.759792999997</v>
+        <v>57184.539792999996</v>
       </c>
       <c r="O47" s="52"/>
       <c r="Q47" s="49">
@@ -5982,16 +5951,16 @@
       </c>
       <c r="K48" s="18">
         <f t="shared" si="3"/>
-        <v>37668.26</v>
+        <v>44100</v>
       </c>
       <c r="L48" s="66"/>
       <c r="M48" s="1">
         <f t="shared" si="4"/>
-        <v>46436.985468999999</v>
+        <v>52868.725468999997</v>
       </c>
       <c r="N48" s="4">
         <f t="shared" si="1"/>
-        <v>49223.20459714</v>
+        <v>56040.848997139998</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
@@ -6012,7 +5981,7 @@
       <c r="F49" s="18">
         <v>46436.985468999999</v>
       </c>
-      <c r="G49" s="219">
+      <c r="G49" s="148">
         <f t="shared" si="8"/>
         <v>46436.985468999999</v>
       </c>
@@ -6027,16 +5996,16 @@
       </c>
       <c r="K49" s="18">
         <f t="shared" si="3"/>
-        <v>37668.26</v>
+        <v>44100</v>
       </c>
       <c r="L49" s="66"/>
       <c r="M49" s="1">
         <f t="shared" si="4"/>
-        <v>46436.985468999999</v>
+        <v>52868.725468999997</v>
       </c>
       <c r="N49" s="4">
         <f t="shared" si="1"/>
-        <v>49223.20459714</v>
+        <v>56040.848997139998</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
@@ -6056,7 +6025,7 @@
       <c r="F50" s="18">
         <v>55913.921279000002</v>
       </c>
-      <c r="G50" s="218">
+      <c r="G50" s="103">
         <f t="shared" si="8"/>
         <v>55913.921279000002</v>
       </c>
@@ -6071,16 +6040,16 @@
       </c>
       <c r="K50" s="18">
         <f t="shared" si="3"/>
-        <v>45355.66</v>
+        <v>53100</v>
       </c>
       <c r="L50" s="66"/>
       <c r="M50" s="1">
         <f t="shared" si="4"/>
-        <v>55913.921279000002</v>
+        <v>63658.261278999998</v>
       </c>
       <c r="N50" s="4">
         <f t="shared" si="1"/>
-        <v>59268.756555740001</v>
+        <v>67477.756955739998</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
@@ -6100,7 +6069,7 @@
       <c r="F51" s="18">
         <v>54018.534116999996</v>
       </c>
-      <c r="G51" s="219">
+      <c r="G51" s="148">
         <f t="shared" si="8"/>
         <v>54018.534116999996</v>
       </c>
@@ -6115,16 +6084,16 @@
       </c>
       <c r="K51" s="18">
         <f t="shared" si="3"/>
-        <v>43818.18</v>
+        <v>51300</v>
       </c>
       <c r="L51" s="66"/>
       <c r="M51" s="1">
         <f t="shared" si="4"/>
-        <v>54018.534116999996</v>
+        <v>61500.354116999995</v>
       </c>
       <c r="N51" s="4">
         <f t="shared" si="1"/>
-        <v>57259.646164019992</v>
+        <v>65190.375364019994</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6138,11 +6107,11 @@
       </c>
       <c r="F52" s="83">
         <f>SUM(F7:F51)</f>
-        <v>6503517.6367330411</v>
+        <v>6523486.0606472259</v>
       </c>
       <c r="G52" s="83">
         <f>SUM(G7:G51)</f>
-        <v>8264798.2205740046</v>
+        <v>7788154.2205740046</v>
       </c>
       <c r="H52" s="19"/>
       <c r="I52" s="19"/>
@@ -6152,55 +6121,55 @@
       </c>
       <c r="K52" s="20">
         <f>SUM(K7:K51)</f>
-        <v>7375912.5599579988</v>
+        <v>8848068.0833020005</v>
       </c>
       <c r="L52" s="85">
         <f>SUM(L7:L51)</f>
-        <v>0</v>
+        <v>380000</v>
       </c>
       <c r="M52" s="21">
         <f>SUM(M7:M51)</f>
-        <v>7404167.7861170406</v>
+        <v>9752935.7333752178</v>
       </c>
       <c r="N52" s="20">
         <f>SUM(N7:N51)</f>
-        <v>7848417.8532840572</v>
+        <v>10338111.877377732</v>
       </c>
       <c r="P52" s="49"/>
     </row>
     <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K53" s="52">
         <f>K52-L1</f>
-        <v>-4839794.9700420005</v>
+        <v>-2665176.4066979978</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="189"/>
-      <c r="D54" s="189"/>
-      <c r="E54" s="189"/>
-      <c r="F54" s="189"/>
-      <c r="G54" s="189"/>
-      <c r="H54" s="189"/>
-      <c r="I54" s="189"/>
-      <c r="J54" s="189"/>
-      <c r="K54" s="189"/>
-      <c r="L54" s="189"/>
-      <c r="M54" s="189"/>
-      <c r="N54" s="189"/>
+      <c r="C54" s="208"/>
+      <c r="D54" s="208"/>
+      <c r="E54" s="208"/>
+      <c r="F54" s="208"/>
+      <c r="G54" s="208"/>
+      <c r="H54" s="208"/>
+      <c r="I54" s="208"/>
+      <c r="J54" s="208"/>
+      <c r="K54" s="208"/>
+      <c r="L54" s="208"/>
+      <c r="M54" s="208"/>
+      <c r="N54" s="208"/>
     </row>
     <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="189"/>
-      <c r="D55" s="189"/>
-      <c r="E55" s="189"/>
-      <c r="F55" s="189"/>
-      <c r="G55" s="189"/>
-      <c r="H55" s="189"/>
-      <c r="I55" s="189"/>
-      <c r="J55" s="189"/>
-      <c r="K55" s="189"/>
-      <c r="L55" s="189"/>
-      <c r="M55" s="189"/>
-      <c r="N55" s="189"/>
+      <c r="C55" s="208"/>
+      <c r="D55" s="208"/>
+      <c r="E55" s="208"/>
+      <c r="F55" s="208"/>
+      <c r="G55" s="208"/>
+      <c r="H55" s="208"/>
+      <c r="I55" s="208"/>
+      <c r="J55" s="208"/>
+      <c r="K55" s="208"/>
+      <c r="L55" s="208"/>
+      <c r="M55" s="208"/>
+      <c r="N55" s="208"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C56" s="68"/>
@@ -6217,107 +6186,109 @@
       <c r="N56" s="68"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="189" t="s">
+      <c r="C57" s="208" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="189"/>
-      <c r="E57" s="189"/>
-      <c r="F57" s="189"/>
-      <c r="G57" s="189"/>
-      <c r="H57" s="189"/>
-      <c r="I57" s="189"/>
-      <c r="J57" s="189"/>
-      <c r="K57" s="189"/>
-      <c r="L57" s="189"/>
-      <c r="M57" s="189"/>
-      <c r="N57" s="189"/>
+      <c r="D57" s="208"/>
+      <c r="E57" s="208"/>
+      <c r="F57" s="208"/>
+      <c r="G57" s="208"/>
+      <c r="H57" s="208"/>
+      <c r="I57" s="208"/>
+      <c r="J57" s="208"/>
+      <c r="K57" s="208"/>
+      <c r="L57" s="208"/>
+      <c r="M57" s="208"/>
+      <c r="N57" s="208"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="189"/>
-      <c r="D58" s="189"/>
-      <c r="E58" s="189"/>
-      <c r="F58" s="189"/>
-      <c r="G58" s="189"/>
-      <c r="H58" s="189"/>
-      <c r="I58" s="189"/>
-      <c r="J58" s="189"/>
-      <c r="K58" s="189"/>
-      <c r="L58" s="189"/>
-      <c r="M58" s="189"/>
-      <c r="N58" s="189"/>
+      <c r="C58" s="208"/>
+      <c r="D58" s="208"/>
+      <c r="E58" s="208"/>
+      <c r="F58" s="208"/>
+      <c r="G58" s="208"/>
+      <c r="H58" s="208"/>
+      <c r="I58" s="208"/>
+      <c r="J58" s="208"/>
+      <c r="K58" s="208"/>
+      <c r="L58" s="208"/>
+      <c r="M58" s="208"/>
+      <c r="N58" s="208"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="189"/>
-      <c r="D59" s="189"/>
-      <c r="E59" s="189"/>
-      <c r="F59" s="189"/>
-      <c r="G59" s="189"/>
-      <c r="H59" s="189"/>
-      <c r="I59" s="189"/>
-      <c r="J59" s="189"/>
-      <c r="K59" s="189"/>
-      <c r="L59" s="189"/>
-      <c r="M59" s="189"/>
-      <c r="N59" s="189"/>
+      <c r="C59" s="208"/>
+      <c r="D59" s="208"/>
+      <c r="E59" s="208"/>
+      <c r="F59" s="208"/>
+      <c r="G59" s="208"/>
+      <c r="H59" s="208"/>
+      <c r="I59" s="208"/>
+      <c r="J59" s="208"/>
+      <c r="K59" s="208"/>
+      <c r="L59" s="208"/>
+      <c r="M59" s="208"/>
+      <c r="N59" s="208"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="189"/>
-      <c r="D60" s="189"/>
-      <c r="E60" s="189"/>
-      <c r="F60" s="189"/>
-      <c r="G60" s="189"/>
-      <c r="H60" s="189"/>
-      <c r="I60" s="189"/>
-      <c r="J60" s="189"/>
-      <c r="K60" s="189"/>
-      <c r="L60" s="189"/>
-      <c r="M60" s="189"/>
-      <c r="N60" s="189"/>
+      <c r="C60" s="208"/>
+      <c r="D60" s="208"/>
+      <c r="E60" s="208"/>
+      <c r="F60" s="208"/>
+      <c r="G60" s="208"/>
+      <c r="H60" s="208"/>
+      <c r="I60" s="208"/>
+      <c r="J60" s="208"/>
+      <c r="K60" s="208"/>
+      <c r="L60" s="208"/>
+      <c r="M60" s="208"/>
+      <c r="N60" s="208"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="189"/>
-      <c r="D61" s="189"/>
-      <c r="E61" s="189"/>
-      <c r="F61" s="189"/>
-      <c r="G61" s="189"/>
-      <c r="H61" s="189"/>
-      <c r="I61" s="189"/>
-      <c r="J61" s="189"/>
-      <c r="K61" s="189"/>
-      <c r="L61" s="189"/>
-      <c r="M61" s="189"/>
-      <c r="N61" s="189"/>
+      <c r="C61" s="208"/>
+      <c r="D61" s="208"/>
+      <c r="E61" s="208"/>
+      <c r="F61" s="208"/>
+      <c r="G61" s="208"/>
+      <c r="H61" s="208"/>
+      <c r="I61" s="208"/>
+      <c r="J61" s="208"/>
+      <c r="K61" s="208"/>
+      <c r="L61" s="208"/>
+      <c r="M61" s="208"/>
+      <c r="N61" s="208"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="189"/>
-      <c r="D62" s="189"/>
-      <c r="E62" s="189"/>
-      <c r="F62" s="189"/>
-      <c r="G62" s="189"/>
-      <c r="H62" s="189"/>
-      <c r="I62" s="189"/>
-      <c r="J62" s="189"/>
-      <c r="K62" s="189"/>
-      <c r="L62" s="189"/>
-      <c r="M62" s="189"/>
-      <c r="N62" s="189"/>
+      <c r="C62" s="208"/>
+      <c r="D62" s="208"/>
+      <c r="E62" s="208"/>
+      <c r="F62" s="208"/>
+      <c r="G62" s="208"/>
+      <c r="H62" s="208"/>
+      <c r="I62" s="208"/>
+      <c r="J62" s="208"/>
+      <c r="K62" s="208"/>
+      <c r="L62" s="208"/>
+      <c r="M62" s="208"/>
+      <c r="N62" s="208"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="189"/>
-      <c r="D63" s="189"/>
-      <c r="E63" s="189"/>
-      <c r="F63" s="189"/>
-      <c r="G63" s="189"/>
-      <c r="H63" s="189"/>
-      <c r="I63" s="189"/>
-      <c r="J63" s="189"/>
-      <c r="K63" s="189"/>
-      <c r="L63" s="189"/>
-      <c r="M63" s="189"/>
-      <c r="N63" s="189"/>
+      <c r="C63" s="208"/>
+      <c r="D63" s="208"/>
+      <c r="E63" s="208"/>
+      <c r="F63" s="208"/>
+      <c r="G63" s="208"/>
+      <c r="H63" s="208"/>
+      <c r="I63" s="208"/>
+      <c r="J63" s="208"/>
+      <c r="K63" s="208"/>
+      <c r="L63" s="208"/>
+      <c r="M63" s="208"/>
+      <c r="N63" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C57:N63"/>
+    <mergeCell ref="C54:N55"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="G5:G6"/>
@@ -6334,8 +6305,6 @@
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="C57:N63"/>
-    <mergeCell ref="C54:N55"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
